--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45401</v>
+        <v>44727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45317</v>
+        <v>44784</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1631,13 +1631,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1680,7 +1675,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1694,10 +1689,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45446</v>
+        <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1709,13 +1704,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1758,7 +1748,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1772,10 +1762,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44480</v>
+        <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1788,7 +1778,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1831,7 +1821,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1845,10 +1835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45282</v>
+        <v>44503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1861,7 +1851,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1904,7 +1894,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1918,10 +1908,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44909</v>
+        <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1933,8 +1923,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45379</v>
+        <v>46008</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2006,13 +2001,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2055,7 +2045,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2069,10 +2059,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46066</v>
+        <v>45887</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2085,7 +2075,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2128,7 +2118,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2142,10 +2132,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45887</v>
+        <v>45719</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2157,8 +2147,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2201,7 +2196,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2211,14 +2206,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45835</v>
+        <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2230,8 +2225,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45838</v>
+        <v>45722</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46071</v>
+        <v>45377</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44784</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45898</v>
+        <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44686</v>
+        <v>45919</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2595,13 +2595,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2644,7 +2639,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45317</v>
+        <v>45838</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2673,13 +2668,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2722,7 +2712,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2736,10 +2726,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45715</v>
+        <v>44670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2751,13 +2741,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2800,7 +2785,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2814,10 +2799,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44700</v>
+        <v>46066</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2830,7 +2815,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2873,7 +2858,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2887,10 +2872,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45919</v>
+        <v>46071</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2903,7 +2888,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2946,7 +2931,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2960,10 +2945,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44991</v>
+        <v>45939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2976,7 +2961,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3019,7 +3004,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3033,10 +3018,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45644</v>
+        <v>45281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3049,7 +3034,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3092,7 +3077,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3106,10 +3091,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45939</v>
+        <v>45317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3121,8 +3106,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3165,7 +3155,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3175,14 +3165,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46087</v>
+        <v>44931</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3195,7 +3185,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3238,7 +3228,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3248,14 +3238,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46097</v>
+        <v>46087</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3268,7 +3258,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3328,7 +3318,7 @@
         <v>45950</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3384,7 +3374,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3398,10 +3388,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46106</v>
+        <v>45351</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3414,7 +3404,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3457,7 +3447,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3471,10 +3461,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44804</v>
+        <v>45542</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3487,7 +3477,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3530,7 +3520,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3544,10 +3534,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46120</v>
+        <v>46097</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3560,7 +3550,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3603,7 +3593,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3617,10 +3607,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46119</v>
+        <v>46106</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3633,7 +3623,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3676,7 +3666,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3690,10 +3680,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44473</v>
+        <v>46119</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3706,7 +3696,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3749,7 +3739,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3759,14 +3749,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>46120</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3779,7 +3769,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3822,7 +3812,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3836,10 +3826,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>44473</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3852,7 +3842,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3895,7 +3885,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3905,14 +3895,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44795</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3925,7 +3915,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3968,7 +3958,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3982,10 +3972,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45926</v>
+        <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3998,7 +3988,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4041,7 +4031,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4055,10 +4045,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46008</v>
+        <v>45545</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4071,7 +4061,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4114,7 +4104,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4128,10 +4118,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45542</v>
+        <v>45887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4144,7 +4134,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4187,7 +4177,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4201,10 +4191,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45719</v>
+        <v>45233</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4216,13 +4206,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4265,7 +4250,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4279,10 +4264,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45656</v>
+        <v>45317</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4294,8 +4279,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4338,7 +4328,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4352,10 +4342,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44503</v>
+        <v>45926</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4368,7 +4358,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4411,7 +4401,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4425,10 +4415,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44727</v>
+        <v>45401</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4441,7 +4431,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4484,7 +4474,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4498,10 +4488,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45887</v>
+        <v>45190</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4514,7 +4504,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4557,7 +4547,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4571,10 +4561,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45545</v>
+        <v>44991</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4587,7 +4577,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4630,7 +4620,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4644,10 +4634,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45133</v>
+        <v>46147</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4660,7 +4650,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4703,7 +4693,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4717,10 +4707,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46147</v>
+        <v>44795</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4733,7 +4723,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4776,7 +4766,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4790,10 +4780,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45007</v>
+        <v>45600</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4806,7 +4796,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4849,7 +4839,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4863,10 +4853,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45329</v>
+        <v>46174</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4879,7 +4869,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4922,7 +4912,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4936,10 +4926,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45600</v>
+        <v>46196</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4952,7 +4942,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4995,7 +4985,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5009,10 +4999,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44670</v>
+        <v>46238</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5025,7 +5015,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5068,7 +5058,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5082,10 +5072,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45351</v>
+        <v>44804</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5098,7 +5088,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5141,7 +5131,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5155,10 +5145,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46174</v>
+        <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5171,7 +5161,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5214,7 +5204,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5228,10 +5218,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45233</v>
+        <v>46209</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5244,7 +5234,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5287,7 +5277,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5301,10 +5291,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45190</v>
+        <v>45656</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5317,7 +5307,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5360,7 +5350,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5374,10 +5364,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44931</v>
+        <v>46254</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5390,7 +5380,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5433,7 +5423,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5447,10 +5437,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45322</v>
+        <v>46260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5463,7 +5453,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5506,7 +5496,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5520,10 +5510,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45322</v>
+        <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5536,7 +5526,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5579,7 +5569,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5593,10 +5583,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46196</v>
+        <v>46268</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5609,7 +5599,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5652,7 +5642,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5666,10 +5656,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46238</v>
+        <v>45131</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5682,7 +5672,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5725,7 +5715,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5739,10 +5729,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45400</v>
+        <v>45282</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5755,7 +5745,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5798,7 +5788,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5812,10 +5802,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44473</v>
+        <v>45750</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5828,7 +5818,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5871,7 +5861,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5885,10 +5875,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44677</v>
+        <v>45400</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5900,13 +5890,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5949,7 +5934,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5963,10 +5948,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45281</v>
+        <v>45133</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5979,7 +5964,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6022,7 +6007,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6036,10 +6021,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46209</v>
+        <v>44480</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6052,7 +6037,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6095,7 +6080,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6109,10 +6094,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44503</v>
+        <v>45644</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6125,7 +6110,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6168,7 +6153,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6182,10 +6167,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46254</v>
+        <v>44473</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6198,7 +6183,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6241,7 +6226,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 12421-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6255,10 +6240,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45131</v>
+        <v>45379</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6268,6 +6253,11 @@
       <c r="G78" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -6314,7 +6304,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6328,10 +6318,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46260</v>
+        <v>44700</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6344,7 +6334,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6387,7 +6377,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6401,10 +6391,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45750</v>
+        <v>44677</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6416,8 +6406,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6460,7 +6455,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6474,10 +6469,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46265</v>
+        <v>44909</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6490,7 +6485,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6550,7 +6545,7 @@
         <v>44815</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6606,7 +6601,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6620,10 +6615,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46268</v>
+        <v>45329</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6636,7 +6631,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6679,7 +6674,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6693,10 +6688,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45056</v>
+        <v>44686</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6708,8 +6703,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45719</v>
+        <v>45007</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6779,11 +6779,6 @@
       <c r="G85" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -6830,7 +6825,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6844,10 +6839,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45715</v>
+        <v>45056</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6859,13 +6854,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6908,7 +6898,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6922,10 +6912,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45722</v>
+        <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6937,8 +6927,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6981,7 +6976,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6995,10 +6990,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45377</v>
+        <v>45715</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7010,8 +7005,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44502</v>
+        <v>45401</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44686</v>
+        <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1480,13 +1480,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1529,7 +1524,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1543,10 +1538,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44727</v>
+        <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1558,8 +1553,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44784</v>
+        <v>45233</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45322</v>
+        <v>45190</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45322</v>
+        <v>44931</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44503</v>
+        <v>45317</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1850,8 +1850,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1894,7 +1899,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1908,10 +1913,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45715</v>
+        <v>44480</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1923,13 +1928,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46008</v>
+        <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2001,8 +2001,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2062,7 +2067,7 @@
         <v>45887</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2118,7 +2123,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2128,14 +2133,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45719</v>
+        <v>46087</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2147,13 +2152,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45446</v>
+        <v>46097</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2225,13 +2225,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2288,10 +2283,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45722</v>
+        <v>45898</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2304,7 +2299,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2347,7 +2342,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45377</v>
+        <v>45282</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2420,7 +2415,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>44909</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2450,7 +2445,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2493,7 +2488,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2503,14 +2498,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45835</v>
+        <v>46106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2523,7 +2518,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2583,7 +2578,7 @@
         <v>45919</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2639,7 +2634,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 12421-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2653,10 +2648,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45838</v>
+        <v>45379</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2668,8 +2663,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44670</v>
+        <v>46120</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46066</v>
+        <v>46119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46071</v>
+        <v>45322</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45939</v>
+        <v>45322</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3004,7 +3004,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45281</v>
+        <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3077,7 +3077,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45317</v>
+        <v>45400</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3106,13 +3106,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>10.2</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3155,7 +3150,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3169,10 +3164,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44931</v>
+        <v>45950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3185,7 +3180,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3228,7 +3223,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3238,14 +3233,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46087</v>
+        <v>44784</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3258,7 +3253,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3301,7 +3296,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3315,10 +3310,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45950</v>
+        <v>44686</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3330,8 +3325,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45351</v>
+        <v>45317</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3403,8 +3403,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3447,7 +3452,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3461,10 +3466,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45542</v>
+        <v>45887</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3477,7 +3482,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3520,7 +3525,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3534,10 +3539,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46097</v>
+        <v>45715</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3549,8 +3554,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3593,7 +3603,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3607,10 +3617,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46106</v>
+        <v>45545</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3623,7 +3633,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3666,7 +3676,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3680,10 +3690,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46119</v>
+        <v>44700</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3696,7 +3706,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3739,7 +3749,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3753,10 +3763,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46120</v>
+        <v>44991</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3769,7 +3779,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3812,7 +3822,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3822,14 +3832,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44473</v>
+        <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3842,7 +3852,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3885,7 +3895,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3895,14 +3905,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3915,7 +3925,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3958,7 +3968,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3972,10 +3982,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45979</v>
+        <v>45644</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3988,7 +3998,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4031,7 +4041,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4045,10 +4055,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45545</v>
+        <v>44473</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4061,7 +4071,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4104,7 +4114,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4118,10 +4128,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45887</v>
+        <v>44677</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4133,8 +4143,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4177,7 +4192,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4191,10 +4206,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45233</v>
+        <v>46147</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4207,7 +4222,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4250,7 +4265,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4264,10 +4279,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45317</v>
+        <v>45926</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4279,13 +4294,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4328,7 +4338,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4342,10 +4352,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45926</v>
+        <v>46008</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4358,7 +4368,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4401,7 +4411,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4415,10 +4425,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45401</v>
+        <v>44804</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4431,7 +4441,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4474,7 +4484,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4488,10 +4498,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45190</v>
+        <v>45600</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4504,7 +4514,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4547,7 +4557,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4561,10 +4571,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44991</v>
+        <v>45719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4576,8 +4586,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4620,7 +4635,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4634,10 +4649,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46147</v>
+        <v>45281</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4650,7 +4665,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4693,7 +4708,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4707,10 +4722,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44795</v>
+        <v>44473</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4723,7 +4738,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4766,7 +4781,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4780,10 +4795,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45600</v>
+        <v>44795</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4796,7 +4811,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4856,7 +4871,7 @@
         <v>46174</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4912,7 +4927,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4926,10 +4941,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46196</v>
+        <v>45542</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4942,7 +4957,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4985,7 +5000,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4999,10 +5014,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46238</v>
+        <v>44503</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5015,7 +5030,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5058,7 +5073,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5072,10 +5087,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44804</v>
+        <v>45656</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5088,7 +5103,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5131,7 +5146,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5145,10 +5160,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44503</v>
+        <v>46066</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5161,7 +5176,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5204,7 +5219,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5218,10 +5233,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46209</v>
+        <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5234,7 +5249,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5277,7 +5292,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5291,10 +5306,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45656</v>
+        <v>44727</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5307,7 +5322,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5350,7 +5365,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5364,10 +5379,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46254</v>
+        <v>46071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5380,7 +5395,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5423,7 +5438,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5437,10 +5452,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46260</v>
+        <v>45133</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5453,7 +5468,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5496,7 +5511,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5510,10 +5525,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46265</v>
+        <v>45131</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5526,7 +5541,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5569,7 +5584,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5583,10 +5598,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46268</v>
+        <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5599,7 +5614,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5642,7 +5657,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5656,10 +5671,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45131</v>
+        <v>45007</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5672,7 +5687,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5715,7 +5730,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5729,10 +5744,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45282</v>
+        <v>46209</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5745,7 +5760,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5805,7 +5820,7 @@
         <v>45750</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5861,7 +5876,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5875,10 +5890,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45400</v>
+        <v>45329</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5891,7 +5906,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5934,7 +5949,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5948,10 +5963,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45133</v>
+        <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5964,7 +5979,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6007,7 +6022,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6021,10 +6036,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44480</v>
+        <v>44670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6037,7 +6052,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6080,7 +6095,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6094,10 +6109,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45644</v>
+        <v>45351</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6110,7 +6125,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6153,7 +6168,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6167,10 +6182,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44473</v>
+        <v>44815</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6183,7 +6198,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6226,7 +6241,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6240,10 +6255,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45379</v>
+        <v>46260</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6255,13 +6270,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6304,7 +6314,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6318,10 +6328,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44700</v>
+        <v>46265</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6334,7 +6344,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6377,7 +6387,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6391,10 +6401,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44677</v>
+        <v>46268</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6406,13 +6416,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6455,7 +6460,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6469,10 +6474,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44909</v>
+        <v>46238</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6485,7 +6490,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6528,7 +6533,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6542,10 +6547,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44815</v>
+        <v>45056</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6558,7 +6563,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6601,7 +6606,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6615,10 +6620,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45329</v>
+        <v>45719</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6628,6 +6633,11 @@
       <c r="G83" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -6674,7 +6684,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6688,10 +6698,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44686</v>
+        <v>45715</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6705,11 +6715,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6752,7 +6762,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6766,10 +6776,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45007</v>
+        <v>45722</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6782,7 +6792,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6825,7 +6835,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6839,10 +6849,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45056</v>
+        <v>45377</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6855,7 +6865,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6898,7 +6908,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6908,14 +6918,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45719</v>
+        <v>45835</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6927,13 +6937,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6976,7 +6981,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6990,10 +6995,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45715</v>
+        <v>45838</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7005,13 +7010,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45401</v>
+        <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44502</v>
+        <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1480,8 +1480,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1524,7 +1529,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44686</v>
+        <v>44727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1553,13 +1558,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45233</v>
+        <v>45322</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45190</v>
+        <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44931</v>
+        <v>44784</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45317</v>
+        <v>44503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1850,13 +1850,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>10.2</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1899,7 +1894,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1913,10 +1908,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44480</v>
+        <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1928,8 +1923,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45887</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46097</v>
+        <v>45377</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45898</v>
+        <v>44670</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45282</v>
+        <v>45898</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2425,14 +2425,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44909</v>
+        <v>45835</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46106</v>
+        <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
         <v>45919</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45379</v>
+        <v>45281</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2663,13 +2663,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2712,7 +2707,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2726,10 +2721,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46120</v>
+        <v>45317</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2741,8 +2736,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>10.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46119</v>
+        <v>44931</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45322</v>
+        <v>45542</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45400</v>
+        <v>45950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45950</v>
+        <v>44473</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44784</v>
+        <v>46066</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3296,7 +3296,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3306,14 +3306,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44686</v>
+        <v>45979</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3325,13 +3325,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3374,7 +3369,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3388,10 +3383,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45317</v>
+        <v>46071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3403,13 +3398,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3452,7 +3442,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3466,10 +3456,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45887</v>
+        <v>45979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3482,7 +3472,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3525,7 +3515,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3539,10 +3529,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45715</v>
+        <v>45233</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3554,13 +3544,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3603,7 +3588,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3617,10 +3602,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45545</v>
+        <v>45317</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3632,8 +3617,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3676,7 +3666,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3686,14 +3676,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44700</v>
+        <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3706,7 +3696,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3749,7 +3739,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44991</v>
+        <v>45926</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3779,7 +3769,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3822,7 +3812,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3832,14 +3822,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>46008</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3852,7 +3842,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3895,7 +3885,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3909,10 +3899,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>45401</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3925,7 +3915,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3968,7 +3958,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3982,10 +3972,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45644</v>
+        <v>45190</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3998,7 +3988,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4041,7 +4031,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4055,10 +4045,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44473</v>
+        <v>44991</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4071,7 +4061,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4114,7 +4104,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4128,10 +4118,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44677</v>
+        <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4145,11 +4135,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4192,7 +4182,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4206,10 +4196,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46147</v>
+        <v>46097</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4222,7 +4212,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4265,7 +4255,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4279,10 +4269,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45926</v>
+        <v>46106</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4295,7 +4285,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4338,7 +4328,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4352,10 +4342,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46008</v>
+        <v>44795</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4368,7 +4358,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4411,7 +4401,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4425,10 +4415,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44804</v>
+        <v>46119</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4441,7 +4431,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4484,7 +4474,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4498,10 +4488,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45600</v>
+        <v>46120</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4514,7 +4504,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4557,7 +4547,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4571,10 +4561,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45719</v>
+        <v>44804</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4586,13 +4576,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4635,7 +4620,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4649,10 +4634,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45281</v>
+        <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4665,7 +4650,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4708,7 +4693,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4722,10 +4707,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44473</v>
+        <v>45656</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4738,7 +4723,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4781,7 +4766,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4795,10 +4780,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44795</v>
+        <v>45545</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4811,7 +4796,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4854,7 +4839,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4868,10 +4853,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46174</v>
+        <v>45887</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4884,7 +4869,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4927,7 +4912,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4941,10 +4926,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45542</v>
+        <v>45131</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4957,7 +4942,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5000,7 +4985,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5014,10 +4999,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44503</v>
+        <v>45282</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5030,7 +5015,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5073,7 +5058,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5087,10 +5072,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45656</v>
+        <v>45750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5103,7 +5088,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5146,7 +5131,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5160,10 +5145,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46066</v>
+        <v>45400</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5176,7 +5161,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5219,7 +5204,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5233,10 +5218,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44503</v>
+        <v>46147</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5249,7 +5234,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5292,7 +5277,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5306,10 +5291,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44727</v>
+        <v>45133</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5322,7 +5307,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5365,7 +5350,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5379,10 +5364,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46071</v>
+        <v>45600</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5395,7 +5380,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5438,7 +5423,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5452,10 +5437,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45133</v>
+        <v>44480</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5468,7 +5453,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5511,7 +5496,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5525,10 +5510,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45131</v>
+        <v>46174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5541,7 +5526,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5584,7 +5569,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5598,10 +5583,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46196</v>
+        <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5614,7 +5599,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5657,7 +5642,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5671,10 +5656,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45007</v>
+        <v>44473</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5687,7 +5672,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5730,7 +5715,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 12421-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5744,10 +5729,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46209</v>
+        <v>45379</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5759,8 +5744,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5803,7 +5793,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5817,10 +5807,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45750</v>
+        <v>44700</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5833,7 +5823,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5876,7 +5866,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5890,10 +5880,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45329</v>
+        <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5905,8 +5895,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5949,7 +5944,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5963,10 +5958,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46254</v>
+        <v>44909</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5979,7 +5974,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6022,7 +6017,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44670</v>
+        <v>46196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6052,7 +6047,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6095,7 +6090,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45351</v>
+        <v>46209</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6125,7 +6120,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6185,7 +6180,7 @@
         <v>44815</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6241,7 +6236,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6255,10 +6250,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46260</v>
+        <v>46254</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6271,7 +6266,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6314,7 +6309,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6328,10 +6323,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46265</v>
+        <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6344,7 +6339,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6387,7 +6382,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6401,10 +6396,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46268</v>
+        <v>44686</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6416,8 +6411,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6460,7 +6460,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46238</v>
+        <v>46260</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6533,7 +6533,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45056</v>
+        <v>45007</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6606,7 +6606,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6620,10 +6620,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45719</v>
+        <v>46265</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6635,13 +6635,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6684,7 +6679,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6698,10 +6693,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45715</v>
+        <v>46268</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6713,13 +6708,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6762,7 +6752,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6776,10 +6766,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45722</v>
+        <v>46238</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6792,7 +6782,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6835,7 +6825,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6849,10 +6839,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45377</v>
+        <v>45056</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6865,7 +6855,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6908,7 +6898,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6918,14 +6908,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45835</v>
+        <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6937,8 +6927,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6981,7 +6976,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6995,10 +6990,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45838</v>
+        <v>45715</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7010,8 +7005,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44727</v>
+        <v>45401</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45322</v>
+        <v>45317</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1631,8 +1631,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>10.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1675,7 +1680,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1689,10 +1694,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45322</v>
+        <v>45446</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1704,8 +1709,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1748,7 +1758,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,10 +1772,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44784</v>
+        <v>44480</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1778,7 +1788,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1821,7 +1831,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1835,10 +1845,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44503</v>
+        <v>44909</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1851,7 +1861,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1894,7 +1904,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1908,10 +1918,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45715</v>
+        <v>45282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1923,13 +1933,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 12421-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45446</v>
+        <v>45379</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2003,11 +2008,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2050,7 +2055,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2064,10 +2069,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45887</v>
+        <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2080,7 +2085,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2123,7 +2128,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2137,10 +2142,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45722</v>
+        <v>46071</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2153,7 +2158,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2196,7 +2201,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2210,10 +2215,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45377</v>
+        <v>45887</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2226,7 +2231,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2269,7 +2274,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2279,14 +2284,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44670</v>
+        <v>45835</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2299,7 +2304,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45898</v>
+        <v>45838</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2372,7 +2377,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2415,7 +2420,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2425,14 +2430,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45835</v>
+        <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2445,7 +2450,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2488,7 +2493,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45838</v>
+        <v>44784</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2518,7 +2523,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2561,7 +2566,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45919</v>
+        <v>44686</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2590,8 +2595,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2634,7 +2644,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2648,10 +2658,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45281</v>
+        <v>46097</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2664,7 +2674,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2707,7 +2717,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2724,7 +2734,7 @@
         <v>45317</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2742,7 +2752,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.2</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2785,7 +2795,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2799,10 +2809,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44931</v>
+        <v>45715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2814,8 +2824,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2858,7 +2873,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2872,10 +2887,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2888,7 +2903,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2931,7 +2946,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,10 +2960,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45542</v>
+        <v>46106</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2961,7 +2976,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3004,7 +3019,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3018,10 +3033,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45939</v>
+        <v>44991</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3034,7 +3049,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3077,7 +3092,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3091,10 +3106,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45950</v>
+        <v>46120</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3107,7 +3122,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3150,7 +3165,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3164,10 +3179,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44473</v>
+        <v>46119</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3180,7 +3195,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3223,7 +3238,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3237,10 +3252,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46066</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3253,7 +3268,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3296,7 +3311,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3306,14 +3321,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45979</v>
+        <v>45898</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3326,7 +3341,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3369,7 +3384,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3383,10 +3398,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46071</v>
+        <v>45919</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3399,7 +3414,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3442,7 +3457,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3456,10 +3471,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45979</v>
+        <v>44804</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3472,7 +3487,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3515,7 +3530,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3529,10 +3544,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45233</v>
+        <v>45887</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3545,7 +3560,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3588,7 +3603,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3602,10 +3617,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45317</v>
+        <v>45545</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3617,13 +3632,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3666,7 +3676,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3676,14 +3686,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46087</v>
+        <v>44473</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3696,7 +3706,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3739,7 +3749,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3753,10 +3763,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45926</v>
+        <v>44795</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3769,7 +3779,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3812,7 +3822,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3826,10 +3836,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46008</v>
+        <v>46147</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3842,7 +3852,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3885,7 +3895,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3899,10 +3909,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45401</v>
+        <v>45542</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3915,7 +3925,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3958,7 +3968,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3972,10 +3982,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45190</v>
+        <v>45656</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3988,7 +3998,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4031,7 +4041,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4045,10 +4055,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44991</v>
+        <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4061,7 +4071,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4104,7 +4114,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4118,10 +4128,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45719</v>
+        <v>45600</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4133,13 +4143,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4182,7 +4187,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46097</v>
+        <v>44727</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4212,7 +4217,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>8.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4255,7 +4260,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4269,10 +4274,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46106</v>
+        <v>45939</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4285,7 +4290,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4328,7 +4333,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4342,10 +4347,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44795</v>
+        <v>45133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4401,7 +4406,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4415,10 +4420,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46119</v>
+        <v>46174</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4431,7 +4436,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4474,7 +4479,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4488,10 +4493,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46120</v>
+        <v>45950</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4504,7 +4509,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4547,7 +4552,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4561,10 +4566,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44804</v>
+        <v>45007</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4577,7 +4582,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4620,7 +4625,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4634,10 +4639,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44503</v>
+        <v>45329</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4693,7 +4698,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4707,10 +4712,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45656</v>
+        <v>46196</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4723,7 +4728,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4766,7 +4771,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4780,10 +4785,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45545</v>
+        <v>44670</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4796,7 +4801,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4839,7 +4844,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4849,14 +4854,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45887</v>
+        <v>45979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4869,7 +4874,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4912,7 +4917,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45131</v>
+        <v>45979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4942,7 +4947,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4985,7 +4990,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4999,10 +5004,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45282</v>
+        <v>45351</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5015,7 +5020,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5058,7 +5063,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5072,10 +5077,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45750</v>
+        <v>46209</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5088,7 +5093,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5131,7 +5136,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5145,10 +5150,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45400</v>
+        <v>46254</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5161,7 +5166,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5204,7 +5209,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5218,10 +5223,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46147</v>
+        <v>45233</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5234,7 +5239,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5277,7 +5282,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5291,10 +5296,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45133</v>
+        <v>45190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5307,7 +5312,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5350,7 +5355,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5364,10 +5369,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45600</v>
+        <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5380,7 +5385,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5423,7 +5428,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44480</v>
+        <v>46260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5453,7 +5458,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5496,7 +5501,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5510,10 +5515,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46174</v>
+        <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5526,7 +5531,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5569,7 +5574,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5583,10 +5588,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45644</v>
+        <v>45926</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5599,7 +5604,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5642,7 +5647,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5656,10 +5661,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44473</v>
+        <v>46268</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5672,7 +5677,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5715,7 +5720,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5729,10 +5734,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45379</v>
+        <v>46008</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5744,13 +5749,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44700</v>
+        <v>45719</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5822,8 +5822,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5866,7 +5871,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5880,10 +5885,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44677</v>
+        <v>45322</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5895,13 +5900,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44909</v>
+        <v>45322</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46196</v>
+        <v>45400</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46209</v>
+        <v>44473</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44815</v>
+        <v>44677</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6192,8 +6192,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6236,7 +6241,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6250,10 +6255,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46254</v>
+        <v>46238</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6266,7 +6271,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6309,7 +6314,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6323,10 +6328,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45329</v>
+        <v>45281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6339,7 +6344,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6382,7 +6387,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6396,10 +6401,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44686</v>
+        <v>44503</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6411,13 +6416,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6460,7 +6460,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46260</v>
+        <v>45131</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6533,7 +6533,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45007</v>
+        <v>45750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6606,7 +6606,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6620,10 +6620,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46265</v>
+        <v>44815</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6679,7 +6679,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46268</v>
+        <v>45056</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46238</v>
+        <v>45719</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6781,8 +6781,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6825,7 +6830,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6839,10 +6844,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45056</v>
+        <v>45715</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6854,8 +6859,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6898,7 +6908,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6912,10 +6922,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45719</v>
+        <v>45722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6927,13 +6937,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6976,7 +6981,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6990,10 +6995,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45715</v>
+        <v>45377</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7005,13 +7010,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45401</v>
+        <v>44727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45317</v>
+        <v>44784</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1631,13 +1631,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1680,7 +1675,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1694,10 +1689,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45446</v>
+        <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1709,13 +1704,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1758,7 +1748,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1772,10 +1762,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44480</v>
+        <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1788,7 +1778,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1831,7 +1821,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1845,10 +1835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44909</v>
+        <v>44503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1861,7 +1851,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1904,7 +1894,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1918,10 +1908,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45282</v>
+        <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1933,8 +1923,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45379</v>
+        <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2008,11 +2003,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2055,7 +2050,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2069,10 +2064,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46066</v>
+        <v>44670</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2085,7 +2080,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2128,7 +2123,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2142,10 +2137,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46071</v>
+        <v>45317</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2157,8 +2152,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>10.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45887</v>
+        <v>45281</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2284,14 +2284,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45835</v>
+        <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45838</v>
+        <v>44931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2430,14 +2430,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46087</v>
+        <v>45542</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44784</v>
+        <v>44473</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44686</v>
+        <v>45887</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2595,13 +2595,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2644,7 +2639,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46097</v>
+        <v>45233</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2674,7 +2669,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2734,7 +2729,7 @@
         <v>45317</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2795,7 +2790,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2809,10 +2804,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45715</v>
+        <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2824,13 +2819,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2873,7 +2863,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2887,10 +2877,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44700</v>
+        <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2903,7 +2893,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2946,7 +2936,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2960,10 +2950,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46106</v>
+        <v>45190</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2976,7 +2966,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3036,7 +3026,7 @@
         <v>44991</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3092,7 +3082,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3106,10 +3096,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46120</v>
+        <v>45919</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3122,7 +3112,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3165,7 +3155,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3179,10 +3169,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46119</v>
+        <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3195,7 +3185,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3238,7 +3228,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3252,10 +3242,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>46147</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3268,7 +3258,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3311,7 +3301,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3325,10 +3315,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45898</v>
+        <v>45939</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3341,7 +3331,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3384,7 +3374,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3398,10 +3388,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45919</v>
+        <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3414,7 +3404,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3474,7 +3464,7 @@
         <v>44804</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3530,7 +3520,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3544,10 +3534,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45887</v>
+        <v>44503</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3560,7 +3550,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3603,7 +3593,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3617,10 +3607,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45545</v>
+        <v>45656</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3633,7 +3623,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3676,7 +3666,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3686,14 +3676,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44473</v>
+        <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3706,7 +3696,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3749,7 +3739,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44795</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3779,7 +3769,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3822,7 +3812,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3836,10 +3826,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46147</v>
+        <v>45600</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3852,7 +3842,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3895,7 +3885,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3909,10 +3899,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45542</v>
+        <v>45131</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3925,7 +3915,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3968,7 +3958,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3982,10 +3972,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45656</v>
+        <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3998,7 +3988,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4041,7 +4031,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4055,10 +4045,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44503</v>
+        <v>45750</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4071,7 +4061,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4114,7 +4104,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4128,10 +4118,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45600</v>
+        <v>45400</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4144,7 +4134,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4187,7 +4177,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4201,10 +4191,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44727</v>
+        <v>45926</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4217,7 +4207,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4260,7 +4250,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4274,10 +4264,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45939</v>
+        <v>45133</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4290,7 +4280,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4333,7 +4323,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4347,10 +4337,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45133</v>
+        <v>46008</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4363,7 +4353,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4406,7 +4396,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4420,10 +4410,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46174</v>
+        <v>45719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4435,8 +4425,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4479,7 +4474,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4493,10 +4488,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45950</v>
+        <v>44480</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4509,7 +4504,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4552,7 +4547,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4566,10 +4561,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45007</v>
+        <v>46174</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4582,7 +4577,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4625,7 +4620,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4639,10 +4634,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45329</v>
+        <v>45644</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4655,7 +4650,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4698,7 +4693,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4712,10 +4707,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46196</v>
+        <v>44473</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4728,7 +4723,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4771,7 +4766,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4785,10 +4780,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44670</v>
+        <v>46066</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4801,7 +4796,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4844,7 +4839,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 12421-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4854,14 +4849,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45979</v>
+        <v>45379</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4873,8 +4868,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45979</v>
+        <v>46071</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4990,7 +4990,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46209</v>
+        <v>44677</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5092,8 +5092,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5136,7 +5141,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5146,14 +5151,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46254</v>
+        <v>46087</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5166,7 +5171,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5209,7 +5214,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45233</v>
+        <v>44909</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5282,7 +5287,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5296,10 +5301,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45190</v>
+        <v>46097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5312,7 +5317,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5355,7 +5360,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44931</v>
+        <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5385,7 +5390,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5428,7 +5433,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5442,10 +5447,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46260</v>
+        <v>46106</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5458,7 +5463,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5501,7 +5506,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5515,10 +5520,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46265</v>
+        <v>46119</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5531,7 +5536,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5574,7 +5579,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5588,10 +5593,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45926</v>
+        <v>46120</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5604,7 +5609,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5647,7 +5652,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5661,10 +5666,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46268</v>
+        <v>44815</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5677,7 +5682,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5720,7 +5725,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46008</v>
+        <v>45545</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5750,7 +5755,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5793,7 +5798,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5807,10 +5812,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45719</v>
+        <v>45329</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5822,13 +5827,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45322</v>
+        <v>45887</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45322</v>
+        <v>44686</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5973,8 +5973,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6017,7 +6022,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45400</v>
+        <v>46209</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6047,7 +6052,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6090,7 +6095,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44473</v>
+        <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6120,7 +6125,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6163,7 +6168,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44677</v>
+        <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6192,13 +6197,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46238</v>
+        <v>46260</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45281</v>
+        <v>46265</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44503</v>
+        <v>46268</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6460,7 +6460,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45131</v>
+        <v>45056</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6533,7 +6533,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45750</v>
+        <v>45719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6562,8 +6562,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6606,7 +6611,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6620,10 +6625,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44815</v>
+        <v>45715</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6635,8 +6640,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6679,7 +6689,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6693,10 +6703,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45056</v>
+        <v>46238</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6709,7 +6719,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6752,7 +6762,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6766,10 +6776,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45719</v>
+        <v>45722</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6781,13 +6791,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6830,7 +6835,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6844,10 +6849,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45715</v>
+        <v>45377</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6859,13 +6864,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6908,7 +6908,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6918,14 +6918,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45722</v>
+        <v>45835</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45377</v>
+        <v>45838</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>44727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44784</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>44670</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45317</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45281</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45542</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44473</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45887</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>45233</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45317</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45190</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>44991</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45919</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>46147</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45939</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>44804</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>44503</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45656</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45600</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45131</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45750</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45400</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45926</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45133</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>46008</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44480</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>46174</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>45644</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>44473</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46066</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45379</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>46071</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44677</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46087</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>44909</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46106</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>46119</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>46120</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44815</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45545</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45329</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45887</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>44686</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>46209</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>46260</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>46265</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>46268</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45056</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>45719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>45715</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>46238</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>45722</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45377</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45835</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45838</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE88"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>44727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44784</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>44670</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45317</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45281</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44931</v>
+        <v>45542</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45542</v>
+        <v>44931</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44473</v>
+        <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45887</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45233</v>
+        <v>45887</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45317</v>
+        <v>44473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2741,13 +2741,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2807,7 +2802,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2863,7 +2858,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45401</v>
+        <v>45919</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2893,7 +2888,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2936,7 +2931,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2950,10 +2945,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45190</v>
+        <v>45233</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2966,7 +2961,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3009,7 +3004,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3023,10 +3018,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44991</v>
+        <v>45317</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3038,8 +3033,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45919</v>
+        <v>46147</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44795</v>
+        <v>45939</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46147</v>
+        <v>45401</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45939</v>
+        <v>45190</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45950</v>
+        <v>44991</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44804</v>
+        <v>45950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44503</v>
+        <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45656</v>
+        <v>44795</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.5</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3683,7 +3683,7 @@
         <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45600</v>
+        <v>44804</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45131</v>
+        <v>46174</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45282</v>
+        <v>44503</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4031,7 +4031,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45750</v>
+        <v>45656</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4104,7 +4104,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45400</v>
+        <v>45926</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4177,7 +4177,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45926</v>
+        <v>46008</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45133</v>
+        <v>45719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4279,8 +4279,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4323,7 +4328,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4337,10 +4342,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46008</v>
+        <v>45131</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4353,7 +4358,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4396,7 +4401,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4410,10 +4415,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45719</v>
+        <v>45282</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4425,13 +4430,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44480</v>
+        <v>45750</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4547,7 +4547,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46174</v>
+        <v>45400</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45644</v>
+        <v>46196</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44473</v>
+        <v>46066</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46066</v>
+        <v>45133</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.3</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45379</v>
+        <v>46071</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4868,13 +4868,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4917,7 +4912,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4927,14 +4922,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46071</v>
+        <v>46087</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4947,7 +4942,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4990,7 +4985,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5004,10 +4999,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44700</v>
+        <v>44480</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5020,7 +5015,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5063,7 +5058,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5077,10 +5072,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44677</v>
+        <v>46097</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5092,13 +5087,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5141,7 +5131,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5151,14 +5141,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46087</v>
+        <v>46106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5171,7 +5161,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5214,7 +5204,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5228,10 +5218,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44909</v>
+        <v>46119</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5244,7 +5234,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5287,7 +5277,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5301,10 +5291,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46097</v>
+        <v>46120</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5317,7 +5307,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5360,7 +5350,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5374,10 +5364,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46196</v>
+        <v>45644</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5390,7 +5380,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5433,7 +5423,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5447,10 +5437,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46106</v>
+        <v>44473</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5463,7 +5453,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5506,7 +5496,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 12421-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5520,10 +5510,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46119</v>
+        <v>45379</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5535,8 +5525,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5579,7 +5574,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5593,10 +5588,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46120</v>
+        <v>44700</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5609,7 +5604,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44815</v>
+        <v>46209</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45545</v>
+        <v>44677</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5754,8 +5749,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45329</v>
+        <v>44909</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45887</v>
+        <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44686</v>
+        <v>46260</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5973,13 +5973,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6022,7 +6017,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46209</v>
+        <v>46265</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6052,7 +6047,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6095,7 +6090,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45007</v>
+        <v>46268</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6125,7 +6120,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6168,7 +6163,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6182,10 +6177,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46254</v>
+        <v>44815</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6198,7 +6193,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6241,7 +6236,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6255,10 +6250,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46260</v>
+        <v>45329</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6271,7 +6266,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6314,7 +6309,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6328,10 +6323,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46265</v>
+        <v>44686</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6343,8 +6338,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46268</v>
+        <v>45007</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6460,7 +6460,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45056</v>
+        <v>46238</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6533,7 +6533,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45719</v>
+        <v>46286</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6562,13 +6562,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6611,7 +6606,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6625,10 +6620,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45715</v>
+        <v>45056</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6640,13 +6635,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6689,7 +6679,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6703,10 +6693,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46238</v>
+        <v>45719</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6718,8 +6708,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6762,7 +6757,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6776,10 +6771,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45722</v>
+        <v>45715</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6791,8 +6786,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6835,7 +6835,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45377</v>
+        <v>45722</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6908,148 +6908,221 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
+          <t>A 12006-2024</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>45377</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>A 32176-2025</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D87" s="1" t="n">
+      <c r="D88" s="1" t="n">
         <v>45835</v>
       </c>
-      <c r="E87" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
+      <c r="E88" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
         <v>2.3</v>
       </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>A 32615-2025</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="n">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E88" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
+      <c r="E89" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
         <v>2.9</v>
       </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="2" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44502</v>
+        <v>45056</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44686</v>
+        <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1480,13 +1480,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1529,7 +1524,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1543,10 +1538,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44727</v>
+        <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1558,8 +1553,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44784</v>
+        <v>44804</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45322</v>
+        <v>45401</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45322</v>
+        <v>44473</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44503</v>
+        <v>45719</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1848,6 +1848,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1894,7 +1899,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1911,7 +1916,7 @@
         <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45446</v>
+        <v>44795</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2001,13 +2006,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44670</v>
+        <v>45887</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45317</v>
+        <v>45542</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2152,13 +2152,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>10.2</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2201,7 +2196,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45281</v>
+        <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2230,8 +2225,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>10.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45351</v>
+        <v>44480</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45542</v>
+        <v>45446</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2376,8 +2376,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2420,7 +2425,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,10 +2439,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44931</v>
+        <v>45656</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2450,7 +2455,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3</v>
+        <v>6.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2493,7 +2498,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2507,10 +2512,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45887</v>
+        <v>44503</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2566,7 +2571,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2580,10 +2585,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>45898</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2596,7 +2601,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2639,7 +2644,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45887</v>
+        <v>44727</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2669,7 +2674,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2712,7 +2717,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2726,10 +2731,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44473</v>
+        <v>45133</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2742,7 +2747,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2785,7 +2790,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2799,10 +2804,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45898</v>
+        <v>45919</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2815,7 +2820,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2858,7 +2863,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45919</v>
+        <v>45282</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2888,7 +2893,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2931,7 +2936,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,10 +2950,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45233</v>
+        <v>45722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2961,7 +2966,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3004,7 +3009,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3018,10 +3023,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45317</v>
+        <v>44909</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3033,13 +3038,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46147</v>
+        <v>45377</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3172,7 +3172,7 @@
         <v>45939</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 12421-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45401</v>
+        <v>45379</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3257,8 +3257,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3301,7 +3306,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3315,10 +3320,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45190</v>
+        <v>45007</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3374,7 +3379,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3388,10 +3393,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44991</v>
+        <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3404,7 +3409,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3447,7 +3452,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3461,10 +3466,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45950</v>
+        <v>45329</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3477,7 +3482,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3520,7 +3525,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3534,10 +3539,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45600</v>
+        <v>44784</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3550,7 +3555,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3593,7 +3598,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3607,10 +3612,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44795</v>
+        <v>44686</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3622,8 +3627,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3666,7 +3676,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3676,14 +3686,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45979</v>
+        <v>44670</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3696,7 +3706,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3739,7 +3749,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3753,10 +3763,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>45317</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3768,8 +3778,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3812,7 +3827,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3826,10 +3841,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44804</v>
+        <v>45351</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3842,7 +3857,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3885,7 +3900,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3899,10 +3914,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46174</v>
+        <v>45715</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3914,8 +3929,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3958,7 +3978,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3972,10 +3992,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44503</v>
+        <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3988,7 +4008,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4031,7 +4051,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4041,14 +4061,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45656</v>
+        <v>45979</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4061,7 +4081,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4104,7 +4124,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4118,10 +4138,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45926</v>
+        <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4134,7 +4154,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4177,7 +4197,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4191,10 +4211,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46008</v>
+        <v>44991</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4207,7 +4227,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4250,7 +4270,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4264,10 +4284,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45719</v>
+        <v>45644</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4279,13 +4299,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4328,7 +4343,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4342,10 +4357,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45131</v>
+        <v>45233</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4358,7 +4373,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4401,7 +4416,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4415,10 +4430,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45282</v>
+        <v>45190</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4431,7 +4446,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4474,7 +4489,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4488,10 +4503,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45750</v>
+        <v>45926</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4504,7 +4519,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4547,7 +4562,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4561,10 +4576,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45400</v>
+        <v>44931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4577,7 +4592,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4620,7 +4635,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4630,14 +4645,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46196</v>
+        <v>45835</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4650,7 +4665,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4693,7 +4708,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4707,10 +4722,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46066</v>
+        <v>45838</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4723,7 +4738,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4766,7 +4781,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4780,10 +4795,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45133</v>
+        <v>46008</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4796,7 +4811,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4839,7 +4854,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4853,10 +4868,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46071</v>
+        <v>45719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4868,8 +4883,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4912,7 +4932,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4922,14 +4942,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46087</v>
+        <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4942,7 +4962,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4985,7 +5005,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4999,10 +5019,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44480</v>
+        <v>46066</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5015,7 +5035,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5058,7 +5078,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5072,10 +5092,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46097</v>
+        <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5088,7 +5108,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5131,7 +5151,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5145,10 +5165,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46106</v>
+        <v>45322</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5161,7 +5181,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5204,7 +5224,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5218,10 +5238,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46119</v>
+        <v>46071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5234,7 +5254,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5277,7 +5297,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5291,10 +5311,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46120</v>
+        <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5307,7 +5327,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5350,7 +5370,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5360,14 +5380,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45644</v>
+        <v>46087</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5380,7 +5400,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5440,7 +5460,7 @@
         <v>44473</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5496,7 +5516,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5510,10 +5530,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45379</v>
+        <v>46097</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5525,13 +5545,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5574,7 +5589,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5588,10 +5603,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44700</v>
+        <v>44677</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5603,8 +5618,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5647,7 +5667,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5661,10 +5681,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46209</v>
+        <v>45281</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5677,7 +5697,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5720,7 +5740,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5734,10 +5754,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44677</v>
+        <v>46106</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5749,13 +5769,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5798,7 +5813,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5812,10 +5827,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44909</v>
+        <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5828,7 +5843,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5871,7 +5886,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5885,10 +5900,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46254</v>
+        <v>46120</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5901,7 +5916,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5944,7 +5959,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5958,10 +5973,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46260</v>
+        <v>46119</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5974,7 +5989,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6017,7 +6032,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6031,10 +6046,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46265</v>
+        <v>45131</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6047,7 +6062,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6090,7 +6105,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6104,10 +6119,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46268</v>
+        <v>45750</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6120,7 +6135,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6180,7 +6195,7 @@
         <v>44815</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6236,7 +6251,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6250,10 +6265,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45329</v>
+        <v>45887</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6266,7 +6281,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6309,7 +6324,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6323,10 +6338,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44686</v>
+        <v>45545</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6338,13 +6353,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6387,7 +6397,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6401,10 +6411,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45007</v>
+        <v>46147</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6417,7 +6427,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6460,7 +6470,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6474,10 +6484,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46238</v>
+        <v>45600</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6490,7 +6500,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6533,7 +6543,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6547,10 +6557,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6563,7 +6573,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6606,7 +6616,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6620,10 +6630,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45056</v>
+        <v>46196</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6636,7 +6646,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6679,7 +6689,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6693,10 +6703,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45719</v>
+        <v>46209</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6708,13 +6718,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6757,7 +6762,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6771,10 +6776,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45715</v>
+        <v>46254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6786,13 +6791,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6835,7 +6835,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45722</v>
+        <v>46260</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6908,7 +6908,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45377</v>
+        <v>46265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45835</v>
+        <v>46268</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45838</v>
+        <v>46238</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45056</v>
+        <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44502</v>
+        <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1480,8 +1480,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1524,7 +1529,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44686</v>
+        <v>44727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1553,13 +1558,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44804</v>
+        <v>44784</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45401</v>
+        <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44473</v>
+        <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45719</v>
+        <v>44503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1848,11 +1848,6 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1899,7 +1894,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1916,7 +1911,7 @@
         <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44795</v>
+        <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2006,8 +2001,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45887</v>
+        <v>44670</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45542</v>
+        <v>45281</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44480</v>
+        <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45446</v>
+        <v>45542</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2376,13 +2376,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2425,7 +2420,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2439,10 +2434,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45656</v>
+        <v>44931</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2455,7 +2450,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2498,7 +2493,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2512,10 +2507,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44503</v>
+        <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2571,7 +2566,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2585,10 +2580,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45898</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2601,7 +2596,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2644,7 +2639,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44727</v>
+        <v>45887</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2674,7 +2669,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2717,7 +2712,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2731,10 +2726,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45133</v>
+        <v>44473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2747,7 +2742,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2790,7 +2785,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2804,10 +2799,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45919</v>
+        <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2820,7 +2815,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2863,7 +2858,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45282</v>
+        <v>45233</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2893,7 +2888,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2936,7 +2931,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2950,10 +2945,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45722</v>
+        <v>45317</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2963,6 +2958,11 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -3009,7 +3009,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44909</v>
+        <v>45919</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45377</v>
+        <v>45939</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45939</v>
+        <v>45401</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45379</v>
+        <v>45190</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3257,13 +3257,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3306,7 +3301,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3320,10 +3315,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45007</v>
+        <v>44991</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3336,7 +3331,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3396,7 +3391,7 @@
         <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3452,7 +3447,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3466,10 +3461,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45329</v>
+        <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3482,7 +3477,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3525,7 +3520,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3535,14 +3530,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44784</v>
+        <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3555,7 +3550,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3598,7 +3593,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3612,10 +3607,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44686</v>
+        <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3627,13 +3622,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3676,7 +3666,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3690,10 +3680,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44670</v>
+        <v>44804</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3706,7 +3696,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3749,7 +3739,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45317</v>
+        <v>46147</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3778,13 +3768,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3827,7 +3812,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3841,10 +3826,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45351</v>
+        <v>44503</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3857,7 +3842,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3900,7 +3885,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3914,10 +3899,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45715</v>
+        <v>45656</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3929,13 +3914,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3978,7 +3958,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3992,10 +3972,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44700</v>
+        <v>45926</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4008,7 +3988,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4051,7 +4031,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4061,14 +4041,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45979</v>
+        <v>46008</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4081,7 +4061,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4124,7 +4104,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4138,10 +4118,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45979</v>
+        <v>45600</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4154,7 +4134,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4197,7 +4177,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4211,10 +4191,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44991</v>
+        <v>45719</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4226,8 +4206,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4270,7 +4255,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4284,10 +4269,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45644</v>
+        <v>45131</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4300,7 +4285,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4343,7 +4328,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4357,10 +4342,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45233</v>
+        <v>45282</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4373,7 +4358,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4416,7 +4401,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4430,10 +4415,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45190</v>
+        <v>45750</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4446,7 +4431,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4489,7 +4474,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4503,10 +4488,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45926</v>
+        <v>45400</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4519,7 +4504,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4562,7 +4547,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4576,10 +4561,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44931</v>
+        <v>45133</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4592,7 +4577,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4635,7 +4620,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4645,14 +4630,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45835</v>
+        <v>46066</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4665,7 +4650,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4708,7 +4693,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4722,10 +4707,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45838</v>
+        <v>46071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4738,7 +4723,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4781,7 +4766,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4795,10 +4780,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46008</v>
+        <v>46174</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4811,7 +4796,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4854,7 +4839,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4868,10 +4853,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45719</v>
+        <v>44480</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4883,13 +4868,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4932,7 +4912,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4942,14 +4922,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46286</v>
+        <v>46087</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4962,7 +4942,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5005,7 +4985,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5019,10 +4999,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46066</v>
+        <v>46097</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5035,7 +5015,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5078,7 +5058,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5092,10 +5072,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45322</v>
+        <v>46106</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5108,7 +5088,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5151,7 +5131,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5165,10 +5145,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45322</v>
+        <v>45644</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5181,7 +5161,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5224,7 +5204,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5238,10 +5218,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46071</v>
+        <v>46119</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5254,7 +5234,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5297,7 +5277,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5311,10 +5291,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45400</v>
+        <v>46120</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5327,7 +5307,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5370,7 +5350,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5380,14 +5360,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46087</v>
+        <v>44473</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5400,7 +5380,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5443,7 +5423,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 12421-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5457,10 +5437,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44473</v>
+        <v>45379</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5472,8 +5452,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5516,7 +5501,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5530,10 +5515,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46097</v>
+        <v>44700</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5606,7 +5591,7 @@
         <v>44677</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5667,7 +5652,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5681,10 +5666,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45281</v>
+        <v>46196</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5697,7 +5682,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5740,7 +5725,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5754,10 +5739,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46106</v>
+        <v>44909</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5770,7 +5755,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5813,7 +5798,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5827,10 +5812,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44503</v>
+        <v>46209</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5843,7 +5828,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5886,7 +5871,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5900,10 +5885,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46120</v>
+        <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5916,7 +5901,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5959,7 +5944,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5973,10 +5958,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46119</v>
+        <v>44815</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5989,7 +5974,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6032,7 +6017,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6046,10 +6031,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45131</v>
+        <v>45329</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6062,7 +6047,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6105,7 +6090,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6119,10 +6104,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45750</v>
+        <v>46260</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6135,7 +6120,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6178,7 +6163,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6192,10 +6177,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44815</v>
+        <v>44686</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6207,8 +6192,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6251,7 +6241,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6265,10 +6255,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45887</v>
+        <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6281,7 +6271,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6324,7 +6314,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6338,10 +6328,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45545</v>
+        <v>46268</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6354,7 +6344,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6397,7 +6387,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6411,10 +6401,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46147</v>
+        <v>45007</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6427,7 +6417,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6470,7 +6460,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6484,10 +6474,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45600</v>
+        <v>46238</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6500,7 +6490,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6543,7 +6533,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6557,10 +6547,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46174</v>
+        <v>46286</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6573,7 +6563,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6616,7 +6606,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6630,10 +6620,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46196</v>
+        <v>45056</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6646,7 +6636,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6689,7 +6679,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6703,10 +6693,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46209</v>
+        <v>45719</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6718,8 +6708,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6762,7 +6757,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6776,10 +6771,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46254</v>
+        <v>45715</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6791,8 +6786,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6835,7 +6835,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46260</v>
+        <v>45722</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6908,7 +6908,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46265</v>
+        <v>45377</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46268</v>
+        <v>45835</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46238</v>
+        <v>45838</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE89"/>
+  <dimension ref="A1:AE88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44727</v>
+        <v>45401</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44784</v>
+        <v>45317</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1631,8 +1631,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>10.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1675,7 +1680,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1689,10 +1694,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45322</v>
+        <v>45446</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1704,8 +1709,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1748,7 +1758,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,10 +1772,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45322</v>
+        <v>44480</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1778,7 +1788,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1821,7 +1831,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1835,10 +1845,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44503</v>
+        <v>45719</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1850,8 +1860,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1894,7 +1909,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1908,10 +1923,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45715</v>
+        <v>45887</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1923,13 +1938,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1972,7 +1982,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1986,10 +1996,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45446</v>
+        <v>45898</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2001,13 +2011,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2050,7 +2055,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2064,10 +2069,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44670</v>
+        <v>45282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2123,7 +2128,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2137,10 +2142,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45281</v>
+        <v>44909</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2153,7 +2158,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2196,7 +2201,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2210,10 +2215,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45317</v>
+        <v>45919</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2225,13 +2230,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45351</v>
+        <v>46066</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45542</v>
+        <v>46071</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44931</v>
+        <v>45722</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45887</v>
+        <v>45377</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>46087</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45887</v>
+        <v>45939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44473</v>
+        <v>46097</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45898</v>
+        <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45233</v>
+        <v>44686</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2887,8 +2887,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2931,7 +2936,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,10 +2950,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45317</v>
+        <v>45950</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2960,13 +2965,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45919</v>
+        <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45939</v>
+        <v>45317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3111,8 +3111,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3155,7 +3160,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3169,10 +3174,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45401</v>
+        <v>45715</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3184,8 +3189,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3228,7 +3238,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3242,10 +3252,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45190</v>
+        <v>46120</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3258,7 +3268,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3301,7 +3311,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3315,10 +3325,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44991</v>
+        <v>46119</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3331,7 +3341,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3374,7 +3384,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3388,10 +3398,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45950</v>
+        <v>44700</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3404,7 +3414,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3447,7 +3457,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3461,10 +3471,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44795</v>
+        <v>44991</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3477,7 +3487,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3537,7 +3547,7 @@
         <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3610,7 +3620,7 @@
         <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3666,7 +3676,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3680,10 +3690,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44804</v>
+        <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3696,7 +3706,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3739,7 +3749,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3753,10 +3763,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46147</v>
+        <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3769,7 +3779,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3812,7 +3822,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3826,10 +3836,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44503</v>
+        <v>45545</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3842,7 +3852,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3885,7 +3895,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3899,10 +3909,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45656</v>
+        <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3915,7 +3925,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3958,7 +3968,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3972,10 +3982,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45926</v>
+        <v>46008</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3988,7 +3998,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4031,7 +4041,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4045,10 +4055,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46008</v>
+        <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4061,7 +4071,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4104,7 +4114,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4118,10 +4128,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45600</v>
+        <v>44473</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4134,7 +4144,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4177,7 +4187,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4191,10 +4201,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45719</v>
+        <v>46147</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4206,13 +4216,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4255,7 +4260,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4269,10 +4274,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45131</v>
+        <v>44795</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4285,7 +4290,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4328,7 +4333,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4338,14 +4343,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45282</v>
+        <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4358,7 +4363,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4401,7 +4406,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4415,10 +4420,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45750</v>
+        <v>45838</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4431,7 +4436,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4474,7 +4479,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4488,10 +4493,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45400</v>
+        <v>45542</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4504,7 +4509,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4547,7 +4552,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4561,10 +4566,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45133</v>
+        <v>45600</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4577,7 +4582,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4620,7 +4625,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4634,10 +4639,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46066</v>
+        <v>45656</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4650,7 +4655,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4693,7 +4698,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4707,10 +4712,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46071</v>
+        <v>44503</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4723,7 +4728,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4766,7 +4771,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4780,10 +4785,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46174</v>
+        <v>44727</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4796,7 +4801,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4839,7 +4844,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4853,10 +4858,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44480</v>
+        <v>45133</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4869,7 +4874,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4912,7 +4917,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4922,14 +4927,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46087</v>
+        <v>46174</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4942,7 +4947,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4985,7 +4990,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4999,10 +5004,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46097</v>
+        <v>46196</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5015,7 +5020,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5058,7 +5063,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5072,10 +5077,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46106</v>
+        <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5088,7 +5093,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5131,7 +5136,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5145,10 +5150,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45644</v>
+        <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5161,7 +5166,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5204,7 +5209,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5218,10 +5223,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46119</v>
+        <v>46209</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5234,7 +5239,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5277,7 +5282,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5291,10 +5296,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46120</v>
+        <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5307,7 +5312,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5350,7 +5355,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5364,10 +5369,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44473</v>
+        <v>46254</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5380,7 +5385,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5423,7 +5428,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12421-2024</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45379</v>
+        <v>45351</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5452,13 +5457,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44700</v>
+        <v>46260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5574,7 +5574,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44677</v>
+        <v>46265</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5603,13 +5603,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46196</v>
+        <v>45233</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44909</v>
+        <v>45190</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5755,7 +5750,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5798,7 +5793,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5812,10 +5807,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46209</v>
+        <v>44931</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5828,7 +5823,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>0.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5871,7 +5866,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5885,10 +5880,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46254</v>
+        <v>46268</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5901,7 +5896,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5944,7 +5939,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5958,10 +5953,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44815</v>
+        <v>46238</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5974,7 +5969,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6017,7 +6012,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6031,10 +6026,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45329</v>
+        <v>45322</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6047,7 +6042,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6090,7 +6085,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6104,10 +6099,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46260</v>
+        <v>45322</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6120,7 +6115,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6163,7 +6158,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44686</v>
+        <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6192,13 +6187,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6241,7 +6231,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6255,10 +6245,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46265</v>
+        <v>45400</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6271,7 +6261,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6314,7 +6304,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6328,10 +6318,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46268</v>
+        <v>44473</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6344,7 +6334,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6387,7 +6377,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6401,10 +6391,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45007</v>
+        <v>44677</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6416,8 +6406,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6460,7 +6455,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6474,10 +6469,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46238</v>
+        <v>45281</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6490,7 +6485,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6533,7 +6528,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6547,10 +6542,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46286</v>
+        <v>44503</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6563,7 +6558,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6606,7 +6601,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6620,10 +6615,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45056</v>
+        <v>45131</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6636,7 +6631,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6679,7 +6674,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6693,10 +6688,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45719</v>
+        <v>45750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6708,13 +6703,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6757,7 +6747,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6771,10 +6761,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45715</v>
+        <v>44815</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6786,13 +6776,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6835,7 +6820,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6849,10 +6834,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45722</v>
+        <v>45056</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6865,7 +6850,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6908,7 +6893,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6922,10 +6907,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45377</v>
+        <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6937,8 +6922,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6978,10 +6968,10 @@
       </c>
       <c r="V87" s="2" t="inlineStr"/>
     </row>
-    <row r="88" ht="15" customHeight="1">
+    <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6991,14 +6981,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45835</v>
+        <v>45715</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7010,8 +7000,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7050,79 +7045,6 @@
         <v>0</v>
       </c>
       <c r="V88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>A 32615-2025</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="E89" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>45401</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>45317</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45446</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44480</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45719</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45887</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45898</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44909</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45919</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>46066</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>46071</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45722</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45377</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>46087</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>45939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>46097</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44686</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45950</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>45715</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>46120</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>46119</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44700</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44991</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45545</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>46008</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44473</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>46147</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44795</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45838</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45542</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45600</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45656</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44503</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>44727</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45133</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>46174</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>46196</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>46209</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>46254</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45351</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>46260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>46265</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45233</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45190</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>44931</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>46268</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>46238</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45322</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45322</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45400</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44473</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44677</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45281</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44503</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45131</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44815</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45056</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45715</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>45401</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>45317</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45446</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44480</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45719</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45887</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45898</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44909</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45919</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>46066</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>46071</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45722</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45377</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>46087</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>45939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>46097</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44686</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45950</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>45715</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>46120</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>46119</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44700</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44991</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45545</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>46008</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44473</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>46147</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44795</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45838</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45542</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45600</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45656</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44503</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>44727</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45133</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>46174</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>46196</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>46209</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>46254</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45351</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>46260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>46265</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45233</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45190</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>44931</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>46268</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>46238</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45322</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45322</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45400</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44473</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44677</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45281</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44503</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45131</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44815</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45056</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45715</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44606</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45401</v>
+        <v>44727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45317</v>
+        <v>44784</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1631,13 +1631,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1680,7 +1675,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1694,10 +1689,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45446</v>
+        <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1709,13 +1704,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1758,7 +1748,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1772,10 +1762,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44480</v>
+        <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1788,7 +1778,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1831,7 +1821,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1845,10 +1835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45719</v>
+        <v>44503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1860,13 +1850,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1909,7 +1894,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1923,10 +1908,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45887</v>
+        <v>45056</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1939,7 +1924,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1982,7 +1967,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1996,10 +1981,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45898</v>
+        <v>45926</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2012,7 +1997,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2055,7 +2040,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2069,10 +2054,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45282</v>
+        <v>45719</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2084,8 +2069,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2128,7 +2118,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2142,10 +2132,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44909</v>
+        <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2157,8 +2147,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2201,7 +2196,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45919</v>
+        <v>45887</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2231,7 +2226,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2288,10 +2283,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46066</v>
+        <v>45715</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2303,8 +2298,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46071</v>
+        <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45722</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45377</v>
+        <v>45446</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2522,8 +2522,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2566,7 +2571,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2576,14 +2581,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2596,7 +2601,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2639,7 +2644,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45939</v>
+        <v>45377</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2712,7 +2717,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2726,10 +2731,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46097</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2785,7 +2790,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2795,14 +2800,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44784</v>
+        <v>45835</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2815,7 +2820,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2858,7 +2863,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44686</v>
+        <v>44670</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2887,13 +2892,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45950</v>
+        <v>45719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2965,8 +2965,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3009,7 +3014,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3023,10 +3028,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46106</v>
+        <v>45838</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3039,7 +3044,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3082,7 +3087,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,10 +3101,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45317</v>
+        <v>45939</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3111,13 +3116,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45715</v>
+        <v>45950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3189,13 +3189,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3238,7 +3233,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3252,10 +3247,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46120</v>
+        <v>45281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3268,7 +3263,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3311,7 +3306,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3325,10 +3320,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46119</v>
+        <v>45317</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3340,8 +3335,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>10.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44700</v>
+        <v>44931</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44991</v>
+        <v>45351</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3540,14 +3540,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45979</v>
+        <v>45542</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3613,14 +3613,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
         <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45644</v>
+        <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45887</v>
+        <v>44473</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45545</v>
+        <v>45233</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45926</v>
+        <v>46066</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46008</v>
+        <v>45317</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3997,8 +3997,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44804</v>
+        <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4124,14 +4129,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44473</v>
+        <v>46087</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46147</v>
+        <v>45401</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44795</v>
+        <v>46097</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4343,14 +4348,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45835</v>
+        <v>45190</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45838</v>
+        <v>44991</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4436,7 +4441,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45542</v>
+        <v>46106</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4566,10 +4571,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45600</v>
+        <v>44795</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45656</v>
+        <v>46119</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44503</v>
+        <v>46120</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4771,7 +4776,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4785,10 +4790,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44727</v>
+        <v>44804</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4801,7 +4806,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.6</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4844,7 +4849,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4858,10 +4863,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45133</v>
+        <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4874,7 +4879,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4917,7 +4922,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46174</v>
+        <v>45545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4947,7 +4952,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4990,7 +4995,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5004,10 +5009,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46196</v>
+        <v>45656</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5020,7 +5025,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5063,7 +5068,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5077,10 +5082,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45007</v>
+        <v>45887</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5093,7 +5098,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5136,7 +5141,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5150,10 +5155,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45329</v>
+        <v>45131</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5166,7 +5171,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5209,7 +5214,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46209</v>
+        <v>45282</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5282,7 +5287,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5296,10 +5301,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44670</v>
+        <v>45750</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5312,7 +5317,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5355,7 +5360,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46254</v>
+        <v>46147</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5385,7 +5390,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5428,7 +5433,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5442,10 +5447,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45351</v>
+        <v>45400</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5458,7 +5463,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5501,7 +5506,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5515,10 +5520,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46260</v>
+        <v>45133</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5531,7 +5536,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5574,7 +5579,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5588,10 +5593,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46265</v>
+        <v>45600</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5604,7 +5609,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5647,7 +5652,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5661,10 +5666,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45233</v>
+        <v>44480</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5677,7 +5682,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5720,7 +5725,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45190</v>
+        <v>46174</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5750,7 +5755,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5793,7 +5798,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5807,10 +5812,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44931</v>
+        <v>45644</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5823,7 +5828,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5866,7 +5871,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5880,10 +5885,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46268</v>
+        <v>44473</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5896,7 +5901,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5939,7 +5944,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5953,10 +5958,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46238</v>
+        <v>44700</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5969,7 +5974,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6012,7 +6017,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6026,10 +6031,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45322</v>
+        <v>44677</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6041,8 +6046,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6085,7 +6095,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6099,10 +6109,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45322</v>
+        <v>44909</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6115,7 +6125,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6158,7 +6168,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6172,10 +6182,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46286</v>
+        <v>46196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6188,7 +6198,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6231,7 +6241,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6245,10 +6255,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45400</v>
+        <v>46209</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6261,7 +6271,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6304,7 +6314,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6318,10 +6328,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44473</v>
+        <v>44815</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6334,7 +6344,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6377,7 +6387,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6391,10 +6401,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44677</v>
+        <v>46254</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6406,13 +6416,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6455,7 +6460,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6469,10 +6474,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45281</v>
+        <v>45329</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6485,7 +6490,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6528,7 +6533,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6542,10 +6547,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44503</v>
+        <v>44686</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6557,8 +6562,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6601,7 +6611,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6615,10 +6625,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45131</v>
+        <v>46260</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6631,7 +6641,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6674,7 +6684,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6688,10 +6698,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45750</v>
+        <v>45007</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6704,7 +6714,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6747,7 +6757,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6761,10 +6771,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44815</v>
+        <v>46265</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6777,7 +6787,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6820,7 +6830,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6834,10 +6844,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45056</v>
+        <v>46268</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6850,7 +6860,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6893,7 +6903,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6907,10 +6917,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45719</v>
+        <v>46238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6922,13 +6932,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -6971,7 +6976,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6985,10 +6990,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45715</v>
+        <v>46286</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7000,13 +7005,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE88"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,154 +647,154 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 7398-2022</t>
+          <t>A 40387-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44606</v>
+        <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -854,20 +854,56 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 61593-2021</t>
+          <t>A 7398-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -881,10 +917,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44501</v>
+        <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -897,7 +933,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -940,7 +976,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54448-2021</t>
+          <t>A 61593-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -954,10 +990,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44473</v>
+        <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -970,7 +1006,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1013,7 +1049,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12631-2022</t>
+          <t>A 54448-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1063,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44641</v>
+        <v>44473</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1079,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1122,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 62536-2021</t>
+          <t>A 12631-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1136,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44503</v>
+        <v>44641</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1152,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1159,7 +1195,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54521-2021</t>
+          <t>A 62536-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1173,10 +1209,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44473</v>
+        <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1189,7 +1225,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1232,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 62503-2021</t>
+          <t>A 54521-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1246,10 +1282,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44503</v>
+        <v>44473</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1262,7 +1298,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1305,7 +1341,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 62503-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1319,10 +1355,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44686</v>
+        <v>44503</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1335,7 +1371,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1378,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44502</v>
+        <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1408,7 +1444,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1451,7 +1487,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1465,10 +1501,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44686</v>
+        <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1480,13 +1516,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1529,7 +1560,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1543,10 +1574,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44727</v>
+        <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1558,8 +1589,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1602,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1616,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44784</v>
+        <v>45401</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1632,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1675,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1689,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45322</v>
+        <v>45317</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1704,8 +1740,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>10.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1748,7 +1789,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,10 +1803,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45322</v>
+        <v>45719</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1777,8 +1818,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1821,7 +1867,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1835,10 +1881,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44503</v>
+        <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1851,7 +1897,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1894,7 +1940,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1908,10 +1954,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45056</v>
+        <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1923,8 +1969,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1967,7 +2018,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1981,10 +2032,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45926</v>
+        <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1996,8 +2047,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2040,7 +2096,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2057,7 +2113,7 @@
         <v>45719</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2075,7 +2131,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2118,7 +2174,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2132,10 +2188,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45715</v>
+        <v>45887</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2145,11 +2201,6 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2196,7 +2247,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2210,10 +2261,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45887</v>
+        <v>45898</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2226,7 +2277,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2269,7 +2320,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2283,10 +2334,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45715</v>
+        <v>45722</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2298,13 +2349,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2347,7 +2393,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2361,10 +2407,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46008</v>
+        <v>45377</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2377,7 +2423,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2420,7 +2466,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,10 +2480,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>45282</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2450,7 +2496,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2493,7 +2539,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2507,10 +2553,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45446</v>
+        <v>44909</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2522,13 +2568,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2571,7 +2612,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2585,10 +2626,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45722</v>
+        <v>45919</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2601,7 +2642,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2644,7 +2685,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2654,14 +2695,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45377</v>
+        <v>45835</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2674,7 +2715,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2717,7 +2758,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2731,10 +2772,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>45838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2747,7 +2788,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2790,7 +2831,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2800,14 +2841,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45835</v>
+        <v>45939</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2820,7 +2861,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2863,7 +2904,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2877,10 +2918,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44670</v>
+        <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2893,7 +2934,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2936,7 +2977,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2950,10 +2991,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45719</v>
+        <v>44686</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2967,11 +3008,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3014,7 +3055,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3028,10 +3069,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45838</v>
+        <v>45950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3044,7 +3085,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3087,7 +3128,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3101,10 +3142,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45939</v>
+        <v>45317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3116,8 +3157,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3160,7 +3206,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3174,10 +3220,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45950</v>
+        <v>45715</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3189,8 +3235,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3233,7 +3284,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3247,10 +3298,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45281</v>
+        <v>44700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3263,7 +3314,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3306,7 +3357,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3320,10 +3371,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45317</v>
+        <v>44991</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3335,13 +3386,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>10.2</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3384,7 +3430,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3398,10 +3444,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44931</v>
+        <v>46066</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3414,7 +3460,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3457,7 +3503,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3467,14 +3513,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45351</v>
+        <v>45979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3487,7 +3533,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3530,7 +3576,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3544,10 +3590,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45542</v>
+        <v>46071</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3560,7 +3606,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3603,7 +3649,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3613,14 +3659,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
         <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3633,7 +3679,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3676,7 +3722,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3690,10 +3736,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45979</v>
+        <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3706,7 +3752,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3749,7 +3795,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3759,14 +3805,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44473</v>
+        <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3779,7 +3825,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3822,7 +3868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3836,10 +3882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45233</v>
+        <v>45926</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3852,7 +3898,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3895,7 +3941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3909,10 +3955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46066</v>
+        <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3925,7 +3971,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3968,7 +4014,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3982,10 +4028,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45317</v>
+        <v>46097</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3997,13 +4043,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4046,7 +4087,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4060,10 +4101,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46071</v>
+        <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4076,7 +4117,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4119,7 +4160,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4129,14 +4170,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46087</v>
+        <v>46106</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4149,7 +4190,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4192,7 +4233,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4206,10 +4247,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45401</v>
+        <v>44473</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4222,7 +4263,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4265,7 +4306,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4279,10 +4320,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46097</v>
+        <v>46120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4295,7 +4336,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4338,7 +4379,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4352,10 +4393,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45190</v>
+        <v>46119</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4368,7 +4409,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4411,7 +4452,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4425,10 +4466,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44991</v>
+        <v>44795</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4441,7 +4482,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4484,7 +4525,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4498,10 +4539,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46106</v>
+        <v>45542</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4514,7 +4555,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4557,7 +4598,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4571,10 +4612,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44795</v>
+        <v>45656</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4587,7 +4628,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4630,7 +4671,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4644,10 +4685,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46119</v>
+        <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4660,7 +4701,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4703,7 +4744,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4717,10 +4758,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46120</v>
+        <v>44727</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4733,7 +4774,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4776,7 +4817,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4790,10 +4831,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44804</v>
+        <v>45133</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4806,7 +4847,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4849,7 +4890,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4863,10 +4904,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44503</v>
+        <v>45887</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4879,7 +4920,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4939,7 +4980,7 @@
         <v>45545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4995,7 +5036,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5009,10 +5050,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45656</v>
+        <v>45007</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5025,7 +5066,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5068,7 +5109,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5082,10 +5123,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45887</v>
+        <v>46147</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5098,7 +5139,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5141,7 +5182,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5155,10 +5196,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45131</v>
+        <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5171,7 +5212,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5214,7 +5255,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5228,10 +5269,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45282</v>
+        <v>45600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5244,7 +5285,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5287,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5301,10 +5342,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45750</v>
+        <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5317,7 +5358,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5360,7 +5401,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5374,10 +5415,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46147</v>
+        <v>45351</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5390,7 +5431,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5433,7 +5474,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5447,10 +5488,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45400</v>
+        <v>46174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5463,7 +5504,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5506,7 +5547,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5520,10 +5561,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45133</v>
+        <v>45233</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5536,7 +5577,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5579,7 +5620,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5593,10 +5634,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45600</v>
+        <v>45190</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5609,7 +5650,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5652,7 +5693,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5666,10 +5707,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44480</v>
+        <v>44931</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5682,7 +5723,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5725,7 +5766,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5739,10 +5780,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46174</v>
+        <v>46196</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5755,7 +5796,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5798,7 +5839,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5812,10 +5853,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45644</v>
+        <v>45322</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5828,7 +5869,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5871,7 +5912,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5885,10 +5926,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44473</v>
+        <v>45322</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5901,7 +5942,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5944,7 +5985,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5958,10 +5999,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44700</v>
+        <v>45400</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5974,7 +6015,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6017,7 +6058,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6031,10 +6072,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44677</v>
+        <v>46209</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6046,13 +6087,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6095,7 +6131,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6109,10 +6145,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44909</v>
+        <v>44473</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6125,7 +6161,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6168,7 +6204,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6182,10 +6218,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46196</v>
+        <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6198,7 +6234,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6241,7 +6277,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6255,10 +6291,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46209</v>
+        <v>44677</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6270,8 +6306,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6314,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6328,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44815</v>
+        <v>45281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6344,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6387,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6401,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46254</v>
+        <v>44503</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6417,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6460,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6474,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45329</v>
+        <v>46260</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6490,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6533,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6547,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44686</v>
+        <v>45131</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6562,13 +6603,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6611,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6625,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6641,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6684,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6698,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45007</v>
+        <v>46268</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6714,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6757,7 +6793,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6771,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46265</v>
+        <v>45750</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6787,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6830,7 +6866,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6844,10 +6880,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46268</v>
+        <v>44815</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6860,7 +6896,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6920,7 +6956,7 @@
         <v>46238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6973,7 +7009,7 @@
       </c>
       <c r="V87" s="2" t="inlineStr"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
           <t>A 38806-2026</t>
@@ -6993,7 +7029,7 @@
         <v>46286</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7045,6 +7081,79 @@
         <v>0</v>
       </c>
       <c r="V88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>A 20332-2023</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>45056</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44473</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 12631-2022</t>
+          <t>A 62536-2021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44641</v>
+        <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 62536-2021</t>
+          <t>A 54521-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44503</v>
+        <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 54521-2021</t>
+          <t>A 12631-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44473</v>
+        <v>44641</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>44503</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44686</v>
+        <v>44502</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44502</v>
+        <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45401</v>
+        <v>44931</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45317</v>
+        <v>45351</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1740,13 +1740,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1789,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1803,10 +1798,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45719</v>
+        <v>45542</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1818,13 +1813,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1867,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1881,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44480</v>
+        <v>45750</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1897,7 +1887,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1940,7 +1930,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1954,10 +1944,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45715</v>
+        <v>44727</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1969,13 +1959,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2018,7 +2003,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2032,10 +2017,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45446</v>
+        <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2053,7 +2038,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2096,7 +2081,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2110,10 +2095,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45719</v>
+        <v>45400</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2125,13 +2110,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2174,7 +2154,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2188,10 +2168,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45887</v>
+        <v>45133</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2204,7 +2184,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2247,7 +2227,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2261,10 +2241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45898</v>
+        <v>45007</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2277,7 +2257,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2320,7 +2300,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2334,10 +2314,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45722</v>
+        <v>45322</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2350,7 +2330,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2393,7 +2373,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2407,10 +2387,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45377</v>
+        <v>45322</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2423,7 +2403,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2466,7 +2446,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2480,10 +2460,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45282</v>
+        <v>44784</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2496,7 +2476,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2539,7 +2519,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2553,10 +2533,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44909</v>
+        <v>44480</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2569,7 +2549,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2612,7 +2592,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2626,10 +2606,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45919</v>
+        <v>44473</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2642,7 +2622,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2685,7 +2665,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2695,14 +2675,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45835</v>
+        <v>44503</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2715,7 +2695,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2758,7 +2738,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2772,10 +2752,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45838</v>
+        <v>45233</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2788,7 +2768,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2831,7 +2811,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2845,10 +2825,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45939</v>
+        <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2860,8 +2840,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2904,7 +2889,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2918,10 +2903,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44784</v>
+        <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2934,7 +2919,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2977,7 +2962,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2991,10 +2976,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44686</v>
+        <v>44473</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3006,13 +2991,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3055,7 +3035,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3069,10 +3049,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45950</v>
+        <v>44700</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3085,7 +3065,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3128,7 +3108,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3142,10 +3122,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45317</v>
+        <v>45715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3163,7 +3143,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3206,7 +3186,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3220,10 +3200,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45715</v>
+        <v>45401</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3235,13 +3215,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3284,7 +3259,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3298,10 +3273,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44700</v>
+        <v>45190</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3314,7 +3289,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3374,7 +3349,7 @@
         <v>44991</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3430,7 +3405,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3444,10 +3419,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46066</v>
+        <v>45056</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3460,7 +3435,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3503,7 +3478,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3513,14 +3488,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45979</v>
+        <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3532,8 +3507,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3576,7 +3556,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3590,10 +3570,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46071</v>
+        <v>44909</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3606,7 +3586,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3649,7 +3629,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3663,10 +3643,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45979</v>
+        <v>45719</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3678,8 +3658,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3722,7 +3707,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3736,10 +3721,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45644</v>
+        <v>45715</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3751,8 +3736,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3795,7 +3785,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3805,14 +3795,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46087</v>
+        <v>44795</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3825,7 +3815,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3868,7 +3858,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3882,10 +3872,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45926</v>
+        <v>45446</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3897,8 +3887,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3941,7 +3936,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3955,10 +3950,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46008</v>
+        <v>45722</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3971,7 +3966,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4014,7 +4009,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4028,10 +4023,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46097</v>
+        <v>45377</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4044,7 +4039,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4104,7 +4099,7 @@
         <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4160,7 +4155,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46106</v>
+        <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4190,7 +4185,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4233,7 +4228,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4247,10 +4242,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44473</v>
+        <v>45656</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4263,7 +4258,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4306,7 +4301,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4320,10 +4315,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46120</v>
+        <v>44670</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4336,7 +4331,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4379,7 +4374,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4393,10 +4388,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46119</v>
+        <v>44815</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4409,7 +4404,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4452,7 +4447,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4462,14 +4457,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44795</v>
+        <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4482,7 +4477,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4525,7 +4520,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4539,10 +4534,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45542</v>
+        <v>45329</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4555,7 +4550,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4598,7 +4593,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4612,10 +4607,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45656</v>
+        <v>45838</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4628,7 +4623,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4671,7 +4666,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4685,10 +4680,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44503</v>
+        <v>45131</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4701,7 +4696,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4744,7 +4739,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4758,10 +4753,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44727</v>
+        <v>45282</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4774,7 +4769,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.6</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4817,7 +4812,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4831,10 +4826,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45133</v>
+        <v>45887</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4847,7 +4842,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4890,7 +4885,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4904,10 +4899,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45887</v>
+        <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4920,7 +4915,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4963,7 +4958,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4977,10 +4972,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45545</v>
+        <v>45317</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4992,8 +4987,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>10.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5109,7 +5109,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46147</v>
+        <v>45950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45329</v>
+        <v>45898</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45600</v>
+        <v>45919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5338,14 +5338,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44670</v>
+        <v>45979</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45351</v>
+        <v>45979</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46174</v>
+        <v>45926</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45233</v>
+        <v>46008</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5620,7 +5620,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45190</v>
+        <v>45719</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5649,8 +5649,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5693,7 +5698,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44931</v>
+        <v>46066</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5723,7 +5728,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5766,7 +5771,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5780,10 +5785,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46196</v>
+        <v>46071</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5796,7 +5801,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5839,7 +5844,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5849,14 +5854,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45322</v>
+        <v>46087</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5869,7 +5874,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5912,7 +5917,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5926,10 +5931,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45322</v>
+        <v>46097</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5942,7 +5947,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5985,7 +5990,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5999,10 +6004,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45400</v>
+        <v>46106</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6015,7 +6020,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6058,7 +6063,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6072,10 +6077,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46209</v>
+        <v>46119</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6088,7 +6093,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6131,7 +6136,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6145,10 +6150,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44473</v>
+        <v>46120</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6161,7 +6166,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6204,7 +6209,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6218,10 +6223,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46254</v>
+        <v>45545</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6234,7 +6239,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6277,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6291,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44677</v>
+        <v>45887</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6306,13 +6311,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6355,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45281</v>
+        <v>46147</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44503</v>
+        <v>45600</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46260</v>
+        <v>46174</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45131</v>
+        <v>46196</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46265</v>
+        <v>46209</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46268</v>
+        <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45750</v>
+        <v>46260</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6866,7 +6866,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44815</v>
+        <v>46265</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6939,7 +6939,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46238</v>
+        <v>46268</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7012,7 +7012,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46286</v>
+        <v>46238</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45056</v>
+        <v>46286</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44473</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 62536-2021</t>
+          <t>A 12631-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44503</v>
+        <v>44641</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54521-2021</t>
+          <t>A 62536-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44473</v>
+        <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 12631-2022</t>
+          <t>A 54521-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44641</v>
+        <v>44473</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>44503</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44502</v>
+        <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44686</v>
+        <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44931</v>
+        <v>45401</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45351</v>
+        <v>45317</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1740,8 +1740,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>10.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1789,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45542</v>
+        <v>45719</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1813,8 +1818,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1857,7 +1867,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1881,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45750</v>
+        <v>45719</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1886,8 +1896,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1930,7 +1945,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1944,10 +1959,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44727</v>
+        <v>44480</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1960,7 +1975,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2003,7 +2018,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2017,10 +2032,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44686</v>
+        <v>45715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2034,11 +2049,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2081,7 +2096,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2095,10 +2110,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45400</v>
+        <v>45446</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2110,8 +2125,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2154,7 +2174,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2168,10 +2188,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45133</v>
+        <v>45887</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2184,7 +2204,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2227,7 +2247,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2241,10 +2261,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45007</v>
+        <v>45898</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2257,7 +2277,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2300,7 +2320,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2314,10 +2334,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45322</v>
+        <v>45282</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2330,7 +2350,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2373,7 +2393,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2387,10 +2407,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45322</v>
+        <v>46066</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2403,7 +2423,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2446,7 +2466,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2460,10 +2480,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44784</v>
+        <v>44909</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2476,7 +2496,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2519,7 +2539,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2533,10 +2553,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44480</v>
+        <v>45919</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2549,7 +2569,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2592,7 +2612,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2606,10 +2626,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44473</v>
+        <v>46071</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2622,7 +2642,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2665,7 +2685,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2675,14 +2695,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44503</v>
+        <v>46087</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2695,7 +2715,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2738,7 +2758,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2752,10 +2772,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45233</v>
+        <v>45722</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2768,7 +2788,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2811,7 +2831,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2825,10 +2845,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45317</v>
+        <v>45939</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2840,13 +2860,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2889,7 +2904,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2903,10 +2918,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45644</v>
+        <v>45377</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2919,7 +2934,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2962,7 +2977,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2976,10 +2991,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44473</v>
+        <v>46097</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3035,7 +3050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3049,10 +3064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44700</v>
+        <v>45950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3065,7 +3080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3108,7 +3123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3122,10 +3137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45715</v>
+        <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3137,13 +3152,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3186,7 +3196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3200,10 +3210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45401</v>
+        <v>46106</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3216,7 +3226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3259,7 +3269,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3273,10 +3283,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45190</v>
+        <v>44686</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3288,8 +3298,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3332,7 +3347,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3346,10 +3361,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44991</v>
+        <v>45317</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3361,8 +3376,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3405,7 +3425,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3419,10 +3439,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45056</v>
+        <v>46120</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3435,7 +3455,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3478,7 +3498,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3492,10 +3512,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44677</v>
+        <v>46119</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3507,13 +3527,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3556,7 +3571,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3570,10 +3585,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44909</v>
+        <v>45715</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,8 +3600,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3629,7 +3649,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3643,10 +3663,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45719</v>
+        <v>44700</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,13 +3678,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3707,7 +3722,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3717,14 +3732,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45715</v>
+        <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3736,13 +3751,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3785,7 +3795,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3799,10 +3809,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44795</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3815,7 +3825,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3858,7 +3868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3872,10 +3882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45446</v>
+        <v>44991</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3887,13 +3897,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3936,7 +3941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3950,10 +3955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45722</v>
+        <v>45644</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3966,7 +3971,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4009,7 +4014,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4023,10 +4028,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45377</v>
+        <v>45887</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4039,7 +4044,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4082,7 +4087,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4096,10 +4101,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44804</v>
+        <v>45545</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4112,7 +4117,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4155,7 +4160,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4169,10 +4174,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44503</v>
+        <v>45926</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4185,7 +4190,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4228,7 +4233,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45656</v>
+        <v>46008</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4258,7 +4263,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4301,7 +4306,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4311,14 +4316,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44670</v>
+        <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4331,7 +4336,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4374,7 +4379,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4388,10 +4393,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44815</v>
+        <v>45838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4404,7 +4409,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4447,7 +4452,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4457,14 +4462,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45835</v>
+        <v>44804</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4477,7 +4482,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4520,7 +4525,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4534,10 +4539,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45329</v>
+        <v>44473</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4550,7 +4555,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4593,7 +4598,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4607,10 +4612,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45838</v>
+        <v>44795</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4623,7 +4628,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4666,7 +4671,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4680,10 +4685,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45131</v>
+        <v>46147</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4696,7 +4701,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4739,7 +4744,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4753,10 +4758,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45282</v>
+        <v>45542</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4769,7 +4774,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4812,7 +4817,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4826,10 +4831,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45887</v>
+        <v>45656</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4842,7 +4847,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4885,7 +4890,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4899,10 +4904,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45281</v>
+        <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4915,7 +4920,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4958,7 +4963,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4972,10 +4977,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45317</v>
+        <v>45600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4987,13 +4992,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45939</v>
+        <v>44727</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>8.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5109,7 +5109,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45950</v>
+        <v>45133</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45898</v>
+        <v>46174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45919</v>
+        <v>45007</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5338,14 +5338,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45979</v>
+        <v>45329</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45979</v>
+        <v>44670</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45926</v>
+        <v>46196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46008</v>
+        <v>45351</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5620,7 +5620,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45719</v>
+        <v>46209</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5649,13 +5649,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5698,7 +5693,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46066</v>
+        <v>45233</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5728,7 +5723,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5771,7 +5766,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5785,10 +5780,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46071</v>
+        <v>46260</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5801,7 +5796,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5844,7 +5839,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5854,14 +5849,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46087</v>
+        <v>45190</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5874,7 +5869,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5917,7 +5912,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5931,10 +5926,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46097</v>
+        <v>44931</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5947,7 +5942,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5990,7 +5985,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6004,10 +5999,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46106</v>
+        <v>46265</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6020,7 +6015,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6063,7 +6058,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6077,10 +6072,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46119</v>
+        <v>46268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6093,7 +6088,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6136,7 +6131,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6150,10 +6145,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46120</v>
+        <v>45322</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6166,7 +6161,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6209,7 +6204,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6223,10 +6218,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45545</v>
+        <v>45322</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6239,7 +6234,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6282,7 +6277,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6296,10 +6291,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45887</v>
+        <v>45400</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6312,7 +6307,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6355,7 +6350,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6364,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46147</v>
+        <v>44473</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6380,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6423,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6437,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45600</v>
+        <v>44677</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6457,8 +6452,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46174</v>
+        <v>46238</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46196</v>
+        <v>45281</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46209</v>
+        <v>46286</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46254</v>
+        <v>44503</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46260</v>
+        <v>45131</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6866,7 +6866,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46265</v>
+        <v>45750</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6939,7 +6939,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46268</v>
+        <v>44815</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7012,7 +7012,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46286</v>
+        <v>45056</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44473</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44641</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44473</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44503</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45401</v>
+        <v>44727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45317</v>
+        <v>44784</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1740,13 +1740,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1789,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1803,10 +1798,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45719</v>
+        <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1818,13 +1813,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1867,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1881,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45719</v>
+        <v>45322</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,13 +1886,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1945,7 +1930,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1959,10 +1944,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44480</v>
+        <v>44503</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1975,7 +1960,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2018,7 +2003,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2032,10 +2017,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45715</v>
+        <v>45056</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2047,13 +2032,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2096,7 +2076,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2110,10 +2090,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45446</v>
+        <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2125,13 +2105,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2174,7 +2149,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2188,10 +2163,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45887</v>
+        <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2203,8 +2178,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2247,7 +2227,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2261,10 +2241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45898</v>
+        <v>45887</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2277,7 +2257,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2320,7 +2300,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2334,10 +2314,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45282</v>
+        <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2350,7 +2330,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2393,7 +2373,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2407,10 +2387,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46066</v>
+        <v>45719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2422,8 +2402,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2466,7 +2451,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2480,10 +2465,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44909</v>
+        <v>45715</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2495,8 +2480,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2539,7 +2529,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2553,10 +2543,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45919</v>
+        <v>45719</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2568,8 +2558,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2612,7 +2607,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46071</v>
+        <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2641,8 +2636,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2685,7 +2685,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46087</v>
+        <v>45898</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45722</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2831,7 +2831,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45939</v>
+        <v>44670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45377</v>
+        <v>46066</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2977,7 +2977,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46097</v>
+        <v>46071</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45950</v>
+        <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44784</v>
+        <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46106</v>
+        <v>45317</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3225,8 +3225,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>10.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3269,7 +3274,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3283,10 +3288,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44686</v>
+        <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3298,13 +3303,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45317</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3376,13 +3376,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3425,7 +3420,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3439,10 +3434,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46120</v>
+        <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3455,7 +3450,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3498,7 +3493,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3512,10 +3507,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46119</v>
+        <v>44931</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3528,7 +3523,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3571,7 +3566,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45715</v>
+        <v>45351</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3600,13 +3595,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3649,7 +3639,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3663,10 +3653,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44700</v>
+        <v>45542</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3679,7 +3669,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3722,7 +3712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3736,10 +3726,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45979</v>
+        <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3752,7 +3742,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3795,7 +3785,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3809,10 +3799,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>46097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3825,7 +3815,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3868,7 +3858,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3882,10 +3872,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44991</v>
+        <v>46106</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3898,7 +3888,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3941,7 +3931,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3951,14 +3941,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45644</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3971,7 +3961,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4014,7 +4004,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4028,10 +4018,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45887</v>
+        <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4044,7 +4034,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4087,7 +4077,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 54514-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4101,10 +4091,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45545</v>
+        <v>44473</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4117,7 +4107,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4160,7 +4150,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4174,10 +4164,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45926</v>
+        <v>46119</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4190,7 +4180,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4233,7 +4223,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4247,10 +4237,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46008</v>
+        <v>46120</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4263,7 +4253,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4306,7 +4296,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4316,14 +4306,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45835</v>
+        <v>45233</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4336,7 +4326,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4379,7 +4369,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4393,10 +4383,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45838</v>
+        <v>45317</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4408,8 +4398,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4452,7 +4447,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4462,14 +4457,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44804</v>
+        <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4482,7 +4477,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4525,7 +4520,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4539,10 +4534,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44473</v>
+        <v>45838</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4598,7 +4593,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4612,10 +4607,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44795</v>
+        <v>45545</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4628,7 +4623,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4671,7 +4666,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4685,10 +4680,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46147</v>
+        <v>45887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4701,7 +4696,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4744,7 +4739,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4758,10 +4753,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45542</v>
+        <v>45401</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4774,7 +4769,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4817,7 +4812,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4831,10 +4826,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45656</v>
+        <v>45190</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4847,7 +4842,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4890,7 +4885,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4904,10 +4899,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44503</v>
+        <v>44991</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4920,7 +4915,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4963,7 +4958,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4977,10 +4972,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45600</v>
+        <v>44795</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4993,7 +4988,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5036,7 +5031,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5050,10 +5045,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44727</v>
+        <v>46147</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5066,7 +5061,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5109,7 +5104,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5123,10 +5118,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45133</v>
+        <v>44804</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5139,7 +5134,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5182,7 +5177,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5196,10 +5191,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46174</v>
+        <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5212,7 +5207,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5255,7 +5250,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5269,10 +5264,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45007</v>
+        <v>45656</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5285,7 +5280,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5328,7 +5323,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5342,10 +5337,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45329</v>
+        <v>45600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5358,7 +5353,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5401,7 +5396,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5415,10 +5410,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44670</v>
+        <v>45131</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5431,7 +5426,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5474,7 +5469,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5488,10 +5483,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46196</v>
+        <v>46174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5504,7 +5499,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5547,7 +5542,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5561,10 +5556,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45351</v>
+        <v>45282</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5577,7 +5572,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5620,7 +5615,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5634,10 +5629,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46209</v>
+        <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5650,7 +5645,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5693,7 +5688,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5707,10 +5702,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45233</v>
+        <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5723,7 +5718,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5766,7 +5761,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5780,10 +5775,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46260</v>
+        <v>45133</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5796,7 +5791,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5839,7 +5834,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5853,10 +5848,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45190</v>
+        <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5869,7 +5864,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5912,7 +5907,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5926,10 +5921,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44931</v>
+        <v>44480</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5942,7 +5937,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5985,7 +5980,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5999,10 +5994,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46265</v>
+        <v>46209</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6015,7 +6010,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6058,7 +6053,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6072,10 +6067,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46268</v>
+        <v>46260</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6088,7 +6083,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6131,7 +6126,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6145,10 +6140,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45322</v>
+        <v>45644</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6161,7 +6156,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6204,7 +6199,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 54408-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6218,10 +6213,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45322</v>
+        <v>44473</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6234,7 +6229,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6277,7 +6272,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6291,10 +6286,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45400</v>
+        <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6307,7 +6302,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6350,7 +6345,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6364,10 +6359,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44473</v>
+        <v>46268</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6380,7 +6375,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6423,7 +6418,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6437,10 +6432,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44677</v>
+        <v>44700</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6452,13 +6447,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6491,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6505,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46238</v>
+        <v>44677</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6530,8 +6520,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6569,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6583,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45281</v>
+        <v>44909</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6599,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6642,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6656,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46286</v>
+        <v>46238</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6672,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6715,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6729,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44503</v>
+        <v>46286</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6745,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6788,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6802,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45131</v>
+        <v>44815</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6818,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6866,7 +6861,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6880,10 +6875,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45750</v>
+        <v>45329</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6896,7 +6891,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6939,7 +6934,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6953,10 +6948,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44815</v>
+        <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6969,7 +6964,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7012,7 +7007,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7026,10 +7021,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46254</v>
+        <v>44686</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7041,8 +7036,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45056</v>
+        <v>45007</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44891</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44473</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44641</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44473</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44503</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>44727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>44784</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45322</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44503</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45056</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45887</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>45719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45715</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45719</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45898</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>44670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46066</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>46071</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45317</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>44931</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45351</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45542</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>46097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>46106</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44473</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>46119</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46120</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>45233</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45317</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45838</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45545</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45401</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45190</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44991</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44795</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46147</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44804</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45656</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>45600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45131</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>46174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45282</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45133</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44480</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>46209</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>46260</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45644</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44473</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>46268</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44700</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44677</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44909</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46238</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>46286</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44815</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45329</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44686</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45007</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44891</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44473</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44641</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44473</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44503</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>44727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>44784</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45322</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44503</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45056</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45887</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>45719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45715</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45719</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45898</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>44670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46066</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>46071</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45317</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>44931</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45351</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45542</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>46097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>46106</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44473</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>46119</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46120</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>45233</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45317</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45838</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45545</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45401</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45190</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44991</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44795</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46147</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44804</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45656</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>45600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45131</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>46174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45282</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45133</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44480</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>46209</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>46260</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45644</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44473</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>46268</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44700</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44677</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44909</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46238</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>46286</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44815</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45329</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44686</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45007</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE89"/>
+  <dimension ref="A1:AE85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 54448-2021</t>
+          <t>A 12631-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44473</v>
+        <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 12631-2022</t>
+          <t>A 62536-2021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44641</v>
+        <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 62536-2021</t>
+          <t>A 62503-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 54521-2021</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44473</v>
+        <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1341,7 +1341,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 62503-2021</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44503</v>
+        <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1443,8 +1443,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>9.699999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1487,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1501,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44502</v>
+        <v>45401</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1517,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1560,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1574,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44686</v>
+        <v>45317</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1591,11 +1596,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>10.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1643,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1657,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44727</v>
+        <v>45446</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1667,8 +1672,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1721,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1735,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44784</v>
+        <v>44480</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1751,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1794,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1798,10 +1808,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45322</v>
+        <v>45282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1814,7 +1824,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1857,7 +1867,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1881,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45322</v>
+        <v>45722</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1887,7 +1897,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1930,7 +1940,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1944,10 +1954,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44503</v>
+        <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1960,7 +1970,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2003,7 +2013,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2017,10 +2027,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45056</v>
+        <v>44909</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2033,7 +2043,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2076,7 +2086,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2090,10 +2100,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45926</v>
+        <v>45887</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2106,7 +2116,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2149,7 +2159,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2159,14 +2169,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45715</v>
+        <v>45835</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2178,13 +2188,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2227,7 +2232,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2241,10 +2246,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45887</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2257,7 +2262,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2300,7 +2305,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2314,10 +2319,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46008</v>
+        <v>45898</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2330,7 +2335,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2373,7 +2378,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2387,10 +2392,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45719</v>
+        <v>44784</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2402,13 +2407,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45715</v>
+        <v>44686</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2482,11 +2482,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45719</v>
+        <v>45919</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2558,13 +2558,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2607,7 +2602,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2621,10 +2616,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45446</v>
+        <v>45317</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2638,11 +2633,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2685,7 +2680,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2699,10 +2694,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45898</v>
+        <v>45715</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2714,8 +2709,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>44700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44670</v>
+        <v>44991</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>46066</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46071</v>
+        <v>45939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45939</v>
+        <v>46071</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45281</v>
+        <v>45644</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45317</v>
+        <v>45950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3225,13 +3225,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>10.2</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3274,7 +3269,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3284,14 +3279,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45722</v>
+        <v>46087</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3304,7 +3299,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3347,7 +3342,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3361,10 +3356,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>46097</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3377,7 +3372,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3420,7 +3415,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45950</v>
+        <v>46106</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3450,7 +3445,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3493,7 +3488,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3507,10 +3502,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44931</v>
+        <v>44804</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3523,7 +3518,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3566,7 +3561,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3580,10 +3575,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45351</v>
+        <v>46120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3596,7 +3591,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3639,7 +3634,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3653,10 +3648,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45542</v>
+        <v>46119</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3669,7 +3664,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3712,7 +3707,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3726,10 +3721,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46087</v>
+        <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3742,7 +3737,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3785,7 +3780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3799,10 +3794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46097</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3815,7 +3810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3858,7 +3853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3872,10 +3867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46106</v>
+        <v>44795</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3888,7 +3883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3931,7 +3926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3941,14 +3936,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3961,7 +3956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4004,7 +3999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4018,10 +4013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45979</v>
+        <v>46008</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4034,7 +4029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4077,7 +4072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54514-2021</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4091,10 +4086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44473</v>
+        <v>45542</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4107,7 +4102,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4150,7 +4145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4164,10 +4159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46119</v>
+        <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4179,8 +4174,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4223,7 +4223,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46120</v>
+        <v>45656</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4296,7 +4296,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45233</v>
+        <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4369,7 +4369,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45317</v>
+        <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4398,13 +4398,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4447,7 +4442,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4457,14 +4452,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45835</v>
+        <v>45887</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4477,7 +4472,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4520,7 +4515,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4534,10 +4529,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45838</v>
+        <v>45545</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4550,7 +4545,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4593,7 +4588,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4607,10 +4602,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45545</v>
+        <v>45133</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4623,7 +4618,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4666,7 +4661,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4680,10 +4675,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45887</v>
+        <v>46147</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4696,7 +4691,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4739,7 +4734,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4753,10 +4748,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45401</v>
+        <v>45600</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4812,7 +4807,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4826,10 +4821,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45190</v>
+        <v>45007</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4885,7 +4880,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4899,10 +4894,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44991</v>
+        <v>45329</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4915,7 +4910,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4958,7 +4953,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4972,10 +4967,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44795</v>
+        <v>44670</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4988,7 +4983,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5031,7 +5026,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5045,10 +5040,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46147</v>
+        <v>46174</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5061,7 +5056,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5104,7 +5099,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5118,10 +5113,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44804</v>
+        <v>45351</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5134,7 +5129,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5177,7 +5172,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5191,10 +5186,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44503</v>
+        <v>45233</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5207,7 +5202,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5250,7 +5245,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5264,10 +5259,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45656</v>
+        <v>45190</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5280,7 +5275,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5323,7 +5318,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5337,10 +5332,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45600</v>
+        <v>44931</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5353,7 +5348,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5396,7 +5391,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5410,10 +5405,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45131</v>
+        <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5426,7 +5421,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5469,7 +5464,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46174</v>
+        <v>46209</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5499,7 +5494,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5542,7 +5537,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5556,10 +5551,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45282</v>
+        <v>45322</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5572,7 +5567,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5615,7 +5610,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5629,10 +5624,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45750</v>
+        <v>45322</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5645,7 +5640,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5705,7 +5700,7 @@
         <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5761,7 +5756,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5775,10 +5770,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45133</v>
+        <v>46260</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5791,7 +5786,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5834,7 +5829,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5848,10 +5843,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46196</v>
+        <v>46265</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5864,7 +5859,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5907,7 +5902,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5921,10 +5916,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44480</v>
+        <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5936,8 +5931,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46209</v>
+        <v>45281</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46260</v>
+        <v>46268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45644</v>
+        <v>44503</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54408-2021</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44473</v>
+        <v>45131</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46265</v>
+        <v>46238</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44700</v>
+        <v>45750</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44677</v>
+        <v>44815</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6520,13 +6520,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6569,7 +6564,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6583,10 +6578,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44909</v>
+        <v>45056</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6599,7 +6594,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6642,7 +6637,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6656,10 +6651,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6672,7 +6667,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6715,7 +6710,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6729,10 +6724,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46286</v>
+        <v>45719</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6744,8 +6739,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6785,10 +6785,10 @@
       </c>
       <c r="V84" s="2" t="inlineStr"/>
     </row>
-    <row r="85" ht="15" customHeight="1">
+    <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44815</v>
+        <v>45715</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6817,8 +6817,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6857,303 +6862,6 @@
         <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>A 4954-2024</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="n">
-        <v>45329</v>
-      </c>
-      <c r="E86" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>A 34360-2026</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="E87" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>A 18499-2022</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="n">
-        <v>44686</v>
-      </c>
-      <c r="E88" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>A 13876-2023</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="n">
-        <v>45007</v>
-      </c>
-      <c r="E89" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45401</v>
+        <v>44727</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45317</v>
+        <v>44784</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1594,13 +1594,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1643,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1657,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45446</v>
+        <v>45322</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1672,13 +1667,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1721,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1735,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44480</v>
+        <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1751,7 +1741,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1794,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1808,10 +1798,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45282</v>
+        <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1824,7 +1814,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1867,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1881,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45722</v>
+        <v>45715</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,8 +1886,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1940,7 +1935,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>45446</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1969,8 +1964,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44909</v>
+        <v>45887</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2086,7 +2086,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45887</v>
+        <v>44670</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45835</v>
+        <v>45722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>45377</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>45898</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44784</v>
+        <v>45281</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44686</v>
+        <v>45317</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2482,11 +2482,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>10.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45919</v>
+        <v>46066</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45317</v>
+        <v>44931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2631,13 +2631,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2680,7 +2675,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2694,10 +2689,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45715</v>
+        <v>46071</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2709,13 +2704,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2758,7 +2748,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2772,10 +2762,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2788,7 +2778,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2831,7 +2821,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2845,10 +2835,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44991</v>
+        <v>45542</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2861,7 +2851,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2904,7 +2894,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2918,10 +2908,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46066</v>
+        <v>45919</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2934,7 +2924,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2977,7 +2967,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2987,14 +2977,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45939</v>
+        <v>46087</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3007,7 +2997,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3050,7 +3040,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3064,10 +3054,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46071</v>
+        <v>46097</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3080,7 +3070,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3123,7 +3113,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3133,14 +3123,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45644</v>
+        <v>45835</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3153,7 +3143,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3196,7 +3186,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3210,10 +3200,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45950</v>
+        <v>45939</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3226,7 +3216,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3269,7 +3259,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3279,14 +3269,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46087</v>
+        <v>45838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3299,7 +3289,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3342,7 +3332,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3356,10 +3346,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46097</v>
+        <v>46106</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3372,7 +3362,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3415,7 +3405,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3429,10 +3419,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46106</v>
+        <v>45950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3445,7 +3435,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3488,7 +3478,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3502,10 +3492,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44804</v>
+        <v>46119</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3518,7 +3508,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3578,7 +3568,7 @@
         <v>46120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3634,7 +3624,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3648,10 +3638,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46119</v>
+        <v>45233</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3664,7 +3654,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3707,7 +3697,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3717,14 +3707,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45979</v>
+        <v>45317</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3736,8 +3726,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3780,7 +3775,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3794,10 +3789,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>45545</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3810,7 +3805,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3853,7 +3848,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3867,10 +3862,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44795</v>
+        <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3883,7 +3878,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3926,7 +3921,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3936,14 +3931,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45926</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3956,7 +3951,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3999,7 +3994,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4013,10 +4008,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46008</v>
+        <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4029,7 +4024,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4072,7 +4067,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4086,10 +4081,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45542</v>
+        <v>45926</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4102,7 +4097,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4145,7 +4140,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4159,10 +4154,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45719</v>
+        <v>46008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4174,13 +4169,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4223,7 +4213,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4237,10 +4227,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45656</v>
+        <v>45719</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4252,8 +4242,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4296,7 +4291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4310,10 +4305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44503</v>
+        <v>46147</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4326,7 +4321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4369,7 +4364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4383,10 +4378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44727</v>
+        <v>45600</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4399,7 +4394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4442,7 +4437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4456,10 +4451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45887</v>
+        <v>46174</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4472,7 +4467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4515,7 +4510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4529,10 +4524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45545</v>
+        <v>45401</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4545,7 +4540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4588,7 +4583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4602,10 +4597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45133</v>
+        <v>45190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4618,7 +4613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4661,7 +4656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4675,10 +4670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46147</v>
+        <v>44991</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4691,7 +4686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4734,7 +4729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4748,10 +4743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45600</v>
+        <v>44795</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4764,7 +4759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4807,7 +4802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4821,10 +4816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45007</v>
+        <v>46196</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4837,7 +4832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4880,7 +4875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4894,10 +4889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45329</v>
+        <v>44804</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4910,7 +4905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4953,7 +4948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4967,10 +4962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44670</v>
+        <v>44503</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4983,7 +4978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5026,7 +5021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5040,10 +5035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46174</v>
+        <v>45656</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5056,7 +5051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5099,7 +5094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5113,10 +5108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45351</v>
+        <v>46209</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5129,7 +5124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5172,7 +5167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5186,10 +5181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45233</v>
+        <v>46260</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5202,7 +5197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5245,7 +5240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5259,10 +5254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45190</v>
+        <v>45131</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5275,7 +5270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5318,7 +5313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5332,10 +5327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44931</v>
+        <v>45282</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5348,7 +5343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5391,7 +5386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5405,10 +5400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46196</v>
+        <v>46265</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5421,7 +5416,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5464,7 +5459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5478,10 +5473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46209</v>
+        <v>45750</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5494,7 +5489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5537,7 +5532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5551,10 +5546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45322</v>
+        <v>45400</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5567,7 +5562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5610,7 +5605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5624,10 +5619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45322</v>
+        <v>45133</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5640,7 +5635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5683,7 +5678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5697,10 +5692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45400</v>
+        <v>46268</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5713,7 +5708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5756,7 +5751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5770,10 +5765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46260</v>
+        <v>44480</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5786,7 +5781,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5829,7 +5824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5843,10 +5838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46265</v>
+        <v>46238</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5859,7 +5854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5902,7 +5897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5916,10 +5911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44677</v>
+        <v>46286</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5931,13 +5926,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5980,7 +5970,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5994,10 +5984,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45281</v>
+        <v>45644</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6010,7 +6000,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6053,7 +6043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6067,10 +6057,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46268</v>
+        <v>44700</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6083,7 +6073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6126,7 +6116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6140,10 +6130,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44503</v>
+        <v>44677</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6155,8 +6145,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6199,7 +6194,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6213,10 +6208,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45131</v>
+        <v>44909</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6229,7 +6224,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6272,7 +6267,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6286,10 +6281,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6302,7 +6297,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6345,7 +6340,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6359,10 +6354,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46286</v>
+        <v>44815</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6375,7 +6370,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6418,7 +6413,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6432,10 +6427,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45750</v>
+        <v>45329</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6448,7 +6443,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6491,7 +6486,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6505,10 +6500,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44815</v>
+        <v>44686</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6520,8 +6515,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45056</v>
+        <v>45007</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46254</v>
+        <v>45056</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
         <v>45719</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45715</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1297,8 +1297,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>9.699999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1341,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1355,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44502</v>
+        <v>44686</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1371,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1414,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1428,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44686</v>
+        <v>44804</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1443,13 +1448,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44727</v>
+        <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.6</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44784</v>
+        <v>45401</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45322</v>
+        <v>45056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45322</v>
+        <v>44795</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44503</v>
+        <v>45887</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45715</v>
+        <v>45719</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45446</v>
+        <v>45715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1966,11 +1966,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45887</v>
+        <v>45542</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2086,7 +2086,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44670</v>
+        <v>45317</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2115,8 +2115,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2159,7 +2164,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2173,10 +2178,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45722</v>
+        <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2189,7 +2194,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2232,7 +2237,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2246,10 +2251,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45377</v>
+        <v>44480</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2262,7 +2267,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2305,7 +2310,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2319,10 +2324,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45898</v>
+        <v>45446</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2334,8 +2339,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2378,7 +2388,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2392,10 +2402,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45281</v>
+        <v>45656</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2408,7 +2418,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2451,7 +2461,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2465,10 +2475,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45317</v>
+        <v>44503</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2480,13 +2490,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>10.2</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2529,7 +2534,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2543,10 +2548,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46066</v>
+        <v>45722</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2559,7 +2564,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2602,7 +2607,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2616,10 +2621,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44931</v>
+        <v>44727</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2632,7 +2637,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>8.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2675,7 +2680,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2689,10 +2694,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46071</v>
+        <v>45377</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2705,7 +2710,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2748,7 +2753,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2762,10 +2767,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45351</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2778,7 +2783,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2821,7 +2826,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2835,10 +2840,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45542</v>
+        <v>45133</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2851,7 +2856,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2894,7 +2899,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2904,14 +2909,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45919</v>
+        <v>45835</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2924,7 +2929,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2967,7 +2972,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2977,14 +2982,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46087</v>
+        <v>45838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2997,7 +3002,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3040,7 +3045,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3054,10 +3059,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46097</v>
+        <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3070,7 +3075,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3113,7 +3118,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3123,14 +3128,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45835</v>
+        <v>45282</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3143,7 +3148,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3186,7 +3191,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3200,10 +3205,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45939</v>
+        <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3216,7 +3221,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3259,7 +3264,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45838</v>
+        <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3289,7 +3294,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3332,7 +3337,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3346,10 +3351,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46106</v>
+        <v>45007</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3362,7 +3367,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3405,7 +3410,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45950</v>
+        <v>45329</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3435,7 +3440,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3478,7 +3483,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3492,10 +3497,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46119</v>
+        <v>45887</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3508,7 +3513,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3551,7 +3556,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3565,10 +3570,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46120</v>
+        <v>45545</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3581,7 +3586,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3624,7 +3629,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3638,10 +3643,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45233</v>
+        <v>44670</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3654,7 +3659,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3697,7 +3702,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3711,10 +3716,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45317</v>
+        <v>44784</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3726,13 +3731,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3775,7 +3775,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45545</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45887</v>
+        <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3921,7 +3921,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>44686</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3950,8 +3950,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3994,7 +3999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4008,10 +4013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45979</v>
+        <v>45351</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4024,7 +4029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4067,7 +4072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4081,10 +4086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45926</v>
+        <v>45317</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4096,8 +4101,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4140,7 +4150,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4154,10 +4164,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46008</v>
+        <v>46147</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4170,7 +4180,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4213,7 +4223,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4227,10 +4237,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45719</v>
+        <v>45715</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4291,7 +4301,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4305,10 +4315,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46147</v>
+        <v>44700</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4321,7 +4331,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4364,7 +4374,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4378,10 +4388,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45600</v>
+        <v>44991</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4394,7 +4404,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4437,7 +4447,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4451,10 +4461,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46174</v>
+        <v>45600</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4467,7 +4477,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4510,7 +4520,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4524,10 +4534,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45401</v>
+        <v>45926</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4540,7 +4550,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4583,7 +4593,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4597,10 +4607,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45190</v>
+        <v>45644</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4613,7 +4623,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4656,7 +4666,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4670,10 +4680,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44991</v>
+        <v>46008</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4686,7 +4696,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4729,7 +4739,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4743,10 +4753,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44795</v>
+        <v>45233</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4759,7 +4769,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4802,7 +4812,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4816,10 +4826,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46196</v>
+        <v>45719</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4831,8 +4841,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4875,7 +4890,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4889,10 +4904,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44804</v>
+        <v>45190</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4905,7 +4920,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4948,7 +4963,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4962,10 +4977,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44503</v>
+        <v>44931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4978,7 +4993,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5021,7 +5036,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5035,10 +5050,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45656</v>
+        <v>46174</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5051,7 +5066,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5094,7 +5109,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5108,10 +5123,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46209</v>
+        <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5124,7 +5139,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5167,7 +5182,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5181,10 +5196,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46260</v>
+        <v>45322</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5197,7 +5212,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5240,7 +5255,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5254,10 +5269,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45131</v>
+        <v>45400</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5270,7 +5285,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5313,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5327,10 +5342,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45282</v>
+        <v>46066</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5343,7 +5358,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5386,7 +5401,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5400,10 +5415,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46265</v>
+        <v>46071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5416,7 +5431,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5459,7 +5474,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5473,10 +5488,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45750</v>
+        <v>46196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5489,7 +5504,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5532,7 +5547,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5542,14 +5557,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45400</v>
+        <v>46087</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5562,7 +5577,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5605,7 +5620,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5619,10 +5634,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45133</v>
+        <v>44677</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5634,8 +5649,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5678,7 +5698,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5692,10 +5712,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46268</v>
+        <v>45281</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5708,7 +5728,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5751,7 +5771,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5765,10 +5785,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44480</v>
+        <v>46097</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5781,7 +5801,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5824,7 +5844,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5838,10 +5858,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46238</v>
+        <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5854,7 +5874,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5897,7 +5917,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5911,10 +5931,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46286</v>
+        <v>46209</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5927,7 +5947,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5970,7 +5990,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5984,10 +6004,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45644</v>
+        <v>46106</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6000,7 +6020,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6043,7 +6063,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6057,10 +6077,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44700</v>
+        <v>45131</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6073,7 +6093,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6116,7 +6136,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6130,10 +6150,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44677</v>
+        <v>46120</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6145,13 +6165,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6194,7 +6209,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6208,10 +6223,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44909</v>
+        <v>46119</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6224,7 +6239,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6267,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6281,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46254</v>
+        <v>45750</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6297,7 +6312,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6340,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6354,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44815</v>
+        <v>46265</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6370,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6413,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6427,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45329</v>
+        <v>44815</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6443,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6486,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6500,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44686</v>
+        <v>46268</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6515,13 +6530,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6564,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6578,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45007</v>
+        <v>46238</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6594,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6637,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6651,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45056</v>
+        <v>46286</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6667,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6710,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6724,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45719</v>
+        <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6739,13 +6749,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6788,7 +6793,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6802,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45715</v>
+        <v>46260</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6817,13 +6822,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1297,13 +1297,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1341,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1355,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44686</v>
+        <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1371,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44804</v>
+        <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1448,8 +1443,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44502</v>
+        <v>44727</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45401</v>
+        <v>45322</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45056</v>
+        <v>45322</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44795</v>
+        <v>44784</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45887</v>
+        <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45719</v>
+        <v>45715</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45715</v>
+        <v>45446</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1966,11 +1966,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45542</v>
+        <v>44670</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2086,7 +2086,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45317</v>
+        <v>45281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2115,13 +2115,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>10.2</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2164,7 +2159,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45898</v>
+        <v>45317</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2193,8 +2188,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44480</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45446</v>
+        <v>45887</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2339,13 +2339,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2388,7 +2383,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2402,10 +2397,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45656</v>
+        <v>44931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2418,7 +2413,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2461,7 +2456,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2475,10 +2470,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44503</v>
+        <v>45351</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2491,7 +2486,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2534,7 +2529,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2548,10 +2543,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45722</v>
+        <v>45542</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2564,7 +2559,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2607,7 +2602,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2617,14 +2612,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44727</v>
+        <v>46087</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2637,7 +2632,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.6</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2680,7 +2675,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2694,10 +2689,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45377</v>
+        <v>45898</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2710,7 +2705,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2753,7 +2748,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2767,10 +2762,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>46097</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2826,7 +2821,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2840,10 +2835,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45133</v>
+        <v>45919</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2856,7 +2851,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2899,7 +2894,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2909,14 +2904,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45835</v>
+        <v>46106</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2929,7 +2924,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2972,7 +2967,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2986,10 +2981,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45838</v>
+        <v>45233</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3002,7 +2997,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3045,7 +3040,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3059,10 +3054,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45939</v>
+        <v>45317</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,8 +3069,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45282</v>
+        <v>45939</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44909</v>
+        <v>45950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45950</v>
+        <v>45401</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45007</v>
+        <v>46119</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45329</v>
+        <v>45190</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45887</v>
+        <v>44991</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3556,7 +3556,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45545</v>
+        <v>46120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3629,7 +3629,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44670</v>
+        <v>44795</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,14 +3712,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44784</v>
+        <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3775,7 +3775,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
         <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>44804</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3921,7 +3921,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44686</v>
+        <v>44503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3950,13 +3950,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3999,7 +3994,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4013,10 +4008,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45351</v>
+        <v>45656</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4029,7 +4024,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4072,7 +4067,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4086,10 +4081,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45317</v>
+        <v>45545</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4101,13 +4096,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4150,7 +4140,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4164,10 +4154,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46147</v>
+        <v>45887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4180,7 +4170,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4223,7 +4213,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4237,10 +4227,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45715</v>
+        <v>45926</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4252,13 +4242,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4301,7 +4286,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4315,10 +4300,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44700</v>
+        <v>46008</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4331,7 +4316,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4374,7 +4359,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4388,10 +4373,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44991</v>
+        <v>45719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4403,8 +4388,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4447,7 +4437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4461,10 +4451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45600</v>
+        <v>45131</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4477,7 +4467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4520,7 +4510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4534,10 +4524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45926</v>
+        <v>45282</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4550,7 +4540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4593,7 +4583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4607,10 +4597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45644</v>
+        <v>45750</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4623,7 +4613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4666,7 +4656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4680,10 +4670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46008</v>
+        <v>45400</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4696,7 +4686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4739,7 +4729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4753,10 +4743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45233</v>
+        <v>45133</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4769,7 +4759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4812,7 +4802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4826,10 +4816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45719</v>
+        <v>46066</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4841,13 +4831,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4890,7 +4875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4904,10 +4889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45190</v>
+        <v>46071</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4920,7 +4905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4963,7 +4948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4977,10 +4962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44931</v>
+        <v>46147</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4993,7 +4978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5036,7 +5021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5050,10 +5035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46174</v>
+        <v>44480</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5066,7 +5051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5109,7 +5094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5123,10 +5108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45322</v>
+        <v>45600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5139,7 +5124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5182,7 +5167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5196,10 +5181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45322</v>
+        <v>45644</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5212,7 +5197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5255,7 +5240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5269,10 +5254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45400</v>
+        <v>44700</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5285,7 +5270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5328,7 +5313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5342,10 +5327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46066</v>
+        <v>46174</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5358,7 +5343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5401,7 +5386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5415,10 +5400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46071</v>
+        <v>44677</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5430,8 +5415,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5474,7 +5464,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5488,10 +5478,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46196</v>
+        <v>44909</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5504,7 +5494,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5547,7 +5537,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5557,14 +5547,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46087</v>
+        <v>46196</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5577,7 +5567,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5620,7 +5610,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5634,10 +5624,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44677</v>
+        <v>44815</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5649,13 +5639,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5698,7 +5683,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5712,10 +5697,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45281</v>
+        <v>45329</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5728,7 +5713,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5771,7 +5756,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5785,10 +5770,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46097</v>
+        <v>46209</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5801,7 +5786,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5844,7 +5829,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5858,10 +5843,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44503</v>
+        <v>44686</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5873,8 +5858,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5917,7 +5907,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5931,10 +5921,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46209</v>
+        <v>45007</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5947,7 +5937,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5990,7 +5980,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6004,10 +5994,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46106</v>
+        <v>46265</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6020,7 +6010,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6063,7 +6053,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6077,10 +6067,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45131</v>
+        <v>46268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6093,7 +6083,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6136,7 +6126,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6150,10 +6140,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6166,7 +6156,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6209,7 +6199,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6223,10 +6213,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46119</v>
+        <v>45056</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6239,7 +6229,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6282,7 +6272,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6296,10 +6286,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45750</v>
+        <v>45719</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6311,8 +6301,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6355,7 +6350,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6364,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46265</v>
+        <v>45715</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6384,8 +6379,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44815</v>
+        <v>46286</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46268</v>
+        <v>45722</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46238</v>
+        <v>45377</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6657,14 +6657,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46286</v>
+        <v>45835</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6737,7 +6737,7 @@
         <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>46260</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 62503-2021</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44503</v>
+        <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 62503-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44686</v>
+        <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>9.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44727</v>
+        <v>44795</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45322</v>
+        <v>45542</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45322</v>
+        <v>45750</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44784</v>
+        <v>45656</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1801,7 +1801,7 @@
         <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45715</v>
+        <v>45401</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1886,13 +1886,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1935,7 +1930,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45446</v>
+        <v>44815</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1964,13 +1959,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2013,7 +2003,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2027,10 +2017,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44670</v>
+        <v>45317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2042,8 +2032,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2086,7 +2081,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2100,10 +2095,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45281</v>
+        <v>44727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2116,7 +2111,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2159,7 +2154,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 56629-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2173,10 +2168,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45317</v>
+        <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2188,13 +2183,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>10.2</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2237,7 +2227,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2251,10 +2241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2266,8 +2256,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2327,7 +2322,7 @@
         <v>45887</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2383,7 +2378,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2397,10 +2392,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44931</v>
+        <v>45133</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2456,7 +2451,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2470,10 +2465,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45351</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2486,7 +2481,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2529,7 +2524,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2543,10 +2538,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45542</v>
+        <v>45282</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2559,7 +2554,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2602,7 +2597,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2612,14 +2607,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46087</v>
+        <v>44909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2632,7 +2627,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2675,7 +2670,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2689,10 +2684,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45898</v>
+        <v>45056</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2705,7 +2700,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2748,7 +2743,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2762,10 +2757,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46097</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2821,7 +2816,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2835,10 +2830,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45919</v>
+        <v>45719</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2850,8 +2845,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46106</v>
+        <v>45715</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2923,8 +2923,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2967,7 +2972,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2981,10 +2986,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45233</v>
+        <v>45007</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2997,7 +3002,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3040,7 +3045,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3054,10 +3059,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45317</v>
+        <v>45329</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3069,13 +3074,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45939</v>
+        <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45950</v>
+        <v>45722</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45401</v>
+        <v>44686</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,8 +3293,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3337,7 +3342,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3351,10 +3356,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46119</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3367,7 +3372,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3410,7 +3415,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3424,10 +3429,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45190</v>
+        <v>44670</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3440,7 +3445,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3483,7 +3488,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3497,10 +3502,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44991</v>
+        <v>45939</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3513,7 +3518,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3556,7 +3561,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3570,10 +3575,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46120</v>
+        <v>45351</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3586,7 +3591,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3629,7 +3634,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3643,10 +3648,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44795</v>
+        <v>45317</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,8 +3663,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3702,7 +3712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,14 +3722,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45979</v>
+        <v>45715</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3731,8 +3741,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3775,7 +3790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3789,10 +3804,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>45950</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3805,7 +3820,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3848,7 +3863,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3862,10 +3877,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44804</v>
+        <v>44700</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3921,7 +3936,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3935,10 +3950,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44503</v>
+        <v>44991</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3951,7 +3966,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3994,7 +4009,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4004,14 +4019,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45656</v>
+        <v>45835</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4024,7 +4039,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4067,7 +4082,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4081,10 +4096,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45545</v>
+        <v>45838</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4097,7 +4112,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4140,7 +4155,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4154,10 +4169,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45887</v>
+        <v>45644</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4170,7 +4185,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4213,7 +4228,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4227,10 +4242,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45926</v>
+        <v>45233</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4243,7 +4258,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4286,7 +4301,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4300,10 +4315,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46008</v>
+        <v>45190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4316,7 +4331,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4359,7 +4374,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4373,10 +4388,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45719</v>
+        <v>44931</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4388,13 +4403,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4437,7 +4447,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4447,14 +4457,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45131</v>
+        <v>45979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4467,7 +4477,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4510,7 +4520,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4524,10 +4534,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45282</v>
+        <v>45979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4540,7 +4550,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4583,7 +4593,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4597,10 +4607,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45750</v>
+        <v>44804</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4613,7 +4623,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4656,7 +4666,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4670,10 +4680,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45400</v>
+        <v>46106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4686,7 +4696,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4729,7 +4739,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4743,10 +4753,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45133</v>
+        <v>45322</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4759,7 +4769,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4802,7 +4812,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4816,10 +4826,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46066</v>
+        <v>45322</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4832,7 +4842,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.3</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4875,7 +4885,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4889,10 +4899,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46071</v>
+        <v>46120</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4905,7 +4915,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4948,7 +4958,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4962,10 +4972,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46147</v>
+        <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4978,7 +4988,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5021,7 +5031,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5035,10 +5045,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44480</v>
+        <v>45400</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5051,7 +5061,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5094,7 +5104,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5108,10 +5118,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45600</v>
+        <v>45926</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5124,7 +5134,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5167,7 +5177,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5181,10 +5191,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45644</v>
+        <v>46008</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5197,7 +5207,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5240,7 +5250,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5254,10 +5264,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44700</v>
+        <v>44677</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5269,8 +5279,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5313,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5327,10 +5342,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46174</v>
+        <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5342,8 +5357,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5386,7 +5406,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5400,10 +5420,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44677</v>
+        <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5415,13 +5435,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5464,7 +5479,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5478,10 +5493,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44909</v>
+        <v>45887</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5494,7 +5509,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5537,7 +5552,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5551,10 +5566,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46196</v>
+        <v>45545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5567,7 +5582,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5610,7 +5625,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5624,10 +5639,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44815</v>
+        <v>44503</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5640,7 +5655,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5683,7 +5698,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5697,10 +5712,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45329</v>
+        <v>45131</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5713,7 +5728,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5756,7 +5771,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5770,10 +5785,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46209</v>
+        <v>46066</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5786,7 +5801,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>7.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5829,7 +5844,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5843,10 +5858,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44686</v>
+        <v>46147</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5858,13 +5873,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5907,7 +5917,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5921,10 +5931,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45007</v>
+        <v>46071</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5937,7 +5947,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5980,7 +5990,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5990,14 +6000,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46265</v>
+        <v>46087</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6010,7 +6020,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6053,7 +6063,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6067,10 +6077,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46268</v>
+        <v>45600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6083,7 +6093,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6126,7 +6136,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6140,10 +6150,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46238</v>
+        <v>46097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6156,7 +6166,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6199,7 +6209,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6213,10 +6223,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45056</v>
+        <v>46174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6229,7 +6239,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6272,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6286,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45719</v>
+        <v>46196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6301,13 +6311,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6350,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6364,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45715</v>
+        <v>46209</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6379,13 +6384,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45722</v>
+        <v>46268</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45377</v>
+        <v>46238</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6657,14 +6657,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45835</v>
+        <v>46286</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6737,7 +6737,7 @@
         <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>46260</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44795</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45542</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45750</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45656</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45401</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44815</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45887</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45133</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45282</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45056</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45719</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45715</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45007</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>45329</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45722</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44686</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44670</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45939</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>45351</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>45317</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>45715</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45950</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44700</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44991</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45835</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45838</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45644</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45233</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44931</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44804</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>46106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45322</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45322</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>46120</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45400</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45926</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>46008</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>44677</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45887</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>44503</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45131</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>46066</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>46147</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46071</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>46087</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>46174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>46196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>46209</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>46265</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>46268</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>46238</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46286</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>46260</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44503</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44795</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45542</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45750</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45656</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45401</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44815</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45887</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45133</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45282</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45056</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45719</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45715</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45007</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>45329</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44784</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45722</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>44686</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44670</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45939</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>45351</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>45317</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>45715</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45950</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44700</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44991</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45835</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45838</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45644</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45233</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44931</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44804</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>46106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45322</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45322</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>46120</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45400</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45926</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>46008</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>44677</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45887</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>44503</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45131</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>46066</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>46147</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46071</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>46087</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>46174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>46196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>46209</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>46265</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>46268</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>46238</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46286</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>46260</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE85"/>
+  <dimension ref="A1:AE84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,259 +647,259 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 40387-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 40387-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Röd glada</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 62503-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44686</v>
+        <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 62503-2021</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44503</v>
+        <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44795</v>
+        <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1521,8 +1521,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1570,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1584,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45542</v>
+        <v>45898</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1595,7 +1600,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1643,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1657,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45750</v>
+        <v>45887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1716,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1730,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45656</v>
+        <v>44727</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1746,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1789,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44503</v>
+        <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1814,7 +1819,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1857,7 +1862,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1876,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45401</v>
+        <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1887,7 +1892,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1930,7 +1935,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44815</v>
+        <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1960,7 +1965,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2003,7 +2008,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2017,10 +2022,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45317</v>
+        <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2032,13 +2037,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44727</v>
+        <v>45950</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 56629-2021</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44480</v>
+        <v>45322</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2227,7 +2227,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45446</v>
+        <v>45322</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2256,13 +2256,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2305,7 +2300,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2319,10 +2314,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45887</v>
+        <v>46196</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2335,7 +2330,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2378,7 +2373,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2392,10 +2387,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45133</v>
+        <v>44784</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2408,7 +2403,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2451,7 +2446,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2465,10 +2460,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>45056</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2481,7 +2476,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2524,7 +2519,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2534,14 +2529,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45282</v>
+        <v>45979</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2554,7 +2549,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2597,7 +2592,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2611,10 +2606,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44909</v>
+        <v>46209</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2627,7 +2622,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2670,7 +2665,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2684,10 +2679,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45056</v>
+        <v>45979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2700,7 +2695,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2743,7 +2738,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2757,10 +2752,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>45719</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2772,8 +2767,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45719</v>
+        <v>45715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45715</v>
+        <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2921,11 +2921,6 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2972,7 +2967,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2986,10 +2981,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45007</v>
+        <v>46268</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3002,7 +2997,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3045,7 +3040,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3059,10 +3054,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45329</v>
+        <v>45926</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3075,7 +3070,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3118,7 +3113,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3132,10 +3127,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44784</v>
+        <v>45722</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3148,7 +3143,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3191,7 +3186,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3205,10 +3200,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45722</v>
+        <v>45377</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3221,7 +3216,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3264,7 +3259,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44686</v>
+        <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,13 +3288,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3342,7 +3332,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3356,10 +3346,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>45719</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3371,8 +3361,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3415,7 +3410,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3425,14 +3420,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44670</v>
+        <v>45835</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3445,7 +3440,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3488,7 +3483,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3502,10 +3497,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45939</v>
+        <v>46238</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3518,7 +3513,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3561,7 +3556,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3575,10 +3570,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45351</v>
+        <v>45838</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3591,7 +3586,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3634,7 +3629,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3648,10 +3643,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45317</v>
+        <v>46286</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3663,13 +3658,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3729,7 +3719,7 @@
         <v>45715</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3790,7 +3780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3804,10 +3794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45950</v>
+        <v>46066</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3820,7 +3810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3863,7 +3853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3877,10 +3867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44700</v>
+        <v>46071</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3893,7 +3883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3936,7 +3926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3946,14 +3936,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44991</v>
+        <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3966,7 +3956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4009,7 +3999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4019,14 +4009,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45835</v>
+        <v>46097</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4039,7 +4029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4082,7 +4072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4096,10 +4086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45838</v>
+        <v>45446</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4111,8 +4101,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4155,7 +4150,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4169,10 +4164,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45644</v>
+        <v>46254</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4185,7 +4180,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4228,7 +4223,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4242,10 +4237,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45233</v>
+        <v>46106</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4301,7 +4296,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4315,10 +4310,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45190</v>
+        <v>46119</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4331,7 +4326,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4374,7 +4369,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4388,10 +4383,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44931</v>
+        <v>46120</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4404,7 +4399,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4447,7 +4442,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4457,14 +4452,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45979</v>
+        <v>46260</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4477,7 +4472,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4520,7 +4515,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4534,10 +4529,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45979</v>
+        <v>46265</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4550,7 +4545,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4593,7 +4588,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4607,10 +4602,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44804</v>
+        <v>45545</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4623,7 +4618,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4666,7 +4661,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4680,10 +4675,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46106</v>
+        <v>45887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4696,7 +4691,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4739,7 +4734,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4753,10 +4748,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45322</v>
+        <v>44670</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4769,7 +4764,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4812,7 +4807,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4826,10 +4821,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45322</v>
+        <v>45281</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4842,7 +4837,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4885,7 +4880,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4899,10 +4894,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46120</v>
+        <v>45317</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4914,8 +4909,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>10.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46119</v>
+        <v>44931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45400</v>
+        <v>45351</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45926</v>
+        <v>45542</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46008</v>
+        <v>46147</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44677</v>
+        <v>45600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5279,13 +5279,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5328,7 +5323,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5342,10 +5337,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45719</v>
+        <v>45233</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5357,13 +5352,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5406,7 +5396,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5420,10 +5410,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45281</v>
+        <v>45317</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5435,8 +5425,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5479,7 +5474,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5493,10 +5488,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45887</v>
+        <v>45401</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5509,7 +5504,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5552,7 +5547,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5566,10 +5561,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45545</v>
+        <v>45190</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5582,7 +5577,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5625,7 +5620,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5639,10 +5634,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44503</v>
+        <v>44991</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5655,7 +5650,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5698,7 +5693,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45131</v>
+        <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5728,7 +5723,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5771,7 +5766,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5785,10 +5780,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46066</v>
+        <v>44804</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5801,7 +5796,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5844,7 +5839,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5858,10 +5853,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46147</v>
+        <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5874,7 +5869,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5917,7 +5912,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5931,10 +5926,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46071</v>
+        <v>45656</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5947,7 +5942,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5990,7 +5985,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6000,14 +5995,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46087</v>
+        <v>45131</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6020,7 +6015,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6063,7 +6058,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6077,10 +6072,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45600</v>
+        <v>45282</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6093,7 +6088,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6136,7 +6131,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6150,10 +6145,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46097</v>
+        <v>45750</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6166,7 +6161,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6209,7 +6204,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6223,10 +6218,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46174</v>
+        <v>45400</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6239,7 +6234,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6282,7 +6277,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6296,10 +6291,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46196</v>
+        <v>45133</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6312,7 +6307,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6355,7 +6350,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6364,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46209</v>
+        <v>45644</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6380,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6423,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6437,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46265</v>
+        <v>44700</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6453,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6496,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6510,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46268</v>
+        <v>44677</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6530,8 +6525,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46238</v>
+        <v>44909</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46286</v>
+        <v>44815</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6717,10 +6717,10 @@
       </c>
       <c r="V83" s="2" t="inlineStr"/>
     </row>
-    <row r="84" ht="15" customHeight="1">
+    <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46254</v>
+        <v>45329</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6789,79 +6789,6 @@
         <v>0</v>
       </c>
       <c r="V84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>A 35134-2026</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="E85" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE84"/>
+  <dimension ref="A1:AE85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,259 +647,259 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 40387-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2.5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Röd glada</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44686</v>
+        <v>45401</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1521,13 +1521,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1570,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1584,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45898</v>
+        <v>45317</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1599,8 +1594,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45887</v>
+        <v>45719</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1670,6 +1670,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1716,7 +1721,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1730,10 +1735,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44727</v>
+        <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,8 +1750,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1789,7 +1799,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1803,10 +1813,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46174</v>
+        <v>45719</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1818,8 +1828,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1862,7 +1877,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1876,10 +1891,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45007</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1891,8 +1906,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1935,7 +1955,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,10 +1969,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45919</v>
+        <v>45887</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1965,7 +1985,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2008,7 +2028,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2022,10 +2042,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45939</v>
+        <v>45722</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2038,7 +2058,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2081,7 +2101,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2095,10 +2115,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45950</v>
+        <v>45377</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2111,7 +2131,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2154,7 +2174,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2168,10 +2188,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45322</v>
+        <v>45898</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2184,7 +2204,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2227,7 +2247,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2241,10 +2261,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45322</v>
+        <v>45282</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2257,7 +2277,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2300,7 +2320,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2314,10 +2334,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46196</v>
+        <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2330,7 +2350,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2373,7 +2393,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2387,10 +2407,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44784</v>
+        <v>44909</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2403,7 +2423,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2446,7 +2466,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2456,14 +2476,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45056</v>
+        <v>45835</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2476,7 +2496,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2519,7 +2539,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2529,14 +2549,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45979</v>
+        <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2549,7 +2569,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2592,7 +2612,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2606,10 +2626,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46209</v>
+        <v>45939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2622,7 +2642,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2665,7 +2685,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2679,10 +2699,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45979</v>
+        <v>45950</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2695,7 +2715,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2738,7 +2758,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2752,10 +2772,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45719</v>
+        <v>44784</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2767,13 +2787,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2816,7 +2831,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2830,10 +2845,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45715</v>
+        <v>44686</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2847,11 +2862,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2894,7 +2909,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2904,14 +2919,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44503</v>
+        <v>45979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2924,7 +2939,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2967,7 +2982,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2981,10 +2996,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46268</v>
+        <v>45979</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2997,7 +3012,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3040,7 +3055,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3054,10 +3069,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45926</v>
+        <v>45317</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3069,8 +3084,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3113,7 +3133,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3127,10 +3147,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45722</v>
+        <v>45715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3142,8 +3162,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3186,7 +3211,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3200,10 +3225,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45377</v>
+        <v>44700</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3216,7 +3241,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3259,7 +3284,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3273,10 +3298,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46008</v>
+        <v>46066</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3289,7 +3314,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3332,7 +3357,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3346,10 +3371,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45719</v>
+        <v>44991</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3361,13 +3386,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3410,7 +3430,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3420,14 +3440,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45835</v>
+        <v>46071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3440,7 +3460,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3483,7 +3503,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3497,10 +3517,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46238</v>
+        <v>45926</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3513,7 +3533,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3556,7 +3576,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3570,10 +3590,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45838</v>
+        <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3586,7 +3606,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3629,7 +3649,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3643,10 +3663,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46286</v>
+        <v>46008</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3659,7 +3679,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3702,7 +3722,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,14 +3732,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45715</v>
+        <v>46087</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3731,13 +3751,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3780,7 +3795,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3794,10 +3809,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46066</v>
+        <v>46097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3810,7 +3825,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3853,7 +3868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3867,10 +3882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46071</v>
+        <v>44804</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3883,7 +3898,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3926,7 +3941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3936,14 +3951,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46087</v>
+        <v>46106</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3956,7 +3971,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3999,7 +4014,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4013,10 +4028,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46097</v>
+        <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4029,7 +4044,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4072,7 +4087,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4086,10 +4101,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45446</v>
+        <v>46119</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4101,13 +4116,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4150,7 +4160,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4164,10 +4174,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46254</v>
+        <v>44795</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4180,7 +4190,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4223,7 +4233,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4237,10 +4247,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46106</v>
+        <v>45542</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4253,7 +4263,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4296,7 +4306,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4310,10 +4320,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46119</v>
+        <v>45656</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4326,7 +4336,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4369,7 +4379,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4383,10 +4393,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46120</v>
+        <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4399,7 +4409,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4442,7 +4452,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4456,10 +4466,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46260</v>
+        <v>44727</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4472,7 +4482,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4515,7 +4525,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4529,10 +4539,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46265</v>
+        <v>45887</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4545,7 +4555,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4605,7 +4615,7 @@
         <v>45545</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4661,7 +4671,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4675,10 +4685,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45887</v>
+        <v>45133</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4691,7 +4701,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4734,7 +4744,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4748,10 +4758,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44670</v>
+        <v>46147</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4764,7 +4774,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4807,7 +4817,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4821,10 +4831,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45281</v>
+        <v>45007</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4837,7 +4847,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4880,7 +4890,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4894,10 +4904,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45317</v>
+        <v>45329</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4909,13 +4919,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>10.2</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4958,7 +4963,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4972,10 +4977,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44931</v>
+        <v>45600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4988,7 +4993,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5031,7 +5036,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5045,10 +5050,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45351</v>
+        <v>44670</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5061,7 +5066,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5104,7 +5109,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5118,10 +5123,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45542</v>
+        <v>45351</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5134,7 +5139,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5177,7 +5182,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5191,10 +5196,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46147</v>
+        <v>46174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5207,7 +5212,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5250,7 +5255,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5264,10 +5269,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45600</v>
+        <v>45233</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5280,7 +5285,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5323,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5337,10 +5342,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45233</v>
+        <v>45190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5353,7 +5358,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5396,7 +5401,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5410,10 +5415,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45317</v>
+        <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5425,13 +5430,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45401</v>
+        <v>46196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45190</v>
+        <v>45322</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5620,7 +5620,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44991</v>
+        <v>45322</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44795</v>
+        <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44804</v>
+        <v>46209</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5839,7 +5839,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44503</v>
+        <v>44677</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5868,8 +5868,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5912,7 +5917,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5926,10 +5931,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45656</v>
+        <v>45281</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5942,7 +5947,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5985,7 +5990,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5999,10 +6004,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45131</v>
+        <v>46268</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6015,7 +6020,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6058,7 +6063,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6072,10 +6077,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45282</v>
+        <v>44503</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6088,7 +6093,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6131,7 +6136,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6145,10 +6150,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45750</v>
+        <v>45131</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6161,7 +6166,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6204,7 +6209,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6218,10 +6223,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45400</v>
+        <v>46238</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6234,7 +6239,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6277,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6291,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45133</v>
+        <v>45750</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6307,7 +6312,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6350,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6364,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45644</v>
+        <v>46286</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6380,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6423,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6437,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44700</v>
+        <v>44815</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6453,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6496,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6510,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44677</v>
+        <v>45056</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6525,13 +6530,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44909</v>
+        <v>46254</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,134 +6661,207 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44815</v>
+        <v>46260</v>
       </c>
       <c r="E83" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A 35833-2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>A 42541-2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
         <v>46308</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>A 4954-2024</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="n">
-        <v>45329</v>
-      </c>
-      <c r="E84" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="2" t="inlineStr"/>
+      <c r="E85" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44502</v>
+        <v>45190</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44686</v>
+        <v>44991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1443,13 +1443,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1487,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1501,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45401</v>
+        <v>44502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1517,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1560,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1574,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45317</v>
+        <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1596,11 +1591,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>10.2</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1643,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1657,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45719</v>
+        <v>44727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1672,13 +1667,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1721,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1735,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45715</v>
+        <v>45722</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1750,13 +1740,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1799,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1813,10 +1798,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45719</v>
+        <v>45377</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1828,13 +1813,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1877,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1891,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>44795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1906,13 +1886,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1955,7 +1930,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1969,10 +1944,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45887</v>
+        <v>45322</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1985,7 +1960,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2028,7 +2003,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2042,10 +2017,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45722</v>
+        <v>45322</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2058,7 +2033,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2101,7 +2076,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2115,10 +2090,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45377</v>
+        <v>44784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2131,7 +2106,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2174,7 +2149,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2188,10 +2163,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45898</v>
+        <v>45887</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2204,7 +2179,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2247,7 +2222,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2257,14 +2232,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45282</v>
+        <v>45835</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2277,7 +2252,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2320,7 +2295,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2334,10 +2309,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45919</v>
+        <v>44503</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2350,7 +2325,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2393,7 +2368,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2407,10 +2382,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44909</v>
+        <v>45838</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2423,7 +2398,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2466,7 +2441,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2476,14 +2451,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45835</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2496,7 +2471,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2539,7 +2514,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2553,10 +2528,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45838</v>
+        <v>45715</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2568,8 +2543,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2612,7 +2592,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2626,10 +2606,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45939</v>
+        <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2641,8 +2621,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2685,7 +2670,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2699,10 +2684,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45950</v>
+        <v>45919</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2715,7 +2700,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2758,7 +2743,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2772,10 +2757,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44784</v>
+        <v>44804</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2788,7 +2773,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2831,7 +2816,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2845,10 +2830,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44686</v>
+        <v>46066</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2860,13 +2845,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2909,7 +2889,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2919,14 +2899,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45979</v>
+        <v>45939</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2939,7 +2919,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2982,7 +2962,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2996,10 +2976,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45979</v>
+        <v>46071</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3012,7 +2992,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3055,7 +3035,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3069,10 +3049,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45317</v>
+        <v>44670</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3084,13 +3064,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3133,7 +3108,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3147,10 +3122,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45715</v>
+        <v>45950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3162,13 +3137,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3211,7 +3181,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3221,14 +3191,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44700</v>
+        <v>46087</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3241,7 +3211,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3284,7 +3254,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3298,10 +3268,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46066</v>
+        <v>44503</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3314,7 +3284,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3357,7 +3327,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3371,10 +3341,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44991</v>
+        <v>45656</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3387,7 +3357,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3430,7 +3400,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3444,10 +3414,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46071</v>
+        <v>46097</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3460,7 +3430,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3503,7 +3473,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3517,10 +3487,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45926</v>
+        <v>45281</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3533,7 +3503,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3576,7 +3546,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3590,10 +3560,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45644</v>
+        <v>45317</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3605,8 +3575,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3649,7 +3624,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3663,10 +3638,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46008</v>
+        <v>46106</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3679,7 +3654,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3722,7 +3697,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3732,14 +3707,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46087</v>
+        <v>44931</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3752,7 +3727,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3795,7 +3770,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3809,10 +3784,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46097</v>
+        <v>45351</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3825,7 +3800,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3868,7 +3843,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3882,10 +3857,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44804</v>
+        <v>45542</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3898,7 +3873,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3941,7 +3916,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3951,14 +3926,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46106</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3971,7 +3946,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4014,7 +3989,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4028,10 +4003,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46120</v>
+        <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4044,7 +4019,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4104,7 +4079,7 @@
         <v>46119</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4160,7 +4135,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4174,10 +4149,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44795</v>
+        <v>46120</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4190,7 +4165,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4233,7 +4208,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4247,10 +4222,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45542</v>
+        <v>45926</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4263,7 +4238,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4306,7 +4281,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4320,10 +4295,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45656</v>
+        <v>46008</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4336,7 +4311,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4379,7 +4354,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4393,10 +4368,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44503</v>
+        <v>45545</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4409,7 +4384,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4452,7 +4427,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4466,10 +4441,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44727</v>
+        <v>45887</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4482,7 +4457,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4525,7 +4500,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4539,10 +4514,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45887</v>
+        <v>45719</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4554,8 +4529,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4598,7 +4578,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4612,10 +4592,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45545</v>
+        <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4628,7 +4608,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4671,7 +4651,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4685,10 +4665,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45133</v>
+        <v>45317</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4700,8 +4680,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4744,7 +4729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4758,10 +4743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46147</v>
+        <v>45401</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4774,7 +4759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4817,7 +4802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4831,10 +4816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45007</v>
+        <v>46147</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4847,7 +4832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4890,7 +4875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4904,10 +4889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45329</v>
+        <v>45131</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4920,7 +4905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4963,7 +4948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4977,10 +4962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45600</v>
+        <v>45282</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4993,7 +4978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5036,7 +5021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5050,10 +5035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44670</v>
+        <v>45600</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5066,7 +5051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5109,7 +5094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5123,10 +5108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45351</v>
+        <v>45750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5139,7 +5124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5182,7 +5167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5196,10 +5181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46174</v>
+        <v>45400</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5212,7 +5197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5255,7 +5240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5269,10 +5254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45233</v>
+        <v>45133</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5285,7 +5270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5328,7 +5313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5342,10 +5327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45190</v>
+        <v>46174</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5358,7 +5343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5401,7 +5386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5415,10 +5400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44931</v>
+        <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5431,7 +5416,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5474,7 +5459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5488,10 +5473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46196</v>
+        <v>45644</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5504,7 +5489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5547,7 +5532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5561,10 +5546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45322</v>
+        <v>44700</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5577,7 +5562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5620,7 +5605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5634,10 +5619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45322</v>
+        <v>46209</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5650,7 +5635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5693,7 +5678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5707,10 +5692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45400</v>
+        <v>44677</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5722,8 +5707,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5766,7 +5756,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5780,10 +5770,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46209</v>
+        <v>44909</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5796,7 +5786,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5839,7 +5829,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5853,10 +5843,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44677</v>
+        <v>46268</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5868,13 +5858,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5917,7 +5902,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5931,10 +5916,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45281</v>
+        <v>46238</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5947,7 +5932,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5990,7 +5975,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6004,10 +5989,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6020,7 +6005,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6063,7 +6048,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6077,10 +6062,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44503</v>
+        <v>44815</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6093,7 +6078,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6136,7 +6121,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6150,10 +6135,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45131</v>
+        <v>45329</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6166,7 +6151,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6209,7 +6194,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6223,10 +6208,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46238</v>
+        <v>44686</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6238,8 +6223,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6282,7 +6272,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6296,10 +6286,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45750</v>
+        <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6312,7 +6302,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6355,7 +6345,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6359,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46286</v>
+        <v>46254</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6375,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6418,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6432,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44815</v>
+        <v>46260</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6448,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6491,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6505,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45056</v>
+        <v>46265</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6521,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6564,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6578,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46254</v>
+        <v>45056</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6594,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6637,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6651,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46260</v>
+        <v>45719</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6676,8 +6666,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6715,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6729,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46265</v>
+        <v>45715</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6749,8 +6744,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6810,7 +6810,7 @@
         <v>46308</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44891</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45190</v>
+        <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44991</v>
+        <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1443,8 +1443,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1487,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1501,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44502</v>
+        <v>45722</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1560,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1574,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44686</v>
+        <v>45377</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1589,13 +1594,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44727</v>
+        <v>45401</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45722</v>
+        <v>44795</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45377</v>
+        <v>45835</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44795</v>
+        <v>45838</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45322</v>
+        <v>45542</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2003,7 +2003,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45322</v>
+        <v>45317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2032,8 +2032,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>10.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2076,7 +2081,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2090,10 +2095,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44784</v>
+        <v>45887</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2106,7 +2111,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2149,7 +2154,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45887</v>
+        <v>45446</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2178,8 +2183,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2222,7 +2232,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2232,14 +2242,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45835</v>
+        <v>45656</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2252,7 +2262,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2295,7 +2305,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2312,7 +2322,7 @@
         <v>44503</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2368,7 +2378,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2382,10 +2392,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45838</v>
+        <v>44727</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2398,7 +2408,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2441,7 +2451,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2455,10 +2465,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>45133</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2471,7 +2481,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2514,7 +2524,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2528,10 +2538,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45715</v>
+        <v>45282</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2543,13 +2553,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2592,7 +2597,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2606,10 +2611,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45446</v>
+        <v>44909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2621,13 +2626,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45919</v>
+        <v>45898</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44804</v>
+        <v>46106</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46066</v>
+        <v>46120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45939</v>
+        <v>46119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2962,7 +2962,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46071</v>
+        <v>45007</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44670</v>
+        <v>44784</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45950</v>
+        <v>45329</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46087</v>
+        <v>44686</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3210,8 +3210,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3254,7 +3259,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3268,10 +3273,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44503</v>
+        <v>45317</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3283,8 +3288,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3327,7 +3337,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3341,10 +3351,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45656</v>
+        <v>45715</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3356,8 +3366,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3400,7 +3415,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3414,10 +3429,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46097</v>
+        <v>44670</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3430,7 +3445,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3473,7 +3488,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3487,10 +3502,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45281</v>
+        <v>45887</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3503,7 +3518,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3546,7 +3561,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3560,10 +3575,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45317</v>
+        <v>45545</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3575,13 +3590,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>10.2</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3624,7 +3634,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3638,10 +3648,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46106</v>
+        <v>44700</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3654,7 +3664,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3697,7 +3707,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3711,10 +3721,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44931</v>
+        <v>45351</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3727,7 +3737,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3770,7 +3780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3784,10 +3794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45351</v>
+        <v>44991</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3800,7 +3810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3843,7 +3853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3857,10 +3867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45542</v>
+        <v>45644</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3873,7 +3883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3916,7 +3926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3926,14 +3936,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>46147</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3946,7 +3956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3989,7 +3999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4003,10 +4013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45979</v>
+        <v>45233</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4019,7 +4029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4062,7 +4072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4076,10 +4086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46119</v>
+        <v>45190</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4092,7 +4102,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4135,7 +4145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4149,10 +4159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46120</v>
+        <v>44931</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4165,7 +4175,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4208,7 +4218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4222,10 +4232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45926</v>
+        <v>44804</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4238,7 +4248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4281,7 +4291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4295,10 +4305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46008</v>
+        <v>45600</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4311,7 +4321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4354,7 +4364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4368,10 +4378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45545</v>
+        <v>45919</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4384,7 +4394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4427,7 +4437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4441,10 +4451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45887</v>
+        <v>45322</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4457,7 +4467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4500,7 +4510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4514,10 +4524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45719</v>
+        <v>45322</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4529,13 +4539,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4578,7 +4583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4592,10 +4597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45233</v>
+        <v>46174</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4608,7 +4613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4651,7 +4656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4665,10 +4670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45317</v>
+        <v>45400</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4678,11 +4683,6 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4729,7 +4729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45401</v>
+        <v>44677</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4758,8 +4758,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4802,7 +4807,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4816,10 +4821,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46147</v>
+        <v>45939</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4832,7 +4837,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4875,7 +4880,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4889,10 +4894,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45131</v>
+        <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4905,7 +4910,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4948,7 +4953,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4962,10 +4967,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45282</v>
+        <v>46196</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4978,7 +4983,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5021,7 +5026,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5035,10 +5040,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45600</v>
+        <v>44503</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5051,7 +5056,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5094,7 +5099,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5108,10 +5113,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45750</v>
+        <v>45131</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5124,7 +5129,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5167,7 +5172,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5181,10 +5186,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45400</v>
+        <v>45950</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5197,7 +5202,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5240,7 +5245,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5254,10 +5259,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45133</v>
+        <v>46209</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5270,7 +5275,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5313,7 +5318,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5327,10 +5332,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46174</v>
+        <v>45750</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5343,7 +5348,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5386,7 +5391,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5400,10 +5405,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46196</v>
+        <v>44815</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5416,7 +5421,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5459,7 +5464,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5473,10 +5478,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45644</v>
+        <v>46238</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5489,7 +5494,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5532,7 +5537,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5546,10 +5551,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44700</v>
+        <v>46286</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5562,7 +5567,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5605,7 +5610,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5615,14 +5620,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46209</v>
+        <v>45979</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5635,7 +5640,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5678,7 +5683,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5692,10 +5697,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44677</v>
+        <v>45979</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5707,13 +5712,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5756,7 +5756,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44909</v>
+        <v>45056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5829,7 +5829,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46268</v>
+        <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46238</v>
+        <v>46008</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5975,7 +5975,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5989,10 +5989,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46286</v>
+        <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6048,7 +6048,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44815</v>
+        <v>45719</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6077,8 +6077,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6121,7 +6126,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6135,10 +6140,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45329</v>
+        <v>45715</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6148,6 +6153,11 @@
       <c r="G76" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -6194,7 +6204,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6208,10 +6218,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44686</v>
+        <v>45719</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6225,11 +6235,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6272,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6286,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45007</v>
+        <v>46260</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6302,7 +6312,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6345,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 42541-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6359,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46254</v>
+        <v>46308</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6375,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6418,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6432,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46260</v>
+        <v>46268</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6448,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6491,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6505,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46265</v>
+        <v>46066</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6521,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>7.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6564,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6578,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45056</v>
+        <v>46071</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6594,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6637,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6651,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45719</v>
+        <v>46265</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6666,13 +6676,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6715,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6725,14 +6730,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45715</v>
+        <v>46087</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6744,13 +6749,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42541-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46308</v>
+        <v>46097</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,259 +647,259 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 40387-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 40387-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Röd glada</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45722</v>
+        <v>44727</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45377</v>
+        <v>44784</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45401</v>
+        <v>45322</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44795</v>
+        <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45835</v>
+        <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45838</v>
+        <v>45715</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1886,8 +1886,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1930,7 +1935,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45542</v>
+        <v>45446</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1959,8 +1964,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2003,7 +2013,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2017,10 +2027,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45317</v>
+        <v>44670</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2032,13 +2042,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2081,7 +2086,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2095,10 +2100,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45887</v>
+        <v>45281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2111,7 +2116,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2154,7 +2159,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45446</v>
+        <v>45317</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2185,11 +2190,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>10.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2232,7 +2237,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2246,10 +2251,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45656</v>
+        <v>44931</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2262,7 +2267,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2305,7 +2310,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2319,10 +2324,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44503</v>
+        <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2335,7 +2340,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2378,7 +2383,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2392,10 +2397,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44727</v>
+        <v>45542</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2408,7 +2413,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8.6</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2451,7 +2456,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2465,10 +2470,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45133</v>
+        <v>45887</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2481,7 +2486,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2524,7 +2529,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45282</v>
+        <v>45233</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2554,7 +2559,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2597,7 +2602,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44909</v>
+        <v>45317</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2626,8 +2631,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2687,7 +2697,7 @@
         <v>45898</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2743,7 +2753,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2757,10 +2767,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46106</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2773,7 +2783,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2816,7 +2826,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2830,10 +2840,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46120</v>
+        <v>46147</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2846,7 +2856,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2889,7 +2899,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2903,10 +2913,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46119</v>
+        <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2919,7 +2929,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2962,7 +2972,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2976,10 +2986,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45007</v>
+        <v>45190</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3035,7 +3045,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3049,10 +3059,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44784</v>
+        <v>44991</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3065,7 +3075,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3108,7 +3118,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3122,10 +3132,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45329</v>
+        <v>45939</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3138,7 +3148,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3181,7 +3191,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3195,10 +3205,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44686</v>
+        <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3210,13 +3220,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3259,7 +3264,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45317</v>
+        <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3288,13 +3293,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45715</v>
+        <v>45600</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,13 +3366,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3415,7 +3410,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3429,10 +3424,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44670</v>
+        <v>44804</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3445,7 +3440,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3488,7 +3483,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3498,14 +3493,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45887</v>
+        <v>45979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3518,7 +3513,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3561,7 +3556,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3575,10 +3570,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45545</v>
+        <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3591,7 +3586,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3634,7 +3629,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3648,10 +3643,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44700</v>
+        <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3664,7 +3659,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3707,7 +3702,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45351</v>
+        <v>45656</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3737,7 +3732,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3780,7 +3775,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3794,10 +3789,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44991</v>
+        <v>45926</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3810,7 +3805,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3853,7 +3848,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3867,10 +3862,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45644</v>
+        <v>46174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3883,7 +3878,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3926,7 +3921,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3940,10 +3935,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46147</v>
+        <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3956,7 +3951,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3999,7 +3994,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4013,10 +4008,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45233</v>
+        <v>45131</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4029,7 +4024,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4072,7 +4067,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4086,10 +4081,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45190</v>
+        <v>45282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4102,7 +4097,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4145,7 +4140,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4159,10 +4154,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44931</v>
+        <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4174,8 +4169,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44804</v>
+        <v>45750</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4291,7 +4291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45600</v>
+        <v>45400</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45919</v>
+        <v>45133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4437,7 +4437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45322</v>
+        <v>46066</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4510,7 +4510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45322</v>
+        <v>46071</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4583,7 +4583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46174</v>
+        <v>46087</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4656,7 +4656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45400</v>
+        <v>46097</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4729,7 +4729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44677</v>
+        <v>46106</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4758,13 +4758,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4807,7 +4802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4821,10 +4816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45939</v>
+        <v>46196</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4837,7 +4832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4880,7 +4875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4894,10 +4889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45281</v>
+        <v>45644</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4910,7 +4905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4953,7 +4948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4967,10 +4962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46196</v>
+        <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4983,7 +4978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5026,7 +5021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5040,10 +5035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44503</v>
+        <v>46120</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5056,7 +5051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5099,7 +5094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5113,10 +5108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45131</v>
+        <v>44700</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5129,7 +5124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5172,7 +5167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5186,10 +5181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45950</v>
+        <v>44677</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5201,8 +5196,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5245,7 +5245,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46209</v>
+        <v>44909</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5318,7 +5318,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45750</v>
+        <v>45545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5391,7 +5391,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44815</v>
+        <v>45887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5464,7 +5464,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46238</v>
+        <v>46209</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5537,7 +5537,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46286</v>
+        <v>44815</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5620,14 +5620,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45979</v>
+        <v>45329</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45979</v>
+        <v>46238</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5756,7 +5756,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45056</v>
+        <v>44686</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5785,8 +5785,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5829,7 +5834,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5843,10 +5848,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45926</v>
+        <v>46286</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5859,7 +5864,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5902,7 +5907,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5916,10 +5921,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46008</v>
+        <v>45007</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5932,7 +5937,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5992,7 +5997,7 @@
         <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6048,7 +6053,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6062,10 +6067,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45719</v>
+        <v>45056</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6077,13 +6082,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45715</v>
+        <v>46260</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6155,13 +6155,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6204,7 +6199,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6221,7 +6216,7 @@
         <v>45719</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6239,7 +6234,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6282,7 +6277,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6296,10 +6291,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46260</v>
+        <v>45715</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6311,8 +6306,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6355,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42541-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46308</v>
+        <v>46265</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 42541-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46268</v>
+        <v>46308</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46066</v>
+        <v>45722</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46071</v>
+        <v>45377</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6730,14 +6730,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46087</v>
+        <v>45835</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46097</v>
+        <v>45838</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>46294</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44727</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>44784</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45322</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45715</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45446</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>44670</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>45281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>45317</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>44931</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45542</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45887</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45233</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45317</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45898</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>46147</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45190</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44991</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45939</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45600</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44804</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45656</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45926</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>46174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45131</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45750</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45400</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>45133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>46066</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>46071</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>46087</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>46097</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>46106</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>46196</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45644</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>46120</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>44700</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44677</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44909</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>45545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>45887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46209</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44815</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>45329</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>46238</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44686</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>46286</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45007</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45056</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>46260</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45719</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45715</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>46265</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>46308</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45722</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45377</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46268</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45835</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45838</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>46294</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44727</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>44784</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45322</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45715</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45446</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>44670</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>45281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>45317</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>44931</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45542</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45887</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45233</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45317</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45898</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>46147</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45190</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44991</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45939</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45600</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44804</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45656</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45926</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>46174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45131</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45750</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45400</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>45133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>46066</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>46071</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>46087</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>46097</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>46106</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>46196</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45644</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>46120</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>44700</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44677</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44909</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>45545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>45887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46209</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44815</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>45329</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>46238</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44686</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>46286</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45007</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45056</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>46260</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45719</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45715</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>46265</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>46308</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45722</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45377</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46268</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45835</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45838</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>46294</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>45320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44727</v>
+        <v>45401</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44784</v>
+        <v>45317</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1594,8 +1594,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>10.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1643,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1657,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45322</v>
+        <v>45446</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1667,8 +1672,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1721,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1735,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45322</v>
+        <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1751,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1794,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1798,10 +1808,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44503</v>
+        <v>45282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1814,7 +1824,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1857,7 +1867,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1881,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45715</v>
+        <v>44784</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1886,13 +1896,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1935,7 +1940,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45446</v>
+        <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1970,7 +1975,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2013,7 +2018,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2027,10 +2032,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44670</v>
+        <v>45317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2042,8 +2047,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2086,7 +2096,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2100,10 +2110,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45281</v>
+        <v>45715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2115,8 +2125,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2159,7 +2174,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2173,10 +2188,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45317</v>
+        <v>44700</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2188,13 +2203,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2237,7 +2247,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2251,10 +2261,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44931</v>
+        <v>44991</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2267,7 +2277,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2310,7 +2320,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2324,10 +2334,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45351</v>
+        <v>45887</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2340,7 +2350,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2383,7 +2393,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2397,10 +2407,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45542</v>
+        <v>45545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2413,7 +2423,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2456,7 +2466,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2470,10 +2480,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45887</v>
+        <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2486,7 +2496,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2529,7 +2539,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2543,10 +2553,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45233</v>
+        <v>45887</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2559,7 +2569,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2602,7 +2612,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2616,10 +2626,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45317</v>
+        <v>45898</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2631,13 +2641,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2680,7 +2685,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2694,10 +2699,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45898</v>
+        <v>44804</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2710,7 +2715,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2770,7 +2775,7 @@
         <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2826,7 +2831,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46147</v>
+        <v>44795</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2856,7 +2861,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2899,7 +2904,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2913,10 +2918,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45401</v>
+        <v>45939</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2929,7 +2934,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2972,7 +2977,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45190</v>
+        <v>45950</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3002,7 +3007,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3045,7 +3050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3059,10 +3064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44991</v>
+        <v>46147</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3075,7 +3080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3118,7 +3123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3132,10 +3137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45939</v>
+        <v>45542</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3148,7 +3153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3191,7 +3196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3205,10 +3210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44795</v>
+        <v>45656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3221,7 +3226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3264,7 +3269,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3278,10 +3283,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45950</v>
+        <v>44503</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3294,7 +3299,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3337,7 +3342,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3351,10 +3356,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45600</v>
+        <v>44727</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3367,7 +3372,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3410,7 +3415,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3424,10 +3429,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44804</v>
+        <v>45600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3440,7 +3445,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3500,7 +3505,7 @@
         <v>45979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3573,7 +3578,7 @@
         <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3629,7 +3634,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3643,10 +3648,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44503</v>
+        <v>45133</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3659,7 +3664,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3702,7 +3707,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45656</v>
+        <v>45926</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3732,7 +3737,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3775,7 +3780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3789,10 +3794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45926</v>
+        <v>46008</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3805,7 +3810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3848,7 +3853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3862,10 +3867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46174</v>
+        <v>45719</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3877,8 +3882,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3921,7 +3931,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3935,10 +3945,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46008</v>
+        <v>45007</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3951,7 +3961,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3994,7 +4004,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4008,10 +4018,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45131</v>
+        <v>46174</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4024,7 +4034,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4067,7 +4077,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4081,10 +4091,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45282</v>
+        <v>45329</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4097,7 +4107,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4140,7 +4150,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4154,10 +4164,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45719</v>
+        <v>44670</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4169,13 +4179,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4218,7 +4223,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4232,10 +4237,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45750</v>
+        <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4248,7 +4253,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4291,7 +4296,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4305,10 +4310,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45400</v>
+        <v>46066</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4321,7 +4326,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4364,7 +4369,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4378,10 +4383,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45133</v>
+        <v>46071</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4394,7 +4399,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4437,7 +4442,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4447,14 +4452,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4467,7 +4472,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4510,7 +4515,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4524,10 +4529,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46071</v>
+        <v>46097</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4540,7 +4545,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4583,7 +4588,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4593,14 +4598,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46087</v>
+        <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4613,7 +4618,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4656,7 +4661,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4670,10 +4675,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46097</v>
+        <v>45190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4686,7 +4691,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4729,7 +4734,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4743,10 +4748,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46106</v>
+        <v>44931</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4759,7 +4764,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4802,7 +4807,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4816,10 +4821,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46196</v>
+        <v>46106</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4832,7 +4837,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4875,7 +4880,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4889,10 +4894,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45644</v>
+        <v>46196</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4905,7 +4910,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4948,7 +4953,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4962,10 +4967,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4978,7 +4983,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5021,7 +5026,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5035,10 +5040,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5051,7 +5056,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5094,7 +5099,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5108,10 +5113,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44700</v>
+        <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5124,7 +5129,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5167,7 +5172,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5181,10 +5186,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44677</v>
+        <v>45322</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5196,13 +5201,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5245,7 +5245,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44909</v>
+        <v>45400</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5318,7 +5318,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45545</v>
+        <v>46209</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5391,7 +5391,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45887</v>
+        <v>44677</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5420,8 +5420,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5464,7 +5469,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46209</v>
+        <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5494,7 +5499,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5537,7 +5542,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5551,10 +5556,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44815</v>
+        <v>44503</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5567,7 +5572,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5610,7 +5615,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5624,10 +5629,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45329</v>
+        <v>45131</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5640,7 +5645,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5700,7 +5705,7 @@
         <v>46238</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5756,7 +5761,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5770,10 +5775,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44686</v>
+        <v>46286</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5785,13 +5790,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46286</v>
+        <v>45750</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45007</v>
+        <v>44815</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45056</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46260</v>
+        <v>45719</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6155,8 +6155,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6199,7 +6204,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6213,10 +6218,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45719</v>
+        <v>45715</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6277,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6291,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45715</v>
+        <v>46260</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6306,13 +6311,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6355,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46265</v>
+        <v>45722</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42541-2026</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46308</v>
+        <v>45377</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 42541-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45722</v>
+        <v>46308</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45377</v>
+        <v>46265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6657,14 +6657,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46268</v>
+        <v>45835</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6730,14 +6730,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45838</v>
+        <v>46268</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,259 +647,259 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 40387-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E4" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2.5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Röd glada</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45401</v>
+        <v>44727</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45317</v>
+        <v>44784</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1594,13 +1594,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1643,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1657,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45446</v>
+        <v>45322</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1672,13 +1667,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1721,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1735,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44909</v>
+        <v>45322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1751,7 +1741,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1794,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1808,10 +1798,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45282</v>
+        <v>44503</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1824,7 +1814,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1867,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1881,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44784</v>
+        <v>45715</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,8 +1886,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1940,7 +1935,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44686</v>
+        <v>45719</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1971,11 +1966,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2018,7 +2013,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2032,10 +2027,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45317</v>
+        <v>45715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2053,7 +2048,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2096,7 +2091,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2110,10 +2105,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45715</v>
+        <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2125,13 +2120,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2174,7 +2164,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2188,10 +2178,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44700</v>
+        <v>45887</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2204,7 +2194,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2247,7 +2237,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2261,10 +2251,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44991</v>
+        <v>46008</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2277,7 +2267,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2320,7 +2310,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2334,10 +2324,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45887</v>
+        <v>45446</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2349,8 +2339,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2393,7 +2388,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2407,10 +2402,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45545</v>
+        <v>45719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2422,8 +2417,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45644</v>
+        <v>45722</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45887</v>
+        <v>45377</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2629,7 +2629,7 @@
         <v>45898</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44804</v>
+        <v>45919</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>44670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2831,7 +2831,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44795</v>
+        <v>46066</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45939</v>
+        <v>46071</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2977,7 +2977,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45950</v>
+        <v>45939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46147</v>
+        <v>45281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45542</v>
+        <v>45317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3152,8 +3152,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>10.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3196,7 +3201,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,14 +3211,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45656</v>
+        <v>46087</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3226,7 +3231,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3269,7 +3274,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3283,10 +3288,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44503</v>
+        <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3299,7 +3304,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3342,7 +3347,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3356,10 +3361,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44727</v>
+        <v>44931</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3372,7 +3377,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.6</v>
+        <v>0.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45600</v>
+        <v>45351</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3488,7 +3493,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3498,14 +3503,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45979</v>
+        <v>45542</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3518,7 +3523,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3561,7 +3566,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3575,10 +3580,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45979</v>
+        <v>46097</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3591,7 +3596,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3634,7 +3639,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3648,10 +3653,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45133</v>
+        <v>46106</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3664,7 +3669,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3707,7 +3712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3717,14 +3722,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45926</v>
+        <v>45835</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3737,7 +3742,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3780,7 +3785,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3794,10 +3799,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46008</v>
+        <v>46119</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3810,7 +3815,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3853,7 +3858,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3867,10 +3872,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45719</v>
+        <v>46120</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3882,13 +3887,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45007</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4004,7 +4004,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46174</v>
+        <v>45838</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45329</v>
+        <v>45979</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44670</v>
+        <v>45545</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4223,7 +4223,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45351</v>
+        <v>45887</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4296,7 +4296,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46066</v>
+        <v>45233</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4369,7 +4369,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46071</v>
+        <v>45317</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4398,8 +4398,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4442,7 +4447,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4452,14 +4457,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46087</v>
+        <v>45401</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4472,7 +4477,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4515,7 +4520,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4529,10 +4534,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46097</v>
+        <v>45190</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4545,7 +4550,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4588,7 +4593,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4602,10 +4607,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45233</v>
+        <v>44991</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4618,7 +4623,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4661,7 +4666,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4675,10 +4680,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45190</v>
+        <v>46147</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4691,7 +4696,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4734,7 +4739,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4748,10 +4753,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44931</v>
+        <v>44795</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4764,7 +4769,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4807,7 +4812,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4821,10 +4826,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46106</v>
+        <v>45600</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4837,7 +4842,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4880,7 +4885,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4894,10 +4899,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46196</v>
+        <v>44804</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4910,7 +4915,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4953,7 +4958,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4967,10 +4972,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46120</v>
+        <v>44503</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4983,7 +4988,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5026,7 +5031,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5040,10 +5045,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46119</v>
+        <v>45656</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5056,7 +5061,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5099,7 +5104,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5113,10 +5118,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45322</v>
+        <v>46174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5129,7 +5134,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5172,7 +5177,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5186,10 +5191,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45322</v>
+        <v>45131</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5202,7 +5207,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5245,7 +5250,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5259,10 +5264,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45400</v>
+        <v>45282</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5275,7 +5280,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5318,7 +5323,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5332,10 +5337,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46209</v>
+        <v>45750</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5348,7 +5353,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5391,7 +5396,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5405,10 +5410,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44677</v>
+        <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5420,13 +5425,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45281</v>
+        <v>45400</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44503</v>
+        <v>45133</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45131</v>
+        <v>46209</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>46238</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46286</v>
+        <v>45644</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45750</v>
+        <v>46286</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44815</v>
+        <v>44700</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46254</v>
+        <v>44677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6009,8 +6009,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6053,7 +6058,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6067,10 +6072,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45056</v>
+        <v>44909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6083,7 +6088,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6126,7 +6131,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6140,10 +6145,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45719</v>
+        <v>46254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6155,13 +6160,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6204,7 +6204,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6218,10 +6218,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45715</v>
+        <v>44815</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6233,13 +6233,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6299,7 +6294,7 @@
         <v>46260</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6350,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6364,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45722</v>
+        <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6380,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6423,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6437,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45377</v>
+        <v>46265</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6453,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6496,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42541-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6510,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46308</v>
+        <v>44686</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6530,8 +6525,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 42541-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46265</v>
+        <v>46308</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6657,14 +6657,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45835</v>
+        <v>46268</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45838</v>
+        <v>45007</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46268</v>
+        <v>45056</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44727</v>
+        <v>45401</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44784</v>
+        <v>46008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45322</v>
+        <v>45719</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1667,8 +1667,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1716,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1730,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45322</v>
+        <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1740,8 +1745,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1794,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1798,10 +1808,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44503</v>
+        <v>45317</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1813,8 +1823,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1857,7 +1872,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1886,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45715</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1888,11 +1903,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1935,7 +1950,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,10 +1964,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45719</v>
+        <v>45887</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1962,11 +1977,6 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -2013,7 +2023,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2027,10 +2037,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45715</v>
+        <v>45719</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2048,7 +2058,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2091,7 +2101,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2105,10 +2115,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45926</v>
+        <v>45898</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2121,7 +2131,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2164,7 +2174,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2178,10 +2188,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45887</v>
+        <v>45722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2194,7 +2204,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2237,7 +2247,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2251,10 +2261,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46008</v>
+        <v>45377</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2267,7 +2277,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2310,7 +2320,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2324,10 +2334,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45446</v>
+        <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2339,13 +2349,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2388,7 +2393,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2402,10 +2407,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45719</v>
+        <v>45282</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2417,13 +2422,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45722</v>
+        <v>44909</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2549,14 +2549,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45377</v>
+        <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45898</v>
+        <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2685,7 +2685,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45919</v>
+        <v>45939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44670</v>
+        <v>45950</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2831,7 +2831,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46066</v>
+        <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46071</v>
+        <v>44686</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2933,8 +2933,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2977,7 +2982,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2991,10 +2996,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45939</v>
+        <v>45317</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3006,8 +3011,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3050,7 +3060,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3064,10 +3074,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45281</v>
+        <v>45715</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3079,8 +3089,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3123,7 +3138,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3133,14 +3148,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45317</v>
+        <v>45979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3152,13 +3167,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>10.2</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3201,7 +3211,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3211,14 +3221,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46087</v>
+        <v>45979</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3231,7 +3241,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3274,7 +3284,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3288,10 +3298,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45950</v>
+        <v>44700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3304,7 +3314,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3347,7 +3357,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3361,10 +3371,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44931</v>
+        <v>44991</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3377,7 +3387,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3420,7 +3430,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3434,10 +3444,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45351</v>
+        <v>45644</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3450,7 +3460,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3493,7 +3503,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3507,10 +3517,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45542</v>
+        <v>45926</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3523,7 +3533,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3566,7 +3576,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3580,10 +3590,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46097</v>
+        <v>46066</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3596,7 +3606,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3639,7 +3649,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3653,10 +3663,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46106</v>
+        <v>46071</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3712,7 +3722,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3722,14 +3732,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45835</v>
+        <v>44804</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3742,7 +3752,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3785,7 +3795,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3795,14 +3805,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46119</v>
+        <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3815,7 +3825,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3858,7 +3868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3872,10 +3882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46120</v>
+        <v>46097</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3888,7 +3898,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3931,7 +3941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3941,14 +3951,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>44795</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3961,7 +3971,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4004,7 +4014,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4018,10 +4028,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45838</v>
+        <v>46106</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4034,7 +4044,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4077,7 +4087,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4091,10 +4101,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45979</v>
+        <v>46120</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4107,7 +4117,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4150,7 +4160,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4164,10 +4174,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45545</v>
+        <v>46119</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4180,7 +4190,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4223,7 +4233,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4237,10 +4247,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45887</v>
+        <v>45542</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4253,7 +4263,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4296,7 +4306,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4310,10 +4320,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45233</v>
+        <v>45656</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4326,7 +4336,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4369,7 +4379,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4383,10 +4393,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45317</v>
+        <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4398,13 +4408,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4447,7 +4452,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4461,10 +4466,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45401</v>
+        <v>44727</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4477,7 +4482,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4520,7 +4525,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4534,10 +4539,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45190</v>
+        <v>45133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4550,7 +4555,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4593,7 +4598,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4607,10 +4612,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44991</v>
+        <v>45887</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4623,7 +4628,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4666,7 +4671,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4680,10 +4685,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46147</v>
+        <v>45545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4696,7 +4701,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4739,7 +4744,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4753,10 +4758,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44795</v>
+        <v>45007</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4769,7 +4774,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4812,7 +4817,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4826,10 +4831,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45600</v>
+        <v>46147</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4842,7 +4847,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4885,7 +4890,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4899,10 +4904,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44804</v>
+        <v>45329</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4915,7 +4920,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4958,7 +4963,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4972,10 +4977,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44503</v>
+        <v>44670</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4988,7 +4993,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5031,7 +5036,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5045,10 +5050,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45656</v>
+        <v>45600</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5061,7 +5066,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5104,7 +5109,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5118,10 +5123,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46174</v>
+        <v>45351</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5134,7 +5139,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5177,7 +5182,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5191,10 +5196,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45131</v>
+        <v>46174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5207,7 +5212,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5250,7 +5255,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5264,10 +5269,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45282</v>
+        <v>45233</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5280,7 +5285,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5323,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5337,10 +5342,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45750</v>
+        <v>45190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5353,7 +5358,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5396,7 +5401,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5410,10 +5415,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46196</v>
+        <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5426,7 +5431,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5469,7 +5474,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5483,10 +5488,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45400</v>
+        <v>46196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5499,7 +5504,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5542,7 +5547,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5556,10 +5561,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45133</v>
+        <v>45322</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5572,7 +5577,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5615,7 +5620,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5629,10 +5634,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46209</v>
+        <v>45322</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5645,7 +5650,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5688,7 +5693,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5702,10 +5707,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46238</v>
+        <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5718,7 +5723,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5761,7 +5766,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5775,10 +5780,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45644</v>
+        <v>46209</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5791,7 +5796,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5834,7 +5839,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5848,10 +5853,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46286</v>
+        <v>44677</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5863,8 +5868,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5907,7 +5917,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5921,10 +5931,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44700</v>
+        <v>45281</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5937,7 +5947,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5980,7 +5990,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5994,10 +6004,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44677</v>
+        <v>44503</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6009,13 +6019,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>8</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6058,7 +6063,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6072,10 +6077,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44909</v>
+        <v>45131</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6088,7 +6093,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6131,7 +6136,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6145,10 +6150,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46254</v>
+        <v>46238</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6161,7 +6166,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6204,7 +6209,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6218,10 +6223,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44815</v>
+        <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6234,7 +6239,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6277,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6291,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46260</v>
+        <v>45750</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6307,7 +6312,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6350,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6364,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45329</v>
+        <v>44815</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6380,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6423,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6437,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6453,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6496,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6510,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44686</v>
+        <v>45056</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6525,13 +6530,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42541-2026</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46308</v>
+        <v>46260</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 42541-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46268</v>
+        <v>46308</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45007</v>
+        <v>46265</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45056</v>
+        <v>46268</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44686</v>
+        <v>44502</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1341,7 +1341,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44502</v>
+        <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44686</v>
+        <v>45322</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1443,13 +1443,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1487,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1501,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45401</v>
+        <v>44784</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1517,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1560,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1574,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46008</v>
+        <v>44686</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1595,7 +1590,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1638,7 +1633,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1652,10 +1647,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45719</v>
+        <v>44686</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1669,11 +1664,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1716,7 +1711,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1730,10 +1725,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45715</v>
+        <v>45133</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,13 +1740,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1794,7 +1784,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1808,10 +1798,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45317</v>
+        <v>44727</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1823,13 +1813,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>10.2</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1872,7 +1857,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1886,10 +1871,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45722</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1901,13 +1886,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1950,7 +1930,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1964,10 +1944,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45887</v>
+        <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1980,7 +1960,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2023,7 +2003,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2037,10 +2017,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45719</v>
+        <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2052,13 +2032,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2101,7 +2076,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2115,10 +2090,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45898</v>
+        <v>45887</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2131,7 +2106,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2174,7 +2149,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2184,14 +2159,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45722</v>
+        <v>45835</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2204,7 +2179,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2247,7 +2222,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2261,10 +2236,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45377</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2277,7 +2252,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2320,7 +2295,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2334,10 +2309,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45919</v>
+        <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2350,7 +2325,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2393,7 +2368,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2407,10 +2382,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45282</v>
+        <v>45715</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2422,8 +2397,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2466,7 +2446,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2480,10 +2460,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44909</v>
+        <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2496,7 +2476,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2539,7 +2519,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2549,14 +2529,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45835</v>
+        <v>44700</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2569,7 +2549,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2612,7 +2592,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2626,10 +2606,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45838</v>
+        <v>44677</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2641,8 +2621,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2685,7 +2670,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2699,10 +2684,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45939</v>
+        <v>44909</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2715,7 +2700,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2758,7 +2743,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2772,10 +2757,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45950</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2788,7 +2773,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2831,7 +2816,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2845,10 +2830,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44784</v>
+        <v>45545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2861,7 +2846,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2904,7 +2889,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2918,10 +2903,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44686</v>
+        <v>45887</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2933,13 +2918,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2982,7 +2962,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2996,10 +2976,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45317</v>
+        <v>45939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3011,13 +2991,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3060,7 +3035,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3074,10 +3049,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45715</v>
+        <v>45446</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3091,11 +3066,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3138,7 +3113,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3148,14 +3123,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45979</v>
+        <v>45950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3168,7 +3143,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3211,7 +3186,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3225,10 +3200,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45979</v>
+        <v>44815</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3241,7 +3216,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3284,7 +3259,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3298,10 +3273,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44700</v>
+        <v>45329</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3314,7 +3289,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3357,7 +3332,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3367,14 +3342,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44991</v>
+        <v>45979</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3387,7 +3362,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3430,7 +3405,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3444,10 +3419,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45644</v>
+        <v>45979</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3460,7 +3435,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3503,7 +3478,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3517,10 +3492,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45926</v>
+        <v>46147</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3533,7 +3508,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3576,7 +3551,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3590,10 +3565,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46066</v>
+        <v>44686</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3605,8 +3580,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3649,7 +3629,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3663,10 +3643,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46071</v>
+        <v>45007</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3679,7 +3659,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3722,7 +3702,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3736,10 +3716,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44804</v>
+        <v>45600</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3752,7 +3732,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3795,7 +3775,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3805,14 +3785,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46087</v>
+        <v>45926</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3825,7 +3805,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3868,7 +3848,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3882,10 +3862,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46097</v>
+        <v>46008</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3898,7 +3878,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3941,7 +3921,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3955,10 +3935,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44795</v>
+        <v>45719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3970,8 +3950,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4014,7 +3999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4028,10 +4013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46106</v>
+        <v>46174</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4044,7 +4029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4087,7 +4072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4101,10 +4086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46120</v>
+        <v>44670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4117,7 +4102,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4160,7 +4145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4174,10 +4159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46119</v>
+        <v>46066</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4190,7 +4175,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4233,7 +4218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4247,10 +4232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45542</v>
+        <v>45056</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4263,7 +4248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4306,7 +4291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4320,10 +4305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45656</v>
+        <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4336,7 +4321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4379,7 +4364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4393,10 +4378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44503</v>
+        <v>45719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4406,6 +4391,11 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4452,7 +4442,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4466,10 +4456,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44727</v>
+        <v>45715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4481,8 +4471,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4525,7 +4520,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4535,14 +4530,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45133</v>
+        <v>46087</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4555,7 +4550,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4598,7 +4593,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4612,10 +4607,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45887</v>
+        <v>46196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4628,7 +4623,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4671,7 +4666,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4685,10 +4680,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45545</v>
+        <v>46268</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4701,7 +4696,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4744,7 +4739,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4758,10 +4753,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45007</v>
+        <v>46097</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4774,7 +4769,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4817,7 +4812,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4831,10 +4826,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46147</v>
+        <v>46106</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4847,7 +4842,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4890,7 +4885,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4904,10 +4899,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45329</v>
+        <v>46119</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4920,7 +4915,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4963,7 +4958,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4977,10 +4972,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44670</v>
+        <v>46120</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4993,7 +4988,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5036,7 +5031,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5050,10 +5045,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45600</v>
+        <v>45281</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5066,7 +5061,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5109,7 +5104,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5123,10 +5118,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45351</v>
+        <v>45317</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5138,8 +5133,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>10.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46174</v>
+        <v>46209</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45233</v>
+        <v>44931</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45190</v>
+        <v>45351</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44931</v>
+        <v>45542</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46196</v>
+        <v>46238</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45322</v>
+        <v>46286</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5620,7 +5620,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45322</v>
+        <v>45233</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15306-2024</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45400</v>
+        <v>45317</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5720,6 +5720,11 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -5766,7 +5771,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5780,10 +5785,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46209</v>
+        <v>45401</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5796,7 +5801,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5839,7 +5844,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5853,10 +5858,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44677</v>
+        <v>46254</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5868,13 +5873,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5917,7 +5917,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45281</v>
+        <v>45190</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44503</v>
+        <v>44991</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6063,7 +6063,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6077,10 +6077,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45131</v>
+        <v>44795</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6136,7 +6136,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46238</v>
+        <v>46260</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6209,7 +6209,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46286</v>
+        <v>44804</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6296,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45750</v>
+        <v>44503</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6355,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44815</v>
+        <v>45656</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 42541-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45056</v>
+        <v>46308</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46260</v>
+        <v>45131</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42541-2026</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46308</v>
+        <v>45282</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46265</v>
+        <v>45750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 15306-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46268</v>
+        <v>45400</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE85"/>
+  <dimension ref="A1:AE86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3563-2024</t>
+          <t>A 56429-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45320</v>
+        <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,150 +647,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 3563-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45320</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56429-2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>44891</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 62710-2021</t>
+          <t>A 18394-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44502</v>
+        <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1341,7 +1341,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 3867-2024</t>
+          <t>A 62710-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45322</v>
+        <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 3868-2024</t>
+          <t>A 18510-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45322</v>
+        <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1443,8 +1443,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1487,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32914-2022</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1501,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44784</v>
+        <v>45887</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1517,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1560,7 +1565,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18394-2022</t>
+          <t>A 17072-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1574,10 +1579,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44686</v>
+        <v>44677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1589,8 +1594,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1633,7 +1643,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18510-2022</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1647,10 +1657,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44686</v>
+        <v>45401</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1662,13 +1672,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1711,7 +1716,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33817-2023</t>
+          <t>A 41022-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1725,10 +1730,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45133</v>
+        <v>45898</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1741,7 +1746,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1784,7 +1789,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24686-2022</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44727</v>
+        <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1814,7 +1819,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1857,7 +1862,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1871,10 +1876,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45722</v>
+        <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1887,7 +1892,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1930,7 +1935,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>44503</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1960,7 +1965,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2003,7 +2008,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 33510-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2017,10 +2022,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44503</v>
+        <v>45131</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2033,7 +2038,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2076,7 +2081,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2090,10 +2095,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45887</v>
+        <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2106,7 +2111,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2149,7 +2154,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 24876-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2159,14 +2164,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45835</v>
+        <v>46174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2179,7 +2184,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2222,7 +2227,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2236,10 +2241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>45950</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2252,7 +2257,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2295,7 +2300,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60768-2024</t>
+          <t>A 16145-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2309,10 +2314,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>45750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2325,7 +2330,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2368,7 +2373,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9375-2025</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2382,10 +2387,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45715</v>
+        <v>45317</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2403,7 +2408,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>10.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2446,7 +2451,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41022-2025</t>
+          <t>A 38715-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2460,10 +2465,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45898</v>
+        <v>44815</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2476,7 +2481,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2519,7 +2524,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20555-2022</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2533,10 +2538,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44700</v>
+        <v>46196</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2549,7 +2554,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2592,7 +2597,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 57160-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2602,14 +2607,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44677</v>
+        <v>45979</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2621,13 +2626,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44909</v>
+        <v>45979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>46209</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 38243-2024</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45545</v>
+        <v>45446</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2845,8 +2845,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2889,7 +2894,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38800-2025</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2903,10 +2908,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45887</v>
+        <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2919,7 +2924,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2962,7 +2967,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45939</v>
+        <v>46008</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2992,7 +2997,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3035,7 +3040,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45446</v>
+        <v>45056</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3064,13 +3069,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45950</v>
+        <v>45719</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3142,8 +3142,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3186,7 +3191,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 32414-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3200,10 +3205,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44815</v>
+        <v>46238</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3216,7 +3221,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3259,7 +3264,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4954-2024</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45329</v>
+        <v>45719</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3286,6 +3291,11 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -3332,7 +3342,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57160-2025</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3342,14 +3352,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45979</v>
+        <v>45715</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3361,8 +3371,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3405,7 +3420,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 38806-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3419,10 +3434,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45979</v>
+        <v>46286</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3435,7 +3450,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3478,7 +3493,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21294-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3492,10 +3507,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46147</v>
+        <v>45722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3508,7 +3523,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3551,7 +3566,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18499-2022</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3565,10 +3580,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44686</v>
+        <v>45377</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3580,13 +3595,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3629,7 +3639,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13876-2023</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3643,10 +3653,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45007</v>
+        <v>46066</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3659,7 +3669,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3702,7 +3712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50364-2024</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3716,10 +3726,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45600</v>
+        <v>46071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3732,7 +3742,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3775,7 +3785,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3785,14 +3795,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45926</v>
+        <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3805,7 +3815,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3848,7 +3858,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3858,14 +3868,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46008</v>
+        <v>45835</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3878,7 +3888,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3921,7 +3931,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3935,10 +3945,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45719</v>
+        <v>45838</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3950,13 +3960,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3999,7 +4004,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 34360-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4013,10 +4018,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46174</v>
+        <v>46254</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4029,7 +4034,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4072,7 +4077,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16248-2022</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4086,10 +4091,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44670</v>
+        <v>46097</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4102,7 +4107,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4145,7 +4150,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 15661-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4159,10 +4164,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46066</v>
+        <v>46106</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4175,7 +4180,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4218,7 +4223,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 35134-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4232,10 +4237,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45056</v>
+        <v>46260</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4248,7 +4253,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4291,7 +4296,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 17412-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4305,10 +4310,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46071</v>
+        <v>46120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4321,7 +4326,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4364,7 +4369,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 17386-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4378,10 +4383,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45719</v>
+        <v>46119</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4393,13 +4398,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4442,7 +4442,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 64846-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45715</v>
+        <v>45282</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4471,13 +4471,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4520,7 +4515,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 42541-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4530,14 +4525,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46087</v>
+        <v>46308</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4550,7 +4545,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4593,7 +4588,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 60138-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4607,10 +4602,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46196</v>
+        <v>44909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4623,7 +4618,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4666,7 +4661,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36352-2026</t>
+          <t>A 35833-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4680,10 +4675,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4696,7 +4691,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4739,7 +4734,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 36352-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4753,10 +4748,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46097</v>
+        <v>46268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4769,7 +4764,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4812,7 +4807,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 38800-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4826,10 +4821,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46106</v>
+        <v>45887</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4842,7 +4837,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4885,7 +4880,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 38243-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4899,10 +4894,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46119</v>
+        <v>45545</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4915,7 +4910,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4958,7 +4953,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 44170-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4972,10 +4967,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46120</v>
+        <v>46318</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4988,7 +4983,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5031,7 +5026,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 21294-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5045,10 +5040,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45281</v>
+        <v>46147</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5061,7 +5056,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5104,7 +5099,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5118,10 +5113,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45317</v>
+        <v>44784</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5133,13 +5128,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5182,7 +5172,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5196,10 +5186,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46209</v>
+        <v>44686</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5211,8 +5201,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5255,7 +5250,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 892-2023</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5269,10 +5264,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44931</v>
+        <v>45317</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5284,8 +5279,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8177-2024</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45351</v>
+        <v>45715</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5357,8 +5357,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5401,7 +5406,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37774-2024</t>
+          <t>A 50364-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5415,10 +5420,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45542</v>
+        <v>45600</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5431,7 +5436,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5474,7 +5479,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 20555-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5488,10 +5493,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46238</v>
+        <v>44700</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5504,7 +5509,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5547,7 +5552,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5561,10 +5566,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46286</v>
+        <v>44991</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5577,7 +5582,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5620,7 +5625,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 54555-2023</t>
+          <t>A 60768-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5634,10 +5639,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45233</v>
+        <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5650,7 +5655,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5693,7 +5698,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3320-2024</t>
+          <t>A 36603-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45317</v>
+        <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5722,13 +5727,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 34702-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45401</v>
+        <v>44795</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5844,7 +5844,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46254</v>
+        <v>45542</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5917,7 +5917,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44992-2023</t>
+          <t>A 62122-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45190</v>
+        <v>45656</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10889-2023</t>
+          <t>A 62373-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44991</v>
+        <v>44503</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6063,7 +6063,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34702-2022</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6077,10 +6077,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44795</v>
+        <v>44727</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>8.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6136,7 +6136,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 33817-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46260</v>
+        <v>45133</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6209,7 +6209,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36603-2022</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44804</v>
+        <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62373-2021</t>
+          <t>A 4954-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6296,10 +6296,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44503</v>
+        <v>45329</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62122-2024</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45656</v>
+        <v>44670</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35833-2026</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46265</v>
+        <v>45351</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42541-2026</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46308</v>
+        <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45131</v>
+        <v>45190</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45282</v>
+        <v>44931</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45750</v>
+        <v>45322</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6790,78 +6790,151 @@
       </c>
       <c r="V84" s="2" t="inlineStr"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
+          <t>A 3868-2024</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>45322</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>A 15306-2024</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="n">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="n">
         <v>45400</v>
       </c>
-      <c r="E85" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
+      <c r="E86" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
         <v>1.3</v>
       </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="2" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45887</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>44677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>45401</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45898</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>44503</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45131</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>46174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45950</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>45317</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44815</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>46196</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45979</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46209</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45446</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>46008</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>45056</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>45719</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>46238</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45719</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45715</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>46286</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45377</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46066</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>46071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45835</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45838</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>46254</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>46097</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>46106</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46260</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>46120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>46119</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45282</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>46308</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>46265</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45887</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>45545</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>46318</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>46147</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44784</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44686</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45317</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45715</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45600</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44700</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>44991</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44795</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45542</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45656</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44503</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44727</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45133</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45329</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44670</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45351</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45190</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44931</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45322</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45322</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45400</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44891</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45887</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>44677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>45401</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45898</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>44503</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45131</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>46174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45950</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>45317</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44815</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>46196</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45979</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46209</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45446</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>46008</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>45056</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>45719</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>46238</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45719</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45715</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>46286</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45377</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46066</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>46071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>46087</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45835</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45838</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>46254</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>46097</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>46106</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46260</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>46120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>46119</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45282</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>46308</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>46265</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45887</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>45545</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>46318</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>46147</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44784</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44686</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45317</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45715</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45600</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44700</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>44991</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44795</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45542</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45656</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44503</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44727</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45133</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45329</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44670</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45351</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45190</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44931</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45322</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45322</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45400</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>

--- a/Översikt ESSUNGA.xlsx
+++ b/Översikt ESSUNGA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56429-2022</t>
+          <t>A 3563-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44891</v>
+        <v>45320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,259 +647,259 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 40387-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 56429-2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44891</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESSUNGA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 56429-2022 artfynd.xlsx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 56429-2022 karta.png", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 56429-2022 georefererad karta.tif", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 56429-2022 FSC-klagomål.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 56429-2022 FSC-klagomål mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 56429-2022 tillsynsbegäran.docx", "A 56429-2022")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 56429-2022 tillsynsbegäran mail.docx", "A 56429-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 3563-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 3563-2024 artfynd.xlsx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 3563-2024 karta.png", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 3563-2024 georefererad karta.tif", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 3563-2024 FSC-klagomål.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 3563-2024 FSC-klagomål mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 3563-2024 tillsynsbegäran.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 3563-2024 tillsynsbegäran mail.docx", "A 3563-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 40387-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ESSUNGA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Röd glada</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/artfynd/A 40387-2026 artfynd.xlsx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor/A 40387-2026 karta.png", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/kartor_geotiff/A 40387-2026 georefererad karta.tif", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomål/A 40387-2026 FSC-klagomål.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/klagomålsmail/A 40387-2026 FSC-klagomål mail.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsyn/A 40387-2026 tillsynsbegäran.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/tillsynsmail/A 40387-2026 tillsynsbegäran mail.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1445/fåglar/A 40387-2026 prioriterade fågelarter.docx", "A 40387-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>44606</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44501</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44641</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>44503</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44686</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>44502</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44686</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38794-2025</t>
+          <t>A 18499-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45887</v>
+        <v>44686</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1521,8 +1521,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1565,7 +1570,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17072-2022</t>
+          <t>A 24686-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1579,10 +1584,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44677</v>
+        <v>44727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1594,13 +1599,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15552-2024</t>
+          <t>A 38794-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45401</v>
+        <v>45887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>45898</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64639-2023</t>
+          <t>A 3867-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45281</v>
+        <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1862,7 +1862,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45223-2025</t>
+          <t>A 3868-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45919</v>
+        <v>45322</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62360-2021</t>
+          <t>A 32914-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44503</v>
+        <v>44784</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2008,7 +2008,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33510-2023</t>
+          <t>A 13876-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45131</v>
+        <v>45007</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49693-2025</t>
+          <t>A 45223-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45939</v>
+        <v>45919</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24876-2026</t>
+          <t>A 62360-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46174</v>
+        <v>44503</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2227,7 +2227,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51380-2025</t>
+          <t>A 9375-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45950</v>
+        <v>45715</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2256,8 +2256,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2300,7 +2305,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16145-2025</t>
+          <t>A 49693-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2314,10 +2319,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45750</v>
+        <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2330,7 +2335,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2373,7 +2378,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3317-2024</t>
+          <t>A 51380-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2387,10 +2392,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45317</v>
+        <v>45950</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2402,13 +2407,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>10.2</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38715-2022</t>
+          <t>A 22279-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44815</v>
+        <v>45446</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2480,8 +2480,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2524,7 +2529,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28308-2026</t>
+          <t>A 20332-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46196</v>
+        <v>45056</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2554,7 +2559,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2614,7 +2619,7 @@
         <v>45979</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2670,7 +2675,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57161-2025</t>
+          <t>A 10164-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2684,10 +2689,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45979</v>
+        <v>45719</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2699,8 +2704,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2743,7 +2753,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30337-2026</t>
+          <t>A 57161-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2757,10 +2767,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46209</v>
+        <v>45979</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2773,7 +2783,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2816,7 +2826,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22279-2024</t>
+          <t>A 9374-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2830,10 +2840,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45446</v>
+        <v>45715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2847,11 +2857,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2894,7 +2904,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 46575-2025</t>
+          <t>A 16248-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2908,10 +2918,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45926</v>
+        <v>44670</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2924,7 +2934,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2967,7 +2977,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62737-2025</t>
+          <t>A 28308-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2981,10 +2991,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46008</v>
+        <v>46196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2997,7 +3007,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3040,7 +3050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20332-2023</t>
+          <t>A 64639-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3054,10 +3064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45056</v>
+        <v>45281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3070,7 +3080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3113,7 +3123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10161-2025</t>
+          <t>A 3317-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3127,10 +3137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45719</v>
+        <v>45317</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3148,7 +3158,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>10.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3191,7 +3201,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32414-2026</t>
+          <t>A 10690-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3205,10 +3215,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46238</v>
+        <v>45722</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3221,7 +3231,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3264,7 +3274,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10164-2025</t>
+          <t>A 12006-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3278,10 +3288,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45719</v>
+        <v>45377</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,13 +3303,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3342,7 +3347,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9374-2025</t>
+          <t>A 46575-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3356,10 +3361,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45715</v>
+        <v>45926</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3371,13 +3376,8 @@
           <t>ESSUNGA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38806-2026</t>
+          <t>A 892-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46286</v>
+        <v>44931</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10690-2025</t>
+          <t>A 8177-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45722</v>
+        <v>45351</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3566,7 +3566,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12006-2024</t>
+          <t>A 37774-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45377</v>
+        <v>45542</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8672-2026</t>
+          <t>A 62737-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46066</v>
+        <v>46008</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3712,7 +3712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9531-2026</t>
+          <t>A 10161-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46071</v>
+        <v>45719</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3741,8 +3741,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3785,7 +3790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12203-2026</t>
+          <t>A 32176-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3795,14 +3800,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46087</v>
+        <v>45835</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3815,7 +3820,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3858,7 +3863,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32176-2025</t>
+          <t>A 32615-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3868,14 +3873,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3888,7 +3893,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3931,7 +3936,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32615-2025</t>
+          <t>A 54555-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3945,10 +3950,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45838</v>
+        <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3961,7 +3966,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4004,7 +4009,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34360-2026</t>
+          <t>A 3320-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4018,10 +4023,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46254</v>
+        <v>45317</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4033,8 +4038,13 @@
           <t>ESSUNGA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4077,7 +4087,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13737-2026</t>
+          <t>A 30337-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4091,10 +4101,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46097</v>
+        <v>46209</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4107,7 +4117,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4150,7 +4160,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15661-2026</t>
+          <t>A 8672-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4164,10 +4174,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46106</v>
+        <v>46066</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4180,7 +4190,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4223,7 +4233,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35134-2026</t>
+          <t>A 9531-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4237,10 +4247,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46260</v>
+        <v>46071</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4253,7 +4263,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4296,7 +4306,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17412-2026</t>
+          <t>A 15552-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4310,10 +4320,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46120</v>
+        <v>45401</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4326,7 +4336,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4369,7 +4379,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17386-2026</t>
+          <t>A 44992-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4383,10 +4393,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46119</v>
+        <v>45190</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4399,7 +4409,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4442,7 +4452,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 64846-2023</t>
+          <t>A 10889-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4456,10 +4466,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45282</v>
+        <v>44991</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4472,7 +4482,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4515,7 +4525,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42541-2026</t>
+          <t>A 12203-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4525,14 +4535,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46308</v>
+        <v>46087</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4545,7 +4555,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4588,7 +4598,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60138-2022</t>
+          <t>A 13737-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4602,10 +4612,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n"